--- a/AMZN.xlsx
+++ b/AMZN.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC6262B9-D6D7-462E-A4B2-CC8437E08778}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A7B6300-AD81-4C62-BA47-ADC8A3312120}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" activeTab="1" xr2:uid="{479CF3AA-260E-4E31-88AC-4C0599CDC74D}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" xr2:uid="{479CF3AA-260E-4E31-88AC-4C0599CDC74D}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="73">
   <si>
     <t>Amazon</t>
   </si>
@@ -245,6 +245,18 @@
   <si>
     <t>FY25</t>
   </si>
+  <si>
+    <t>Q126</t>
+  </si>
+  <si>
+    <t>Q226</t>
+  </si>
+  <si>
+    <t>Q326</t>
+  </si>
+  <si>
+    <t>Q426</t>
+  </si>
 </sst>
 </file>
 
@@ -254,13 +266,19 @@
     <numFmt numFmtId="164" formatCode="#,##0;\(#,##0\)"/>
     <numFmt numFmtId="165" formatCode="#,##0.00;\(#,##0.00\)"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -338,31 +356,34 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -723,7 +744,7 @@
         <v>4</v>
       </c>
       <c r="I3" s="2">
-        <v>204</v>
+        <v>257.5</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
@@ -734,10 +755,10 @@
         <v>5</v>
       </c>
       <c r="I4" s="4">
-        <v>10709</v>
-      </c>
-      <c r="J4" s="13" t="s">
-        <v>66</v>
+        <v>10757.109436000001</v>
+      </c>
+      <c r="J4" s="15" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
@@ -746,7 +767,7 @@
       </c>
       <c r="I5" s="4">
         <f>I3*I4</f>
-        <v>2184636</v>
+        <v>2769955.6797700003</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
@@ -760,11 +781,11 @@
         <v>7</v>
       </c>
       <c r="I6" s="4">
-        <f>86810+36219</f>
-        <v>123029</v>
-      </c>
-      <c r="J6" s="13" t="s">
-        <v>66</v>
+        <f>101816+41273</f>
+        <v>143089</v>
+      </c>
+      <c r="J6" s="15" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
@@ -772,10 +793,10 @@
         <v>8</v>
       </c>
       <c r="I7" s="4">
-        <v>65648</v>
-      </c>
-      <c r="J7" s="13" t="s">
-        <v>66</v>
+        <v>119074</v>
+      </c>
+      <c r="J7" s="15" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
@@ -784,7 +805,7 @@
       </c>
       <c r="I8" s="4">
         <f>I5-I6+I7</f>
-        <v>2127255</v>
+        <v>2745940.6797700003</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
@@ -836,7 +857,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C4851AB-88E4-47B4-A48F-9BD557A151E9}">
-  <dimension ref="A1:AA484"/>
+  <dimension ref="A1:AE484"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.7109375" style="2" bestFit="1" customWidth="1"/>
@@ -844,12 +865,12 @@
     <col min="3" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C2" s="5" t="s">
         <v>12</v>
       </c>
@@ -886,32 +907,44 @@
       <c r="N2" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="P2" s="5" t="s">
+      <c r="O2" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="P2" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="Q2" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="R2" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="T2" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="Q2" s="5" t="s">
+      <c r="U2" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="R2" s="5" t="s">
+      <c r="V2" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="S2" s="5" t="s">
+      <c r="W2" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="T2" s="5" t="s">
+      <c r="X2" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="U2" s="5" t="s">
+      <c r="Y2" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="V2" s="5" t="s">
+      <c r="Z2" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="W2" s="13" t="s">
+      <c r="AA2" s="13" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B3" s="2" t="s">
         <v>44</v>
       </c>
@@ -925,7 +958,7 @@
         <v>87887</v>
       </c>
       <c r="F3" s="4">
-        <f>+V3-SUM(C3:E3)</f>
+        <f>+Z3-SUM(C3:E3)</f>
         <v>140183</v>
       </c>
       <c r="G3" s="4">
@@ -938,7 +971,7 @@
         <v>95537</v>
       </c>
       <c r="J3" s="4">
-        <f>+V3-SUM(G3:I3)</f>
+        <f>+Z3-SUM(G3:I3)</f>
         <v>115586</v>
       </c>
       <c r="K3" s="4">
@@ -953,23 +986,29 @@
       <c r="N3" s="4">
         <v>127083</v>
       </c>
-      <c r="O3" s="4"/>
+      <c r="O3" s="4">
+        <v>104143</v>
+      </c>
       <c r="P3" s="4"/>
       <c r="Q3" s="4"/>
       <c r="R3" s="4"/>
       <c r="S3" s="4"/>
       <c r="T3" s="4"/>
-      <c r="U3" s="4">
+      <c r="U3" s="4"/>
+      <c r="V3" s="4"/>
+      <c r="W3" s="4"/>
+      <c r="X3" s="4"/>
+      <c r="Y3" s="4">
         <v>352828</v>
       </c>
-      <c r="V3" s="4">
+      <c r="Z3" s="4">
         <v>387497</v>
       </c>
-      <c r="W3" s="4">
+      <c r="AA3" s="4">
         <v>426305</v>
       </c>
     </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B4" s="2" t="s">
         <v>45</v>
       </c>
@@ -983,7 +1022,7 @@
         <v>32137</v>
       </c>
       <c r="F4" s="4">
-        <f t="shared" ref="F4:F22" si="0">+V4-SUM(C4:E4)</f>
+        <f t="shared" ref="F4:F22" si="0">+Z4-SUM(C4:E4)</f>
         <v>51949</v>
       </c>
       <c r="G4" s="4">
@@ -996,7 +1035,7 @@
         <v>35888</v>
       </c>
       <c r="J4" s="4">
-        <f t="shared" ref="J4:J22" si="1">+V4-SUM(G4:I4)</f>
+        <f t="shared" ref="J4:J22" si="1">+Z4-SUM(G4:I4)</f>
         <v>43420</v>
       </c>
       <c r="K4" s="4">
@@ -1011,23 +1050,29 @@
       <c r="N4" s="14">
         <v>50724</v>
       </c>
-      <c r="O4" s="4"/>
-      <c r="P4" s="4"/>
-      <c r="Q4" s="4"/>
-      <c r="R4" s="4"/>
+      <c r="O4" s="14">
+        <v>39789</v>
+      </c>
+      <c r="P4" s="14"/>
+      <c r="Q4" s="14"/>
+      <c r="R4" s="14"/>
       <c r="S4" s="4"/>
       <c r="T4" s="4"/>
-      <c r="U4" s="4">
+      <c r="U4" s="4"/>
+      <c r="V4" s="4"/>
+      <c r="W4" s="4"/>
+      <c r="X4" s="4"/>
+      <c r="Y4" s="4">
         <v>131200</v>
       </c>
-      <c r="V4" s="4">
+      <c r="Z4" s="4">
         <v>142906</v>
       </c>
-      <c r="W4" s="4">
+      <c r="AA4" s="4">
         <v>161894</v>
       </c>
     </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B5" s="2" t="s">
         <v>46</v>
       </c>
@@ -1069,23 +1114,29 @@
       <c r="N5" s="4">
         <v>35579</v>
       </c>
-      <c r="O5" s="4"/>
+      <c r="O5" s="4">
+        <v>37587</v>
+      </c>
       <c r="P5" s="4"/>
       <c r="Q5" s="4"/>
       <c r="R5" s="4"/>
       <c r="S5" s="4"/>
       <c r="T5" s="4"/>
-      <c r="U5" s="4">
+      <c r="U5" s="4"/>
+      <c r="V5" s="4"/>
+      <c r="W5" s="4"/>
+      <c r="X5" s="4"/>
+      <c r="Y5" s="4">
         <v>90757</v>
       </c>
-      <c r="V5" s="4">
+      <c r="Z5" s="4">
         <v>106556</v>
       </c>
-      <c r="W5" s="4">
+      <c r="AA5" s="4">
         <v>128725</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="2" t="s">
         <v>20</v>
       </c>
@@ -1127,25 +1178,31 @@
       <c r="N6" s="4">
         <v>89992</v>
       </c>
-      <c r="O6" s="4"/>
+      <c r="O6" s="4">
+        <v>71304</v>
+      </c>
       <c r="P6" s="4"/>
       <c r="Q6" s="4"/>
       <c r="R6" s="4"/>
       <c r="S6" s="4"/>
-      <c r="T6" s="4">
+      <c r="T6" s="4"/>
+      <c r="U6" s="4"/>
+      <c r="V6" s="4"/>
+      <c r="W6" s="4"/>
+      <c r="X6" s="4">
         <v>242901</v>
       </c>
-      <c r="U6" s="4">
+      <c r="Y6" s="4">
         <v>255887</v>
       </c>
-      <c r="V6" s="4">
+      <c r="Z6" s="4">
         <v>272311</v>
       </c>
-      <c r="W6" s="4">
+      <c r="AA6" s="4">
         <v>296266</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B7" s="2" t="s">
         <v>21</v>
       </c>
@@ -1187,25 +1244,31 @@
       <c r="N7" s="4">
         <v>123394</v>
       </c>
-      <c r="O7" s="4"/>
+      <c r="O7" s="4">
+        <v>110215</v>
+      </c>
       <c r="P7" s="4"/>
       <c r="Q7" s="4"/>
       <c r="R7" s="4"/>
       <c r="S7" s="4"/>
-      <c r="T7" s="4">
+      <c r="T7" s="4"/>
+      <c r="U7" s="4"/>
+      <c r="V7" s="4"/>
+      <c r="W7" s="4"/>
+      <c r="X7" s="4">
         <v>271082</v>
       </c>
-      <c r="U7" s="4">
+      <c r="Y7" s="4">
         <v>318898</v>
       </c>
-      <c r="V7" s="4">
+      <c r="Z7" s="4">
         <v>365648</v>
       </c>
-      <c r="W7" s="4">
+      <c r="AA7" s="4">
         <v>420658</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B8" s="1" t="s">
         <v>19</v>
       </c>
@@ -1234,7 +1297,7 @@
         <v>147977</v>
       </c>
       <c r="I8" s="9">
-        <f t="shared" ref="I8:N8" si="3">SUM(I6:I7)</f>
+        <f t="shared" ref="I8:O8" si="3">SUM(I6:I7)</f>
         <v>158877</v>
       </c>
       <c r="J8" s="9">
@@ -1257,26 +1320,33 @@
         <f t="shared" si="3"/>
         <v>213386</v>
       </c>
-      <c r="O8" s="4"/>
-      <c r="P8" s="4"/>
-      <c r="Q8" s="4"/>
+      <c r="O8" s="9">
+        <f t="shared" si="3"/>
+        <v>181519</v>
+      </c>
+      <c r="P8" s="9"/>
+      <c r="Q8" s="9"/>
       <c r="R8" s="9"/>
-      <c r="S8" s="9"/>
-      <c r="T8" s="9">
-        <f>+T6+T7</f>
+      <c r="S8" s="4"/>
+      <c r="T8" s="4"/>
+      <c r="U8" s="4"/>
+      <c r="V8" s="9"/>
+      <c r="W8" s="9"/>
+      <c r="X8" s="9">
+        <f>+X6+X7</f>
         <v>513983</v>
       </c>
-      <c r="U8" s="9">
+      <c r="Y8" s="9">
         <v>574785</v>
       </c>
-      <c r="V8" s="9">
+      <c r="Z8" s="9">
         <v>637959</v>
       </c>
-      <c r="W8" s="9">
+      <c r="AA8" s="9">
         <v>716924</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B9" s="2" t="s">
         <v>22</v>
       </c>
@@ -1318,25 +1388,31 @@
       <c r="N9" s="4">
         <v>109959</v>
       </c>
-      <c r="O9" s="4"/>
+      <c r="O9" s="4">
+        <v>87463</v>
+      </c>
       <c r="P9" s="4"/>
       <c r="Q9" s="4"/>
       <c r="R9" s="4"/>
       <c r="S9" s="4"/>
-      <c r="T9" s="4">
+      <c r="T9" s="4"/>
+      <c r="U9" s="4"/>
+      <c r="V9" s="4"/>
+      <c r="W9" s="4"/>
+      <c r="X9" s="4">
         <v>288831</v>
       </c>
-      <c r="U9" s="4">
+      <c r="Y9" s="4">
         <v>304739</v>
       </c>
-      <c r="V9" s="4">
+      <c r="Z9" s="4">
         <v>326288</v>
       </c>
-      <c r="W9" s="4">
+      <c r="AA9" s="4">
         <v>356414</v>
       </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B10" s="2" t="s">
         <v>23</v>
       </c>
@@ -1388,32 +1464,39 @@
         <f>N8-N9</f>
         <v>103427</v>
       </c>
-      <c r="O10" s="4"/>
+      <c r="O10" s="4">
+        <f>O8-O9</f>
+        <v>94056</v>
+      </c>
       <c r="P10" s="4"/>
       <c r="Q10" s="4"/>
       <c r="R10" s="4"/>
-      <c r="S10" s="4">
-        <f t="shared" ref="S10:U10" si="6">+S8-S9</f>
+      <c r="S10" s="4"/>
+      <c r="T10" s="4"/>
+      <c r="U10" s="4"/>
+      <c r="V10" s="4"/>
+      <c r="W10" s="4">
+        <f t="shared" ref="W10:Y10" si="6">+W8-W9</f>
         <v>0</v>
       </c>
-      <c r="T10" s="4">
+      <c r="X10" s="4">
         <f t="shared" si="6"/>
         <v>225152</v>
       </c>
-      <c r="U10" s="4">
+      <c r="Y10" s="4">
         <f t="shared" si="6"/>
         <v>270046</v>
       </c>
-      <c r="V10" s="4">
-        <f>+V8-V9</f>
+      <c r="Z10" s="4">
+        <f>+Z8-Z9</f>
         <v>311671</v>
       </c>
-      <c r="W10" s="4">
-        <f>+W8-W9</f>
+      <c r="AA10" s="4">
+        <f>+AA8-AA9</f>
         <v>360510</v>
       </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B11" s="2" t="s">
         <v>24</v>
       </c>
@@ -1455,25 +1538,31 @@
       <c r="N11" s="4">
         <v>30826</v>
       </c>
-      <c r="O11" s="4"/>
+      <c r="O11" s="4">
+        <v>27289</v>
+      </c>
       <c r="P11" s="4"/>
       <c r="Q11" s="4"/>
       <c r="R11" s="4"/>
       <c r="S11" s="4"/>
-      <c r="T11" s="4">
+      <c r="T11" s="4"/>
+      <c r="U11" s="4"/>
+      <c r="V11" s="4"/>
+      <c r="W11" s="4"/>
+      <c r="X11" s="4">
         <v>84299</v>
       </c>
-      <c r="U11" s="4">
+      <c r="Y11" s="4">
         <v>90619</v>
       </c>
-      <c r="V11" s="4">
+      <c r="Z11" s="4">
         <v>98505</v>
       </c>
-      <c r="W11" s="4">
+      <c r="AA11" s="4">
         <v>109074</v>
       </c>
     </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B12" s="2" t="s">
         <v>25</v>
       </c>
@@ -1515,25 +1604,31 @@
       <c r="N12" s="4">
         <v>29399</v>
       </c>
-      <c r="O12" s="4"/>
+      <c r="O12" s="4">
+        <v>29567</v>
+      </c>
       <c r="P12" s="4"/>
       <c r="Q12" s="4"/>
       <c r="R12" s="4"/>
       <c r="S12" s="4"/>
-      <c r="T12" s="4">
+      <c r="T12" s="4"/>
+      <c r="U12" s="4"/>
+      <c r="V12" s="4"/>
+      <c r="W12" s="4"/>
+      <c r="X12" s="4">
         <v>73213</v>
       </c>
-      <c r="U12" s="4">
+      <c r="Y12" s="4">
         <v>85622</v>
       </c>
-      <c r="V12" s="4">
+      <c r="Z12" s="4">
         <v>88544</v>
       </c>
-      <c r="W12" s="4">
+      <c r="AA12" s="4">
         <v>108521</v>
       </c>
     </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B13" s="2" t="s">
         <v>27</v>
       </c>
@@ -1575,25 +1670,31 @@
       <c r="N13" s="4">
         <v>14264</v>
       </c>
-      <c r="O13" s="4"/>
+      <c r="O13" s="4">
+        <v>10314</v>
+      </c>
       <c r="P13" s="4"/>
       <c r="Q13" s="4"/>
       <c r="R13" s="4"/>
       <c r="S13" s="4"/>
-      <c r="T13" s="4">
+      <c r="T13" s="4"/>
+      <c r="U13" s="4"/>
+      <c r="V13" s="4"/>
+      <c r="W13" s="4"/>
+      <c r="X13" s="4">
         <v>42238</v>
       </c>
-      <c r="U13" s="4">
+      <c r="Y13" s="4">
         <v>44370</v>
       </c>
-      <c r="V13" s="4">
+      <c r="Z13" s="4">
         <v>43907</v>
       </c>
-      <c r="W13" s="4">
+      <c r="AA13" s="4">
         <v>47129</v>
       </c>
     </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B14" s="2" t="s">
         <v>26</v>
       </c>
@@ -1635,25 +1736,31 @@
       <c r="N14" s="4">
         <v>2704</v>
       </c>
-      <c r="O14" s="4"/>
+      <c r="O14" s="4">
+        <v>2587</v>
+      </c>
       <c r="P14" s="4"/>
       <c r="Q14" s="4"/>
       <c r="R14" s="4"/>
       <c r="S14" s="4"/>
-      <c r="T14" s="4">
+      <c r="T14" s="4"/>
+      <c r="U14" s="4"/>
+      <c r="V14" s="4"/>
+      <c r="W14" s="4"/>
+      <c r="X14" s="4">
         <v>11891</v>
       </c>
-      <c r="U14" s="4">
+      <c r="Y14" s="4">
         <v>11816</v>
       </c>
-      <c r="V14" s="4">
+      <c r="Z14" s="4">
         <v>11359</v>
       </c>
-      <c r="W14" s="4">
+      <c r="AA14" s="4">
         <v>11172</v>
       </c>
     </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B15" s="2" t="s">
         <v>29</v>
       </c>
@@ -1695,25 +1802,31 @@
       <c r="N15" s="4">
         <v>1257</v>
       </c>
-      <c r="O15" s="4"/>
+      <c r="O15" s="4">
+        <v>447</v>
+      </c>
       <c r="P15" s="4"/>
       <c r="Q15" s="4"/>
       <c r="R15" s="4"/>
       <c r="S15" s="4"/>
-      <c r="T15" s="4">
+      <c r="T15" s="4"/>
+      <c r="U15" s="4"/>
+      <c r="V15" s="4"/>
+      <c r="W15" s="4"/>
+      <c r="X15" s="4">
         <v>1263</v>
       </c>
-      <c r="U15" s="4">
+      <c r="Y15" s="4">
         <v>767</v>
       </c>
-      <c r="V15" s="4">
+      <c r="Z15" s="4">
         <v>763</v>
       </c>
-      <c r="W15" s="4">
+      <c r="AA15" s="4">
         <v>4639</v>
       </c>
     </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B16" s="2" t="s">
         <v>28</v>
       </c>
@@ -1742,7 +1855,7 @@
         <v>14672</v>
       </c>
       <c r="I16" s="4">
-        <f t="shared" ref="I16:W16" si="8">I10-SUM(I11:I15)</f>
+        <f t="shared" ref="I16:AA16" si="8">I10-SUM(I11:I15)</f>
         <v>17411</v>
       </c>
       <c r="J16" s="4">
@@ -1765,41 +1878,48 @@
         <f>N10-SUM(N11:N15)</f>
         <v>24977</v>
       </c>
-      <c r="O16" s="4"/>
-      <c r="P16" s="4">
+      <c r="O16" s="4">
+        <f>O10-SUM(O11:O15)</f>
+        <v>23852</v>
+      </c>
+      <c r="P16" s="4"/>
+      <c r="Q16" s="4"/>
+      <c r="R16" s="4"/>
+      <c r="S16" s="4"/>
+      <c r="T16" s="4">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="Q16" s="4">
+      <c r="U16" s="4">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="R16" s="4">
+      <c r="V16" s="4">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="S16" s="4">
+      <c r="W16" s="4">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="T16" s="4">
+      <c r="X16" s="4">
         <f t="shared" si="8"/>
         <v>12248</v>
       </c>
-      <c r="U16" s="4">
+      <c r="Y16" s="4">
         <f t="shared" si="8"/>
         <v>36852</v>
       </c>
-      <c r="V16" s="4">
+      <c r="Z16" s="4">
         <f t="shared" si="8"/>
         <v>68593</v>
       </c>
-      <c r="W16" s="4">
+      <c r="AA16" s="4">
         <f t="shared" si="8"/>
         <v>79975</v>
       </c>
     </row>
-    <row r="17" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B17" s="2" t="s">
         <v>31</v>
       </c>
@@ -1841,25 +1961,31 @@
       <c r="N17" s="4">
         <v>1130</v>
       </c>
-      <c r="O17" s="4"/>
+      <c r="O17" s="4">
+        <v>1135</v>
+      </c>
       <c r="P17" s="4"/>
       <c r="Q17" s="4"/>
       <c r="R17" s="4"/>
       <c r="S17" s="4"/>
-      <c r="T17" s="4">
+      <c r="T17" s="4"/>
+      <c r="U17" s="4"/>
+      <c r="V17" s="4"/>
+      <c r="W17" s="4"/>
+      <c r="X17" s="4">
         <v>989</v>
       </c>
-      <c r="U17" s="4">
+      <c r="Y17" s="4">
         <v>2949</v>
       </c>
-      <c r="V17" s="4">
+      <c r="Z17" s="4">
         <v>4677</v>
       </c>
-      <c r="W17" s="4">
+      <c r="AA17" s="4">
         <v>4381</v>
       </c>
     </row>
-    <row r="18" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B18" s="2" t="s">
         <v>30</v>
       </c>
@@ -1901,25 +2027,31 @@
       <c r="N18" s="4">
         <v>679</v>
       </c>
-      <c r="O18" s="4"/>
+      <c r="O18" s="4">
+        <v>800</v>
+      </c>
       <c r="P18" s="4"/>
       <c r="Q18" s="4"/>
       <c r="R18" s="4"/>
       <c r="S18" s="4"/>
-      <c r="T18" s="4">
+      <c r="T18" s="4"/>
+      <c r="U18" s="4"/>
+      <c r="V18" s="4"/>
+      <c r="W18" s="4"/>
+      <c r="X18" s="4">
         <v>2367</v>
       </c>
-      <c r="U18" s="4">
+      <c r="Y18" s="4">
         <v>3182</v>
       </c>
-      <c r="V18" s="4">
+      <c r="Z18" s="4">
         <v>2406</v>
       </c>
-      <c r="W18" s="4">
+      <c r="AA18" s="4">
         <v>2274</v>
       </c>
     </row>
-    <row r="19" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B19" s="2" t="s">
         <v>29</v>
       </c>
@@ -1961,25 +2093,31 @@
       <c r="N19" s="4">
         <v>-1177</v>
       </c>
-      <c r="O19" s="4"/>
+      <c r="O19" s="4">
+        <v>-15647</v>
+      </c>
       <c r="P19" s="4"/>
       <c r="Q19" s="4"/>
       <c r="R19" s="4"/>
       <c r="S19" s="4"/>
-      <c r="T19" s="4">
+      <c r="T19" s="4"/>
+      <c r="U19" s="4"/>
+      <c r="V19" s="4"/>
+      <c r="W19" s="4"/>
+      <c r="X19" s="4">
         <v>16806</v>
       </c>
-      <c r="U19" s="4">
+      <c r="Y19" s="4">
         <v>-938</v>
       </c>
-      <c r="V19" s="4">
+      <c r="Z19" s="4">
         <v>2250</v>
       </c>
-      <c r="W19" s="4">
+      <c r="AA19" s="4">
         <v>-15229</v>
       </c>
     </row>
-    <row r="20" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B20" s="2" t="s">
         <v>32</v>
       </c>
@@ -2008,7 +2146,7 @@
         <v>15245</v>
       </c>
       <c r="I20" s="4">
-        <f t="shared" ref="I20:W20" si="10">I16+I17-I18-I19</f>
+        <f t="shared" ref="I20:AA20" si="10">I16+I17-I18-I19</f>
         <v>18037</v>
       </c>
       <c r="J20" s="4">
@@ -2031,41 +2169,48 @@
         <f t="shared" si="10"/>
         <v>26605</v>
       </c>
-      <c r="O20" s="4"/>
-      <c r="P20" s="4">
+      <c r="O20" s="4">
+        <f t="shared" si="10"/>
+        <v>39834</v>
+      </c>
+      <c r="P20" s="4"/>
+      <c r="Q20" s="4"/>
+      <c r="R20" s="4"/>
+      <c r="S20" s="4"/>
+      <c r="T20" s="4">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="Q20" s="4">
+      <c r="U20" s="4">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="R20" s="4">
+      <c r="V20" s="4">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="S20" s="4">
+      <c r="W20" s="4">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="T20" s="4">
+      <c r="X20" s="4">
         <f t="shared" si="10"/>
         <v>-5936</v>
       </c>
-      <c r="U20" s="4">
+      <c r="Y20" s="4">
         <f t="shared" si="10"/>
         <v>37557</v>
       </c>
-      <c r="V20" s="4">
+      <c r="Z20" s="4">
         <f t="shared" si="10"/>
         <v>68614</v>
       </c>
-      <c r="W20" s="4">
+      <c r="AA20" s="4">
         <f t="shared" si="10"/>
         <v>97311</v>
       </c>
     </row>
-    <row r="21" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B21" s="2" t="s">
         <v>33</v>
       </c>
@@ -2109,25 +2254,31 @@
       <c r="N21" s="4">
         <v>4946</v>
       </c>
-      <c r="O21" s="4"/>
+      <c r="O21" s="4">
+        <v>9560</v>
+      </c>
       <c r="P21" s="4"/>
       <c r="Q21" s="4"/>
       <c r="R21" s="4"/>
       <c r="S21" s="4"/>
-      <c r="T21" s="4">
+      <c r="T21" s="4"/>
+      <c r="U21" s="4"/>
+      <c r="V21" s="4"/>
+      <c r="W21" s="4"/>
+      <c r="X21" s="4">
         <v>-3217</v>
       </c>
-      <c r="U21" s="4">
+      <c r="Y21" s="4">
         <v>7120</v>
       </c>
-      <c r="V21" s="4">
+      <c r="Z21" s="4">
         <v>9265</v>
       </c>
-      <c r="W21" s="4">
+      <c r="AA21" s="4">
         <v>19087</v>
       </c>
     </row>
-    <row r="22" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B22" s="2" t="s">
         <v>41</v>
       </c>
@@ -2169,25 +2320,31 @@
       <c r="N22" s="4">
         <v>467</v>
       </c>
-      <c r="O22" s="4"/>
+      <c r="O22" s="4">
+        <v>19</v>
+      </c>
       <c r="P22" s="4"/>
       <c r="Q22" s="4"/>
       <c r="R22" s="4"/>
       <c r="S22" s="4"/>
-      <c r="T22" s="4">
+      <c r="T22" s="4"/>
+      <c r="U22" s="4"/>
+      <c r="V22" s="4"/>
+      <c r="W22" s="4"/>
+      <c r="X22" s="4">
         <v>3</v>
       </c>
-      <c r="U22" s="4">
+      <c r="Y22" s="4">
         <v>12</v>
       </c>
-      <c r="V22" s="4">
+      <c r="Z22" s="4">
         <v>101</v>
       </c>
-      <c r="W22" s="4">
+      <c r="AA22" s="4">
         <v>554</v>
       </c>
     </row>
-    <row r="23" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B23" s="2" t="s">
         <v>34</v>
       </c>
@@ -2220,7 +2377,7 @@
         <v>15328</v>
       </c>
       <c r="J23" s="4">
-        <f t="shared" ref="J23:W23" si="12">+J20-J21-J22</f>
+        <f t="shared" ref="J22:AA23" si="12">+J20-J21-J22</f>
         <v>20004</v>
       </c>
       <c r="K23" s="4">
@@ -2239,41 +2396,48 @@
         <f t="shared" si="12"/>
         <v>21192</v>
       </c>
-      <c r="O23" s="4"/>
-      <c r="P23" s="4">
+      <c r="O23" s="4">
+        <f t="shared" si="12"/>
+        <v>30255</v>
+      </c>
+      <c r="P23" s="4"/>
+      <c r="Q23" s="4"/>
+      <c r="R23" s="4"/>
+      <c r="S23" s="4"/>
+      <c r="T23" s="4">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="Q23" s="4">
+      <c r="U23" s="4">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="R23" s="4">
+      <c r="V23" s="4">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="S23" s="4">
+      <c r="W23" s="4">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="T23" s="4">
+      <c r="X23" s="4">
         <f t="shared" si="12"/>
         <v>-2722</v>
       </c>
-      <c r="U23" s="4">
+      <c r="Y23" s="4">
         <f t="shared" si="12"/>
         <v>30425</v>
       </c>
-      <c r="V23" s="4">
+      <c r="Z23" s="4">
         <f t="shared" si="12"/>
         <v>59248</v>
       </c>
-      <c r="W23" s="4">
+      <c r="AA23" s="4">
         <f t="shared" si="12"/>
         <v>77670</v>
       </c>
     </row>
-    <row r="24" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C24" s="4"/>
       <c r="D24" s="4"/>
       <c r="E24" s="4"/>
@@ -2294,8 +2458,12 @@
       <c r="T24" s="4"/>
       <c r="U24" s="4"/>
       <c r="V24" s="4"/>
-    </row>
-    <row r="25" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="W24" s="4"/>
+      <c r="X24" s="4"/>
+      <c r="Y24" s="4"/>
+      <c r="Z24" s="4"/>
+    </row>
+    <row r="25" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B25" s="2" t="s">
         <v>35</v>
       </c>
@@ -2347,38 +2515,45 @@
         <f>N23/N26</f>
         <v>1.9788962554860399</v>
       </c>
-      <c r="O25" s="4"/>
-      <c r="P25" s="4"/>
-      <c r="Q25" s="10" t="e">
-        <f t="shared" ref="Q25:U25" si="15">+Q23/Q26</f>
+      <c r="O25" s="10">
+        <f>O23/O26</f>
+        <v>2.8162524434515497</v>
+      </c>
+      <c r="P25" s="10"/>
+      <c r="Q25" s="10"/>
+      <c r="R25" s="10"/>
+      <c r="S25" s="4"/>
+      <c r="T25" s="4"/>
+      <c r="U25" s="10" t="e">
+        <f t="shared" ref="U25:Y25" si="15">+U23/U26</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="R25" s="10" t="e">
+      <c r="V25" s="10" t="e">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="S25" s="10" t="e">
+      <c r="W25" s="10" t="e">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="T25" s="10">
+      <c r="X25" s="10">
         <f t="shared" si="15"/>
         <v>-0.2671508489547551</v>
       </c>
-      <c r="U25" s="10">
+      <c r="Y25" s="10">
         <f t="shared" si="15"/>
         <v>2.9527368012422359</v>
       </c>
-      <c r="V25" s="10">
-        <f>+V23/V26</f>
+      <c r="Z25" s="10">
+        <f>+Z23/Z26</f>
         <v>5.6572137878353859</v>
       </c>
-      <c r="W25" s="10">
-        <f>+W23/W26</f>
+      <c r="AA25" s="10">
+        <f>+AA23/AA26</f>
         <v>7.2888513513513518</v>
       </c>
     </row>
-    <row r="26" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B26" s="2" t="s">
         <v>5</v>
       </c>
@@ -2418,29 +2593,35 @@
       <c r="N26" s="4">
         <v>10709</v>
       </c>
-      <c r="O26" s="4"/>
+      <c r="O26" s="4">
+        <v>10743</v>
+      </c>
       <c r="P26" s="4"/>
       <c r="Q26" s="4"/>
       <c r="R26" s="4"/>
       <c r="S26" s="4"/>
-      <c r="T26" s="4">
+      <c r="T26" s="4"/>
+      <c r="U26" s="4"/>
+      <c r="V26" s="4"/>
+      <c r="W26" s="4"/>
+      <c r="X26" s="4">
         <v>10189</v>
       </c>
-      <c r="U26" s="4">
+      <c r="Y26" s="4">
         <v>10304</v>
       </c>
-      <c r="V26" s="4">
+      <c r="Z26" s="4">
         <v>10473</v>
       </c>
-      <c r="W26" s="4">
+      <c r="AA26" s="4">
         <v>10656</v>
       </c>
-      <c r="X26" s="4"/>
-      <c r="Y26" s="4"/>
-      <c r="Z26" s="4"/>
-      <c r="AA26" s="4"/>
-    </row>
-    <row r="27" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB26" s="4"/>
+      <c r="AC26" s="4"/>
+      <c r="AD26" s="4"/>
+      <c r="AE26" s="4"/>
+    </row>
+    <row r="27" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C27" s="4"/>
       <c r="D27" s="4"/>
       <c r="E27" s="4"/>
@@ -2461,8 +2642,12 @@
       <c r="T27" s="4"/>
       <c r="U27" s="4"/>
       <c r="V27" s="4"/>
-    </row>
-    <row r="28" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="W27" s="4"/>
+      <c r="X27" s="4"/>
+      <c r="Y27" s="4"/>
+      <c r="Z27" s="4"/>
+    </row>
+    <row r="28" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B28" s="2" t="s">
         <v>67</v>
       </c>
@@ -2475,7 +2660,7 @@
         <v>0.17247354125690739</v>
       </c>
       <c r="H28" s="11">
-        <f t="shared" ref="H28:N28" si="16">H5/D5-1</f>
+        <f t="shared" ref="H28:O28" si="16">H5/D5-1</f>
         <v>0.18703703703703711</v>
       </c>
       <c r="I28" s="11">
@@ -2502,16 +2687,23 @@
         <f t="shared" si="16"/>
         <v>0.28046498236521988</v>
       </c>
-      <c r="O28" s="4"/>
-      <c r="P28" s="4"/>
-      <c r="Q28" s="4"/>
-      <c r="R28" s="4"/>
+      <c r="O28" s="11">
+        <f t="shared" si="16"/>
+        <v>0.28427922233231961</v>
+      </c>
+      <c r="P28" s="11"/>
+      <c r="Q28" s="11"/>
+      <c r="R28" s="11"/>
       <c r="S28" s="4"/>
       <c r="T28" s="4"/>
       <c r="U28" s="4"/>
       <c r="V28" s="4"/>
-    </row>
-    <row r="29" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="W28" s="4"/>
+      <c r="X28" s="4"/>
+      <c r="Y28" s="4"/>
+      <c r="Z28" s="4"/>
+    </row>
+    <row r="29" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B29" s="2" t="s">
         <v>42</v>
       </c>
@@ -2528,7 +2720,7 @@
         <v>4.2976690608483636E-2</v>
       </c>
       <c r="I29" s="11">
-        <f t="shared" ref="I29:N31" si="18">I6/E6-1</f>
+        <f t="shared" ref="I29:O31" si="18">I6/E6-1</f>
         <v>7.0127115290243847E-2</v>
       </c>
       <c r="J29" s="11">
@@ -2551,16 +2743,23 @@
         <f t="shared" si="18"/>
         <v>9.4447011894048138E-2</v>
       </c>
-      <c r="O29" s="4"/>
-      <c r="P29" s="4"/>
-      <c r="Q29" s="4"/>
-      <c r="R29" s="4"/>
+      <c r="O29" s="11">
+        <f t="shared" si="18"/>
+        <v>0.1146474910114117</v>
+      </c>
+      <c r="P29" s="11"/>
+      <c r="Q29" s="11"/>
+      <c r="R29" s="11"/>
       <c r="S29" s="4"/>
       <c r="T29" s="4"/>
       <c r="U29" s="4"/>
       <c r="V29" s="4"/>
-    </row>
-    <row r="30" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="W29" s="4"/>
+      <c r="X29" s="4"/>
+      <c r="Y29" s="4"/>
+      <c r="Z29" s="4"/>
+    </row>
+    <row r="30" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B30" s="2" t="s">
         <v>43</v>
       </c>
@@ -2600,16 +2799,23 @@
         <f t="shared" si="18"/>
         <v>0.168880131860637</v>
       </c>
-      <c r="O30" s="4"/>
-      <c r="P30" s="4"/>
-      <c r="Q30" s="4"/>
-      <c r="R30" s="4"/>
+      <c r="O30" s="11">
+        <f t="shared" si="18"/>
+        <v>0.20194771911840093</v>
+      </c>
+      <c r="P30" s="11"/>
+      <c r="Q30" s="11"/>
+      <c r="R30" s="11"/>
       <c r="S30" s="4"/>
       <c r="T30" s="4"/>
       <c r="U30" s="4"/>
       <c r="V30" s="4"/>
-    </row>
-    <row r="31" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="W30" s="4"/>
+      <c r="X30" s="4"/>
+      <c r="Y30" s="4"/>
+      <c r="Z30" s="4"/>
+    </row>
+    <row r="31" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B31" s="1" t="s">
         <v>36</v>
       </c>
@@ -2649,16 +2855,23 @@
         <f t="shared" si="18"/>
         <v>0.13628908579705201</v>
       </c>
-      <c r="O31" s="4"/>
-      <c r="P31" s="4"/>
-      <c r="Q31" s="4"/>
-      <c r="R31" s="4"/>
+      <c r="O31" s="12">
+        <f t="shared" si="18"/>
+        <v>0.16607244952366274</v>
+      </c>
+      <c r="P31" s="12"/>
+      <c r="Q31" s="12"/>
+      <c r="R31" s="12"/>
       <c r="S31" s="4"/>
       <c r="T31" s="4"/>
       <c r="U31" s="4"/>
       <c r="V31" s="4"/>
-    </row>
-    <row r="32" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="W31" s="4"/>
+      <c r="X31" s="4"/>
+      <c r="Y31" s="4"/>
+      <c r="Z31" s="4"/>
+    </row>
+    <row r="32" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B32" s="2" t="s">
         <v>38</v>
       </c>
@@ -2710,16 +2923,23 @@
         <f>N10/N8</f>
         <v>0.48469440356911886</v>
       </c>
-      <c r="O32" s="4"/>
-      <c r="P32" s="4"/>
-      <c r="Q32" s="4"/>
-      <c r="R32" s="4"/>
+      <c r="O32" s="11">
+        <f>O10/O8</f>
+        <v>0.51816063332213158</v>
+      </c>
+      <c r="P32" s="11"/>
+      <c r="Q32" s="11"/>
+      <c r="R32" s="11"/>
       <c r="S32" s="4"/>
       <c r="T32" s="4"/>
       <c r="U32" s="4"/>
       <c r="V32" s="4"/>
-    </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W32" s="4"/>
+      <c r="X32" s="4"/>
+      <c r="Y32" s="4"/>
+      <c r="Z32" s="4"/>
+    </row>
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B33" s="2" t="s">
         <v>37</v>
       </c>
@@ -2771,37 +2991,44 @@
         <f t="shared" si="24"/>
         <v>0.11705079058607407</v>
       </c>
-      <c r="O33" s="4"/>
-      <c r="P33" s="4"/>
-      <c r="Q33" s="4"/>
-      <c r="R33" s="4"/>
+      <c r="O33" s="11">
+        <f t="shared" ref="O33" si="25">O16/O8</f>
+        <v>0.13140222235688825</v>
+      </c>
+      <c r="P33" s="11"/>
+      <c r="Q33" s="11"/>
+      <c r="R33" s="11"/>
       <c r="S33" s="4"/>
       <c r="T33" s="4"/>
       <c r="U33" s="4"/>
       <c r="V33" s="4"/>
-    </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W33" s="4"/>
+      <c r="X33" s="4"/>
+      <c r="Y33" s="4"/>
+      <c r="Z33" s="4"/>
+    </row>
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B34" s="2" t="s">
         <v>39</v>
       </c>
       <c r="C34" s="11">
-        <f t="shared" ref="C34:G34" si="25">C21/C20</f>
+        <f t="shared" ref="C34:G34" si="26">C21/C20</f>
         <v>0.23015294974508377</v>
       </c>
       <c r="D34" s="11">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0.10630702102340341</v>
       </c>
       <c r="E34" s="11">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0.18918697185987365</v>
       </c>
       <c r="F34" s="11">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0.11637574592673715</v>
       </c>
       <c r="G34" s="11">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0.1900177154740815</v>
       </c>
       <c r="H34" s="11">
@@ -2809,39 +3036,46 @@
         <v>0.11590685470646113</v>
       </c>
       <c r="I34" s="11">
-        <f t="shared" ref="I34:J34" si="26">I21/I20</f>
+        <f t="shared" ref="I34:J34" si="27">I21/I20</f>
         <v>0.15002494871652713</v>
       </c>
       <c r="J34" s="11">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0.10403150029084075</v>
       </c>
       <c r="K34" s="11">
-        <f t="shared" ref="K34:L34" si="27">K21/K20</f>
+        <f t="shared" ref="K34:L34" si="28">K21/K20</f>
         <v>0.21001891231145348</v>
       </c>
       <c r="L34" s="11">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0.1283981397132857</v>
       </c>
       <c r="M34" s="11">
-        <f t="shared" ref="M34:N34" si="28">M21/M20</f>
+        <f t="shared" ref="M34:N34" si="29">M21/M20</f>
         <v>0.2452964146254881</v>
       </c>
       <c r="N34" s="11">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0.18590490509302762</v>
       </c>
-      <c r="O34" s="4"/>
-      <c r="P34" s="4"/>
-      <c r="Q34" s="4"/>
-      <c r="R34" s="4"/>
+      <c r="O34" s="11">
+        <f t="shared" ref="O34" si="30">O21/O20</f>
+        <v>0.23999598333082292</v>
+      </c>
+      <c r="P34" s="11"/>
+      <c r="Q34" s="11"/>
+      <c r="R34" s="11"/>
       <c r="S34" s="4"/>
       <c r="T34" s="4"/>
       <c r="U34" s="4"/>
       <c r="V34" s="4"/>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="4"/>
+      <c r="X34" s="4"/>
+      <c r="Y34" s="4"/>
+      <c r="Z34" s="4"/>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="4"/>
       <c r="D35" s="4"/>
       <c r="E35" s="4"/>
@@ -2862,8 +3096,12 @@
       <c r="T35" s="4"/>
       <c r="U35" s="4"/>
       <c r="V35" s="4"/>
-    </row>
-    <row r="36" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W35" s="4"/>
+      <c r="X35" s="4"/>
+      <c r="Y35" s="4"/>
+      <c r="Z35" s="4"/>
+    </row>
+    <row r="36" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C36" s="4"/>
       <c r="D36" s="4"/>
       <c r="E36" s="4"/>
@@ -2884,8 +3122,12 @@
       <c r="T36" s="4"/>
       <c r="U36" s="4"/>
       <c r="V36" s="4"/>
-    </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W36" s="4"/>
+      <c r="X36" s="4"/>
+      <c r="Y36" s="4"/>
+      <c r="Z36" s="4"/>
+    </row>
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C37" s="4"/>
       <c r="D37" s="4"/>
       <c r="E37" s="4"/>
@@ -2906,8 +3148,12 @@
       <c r="T37" s="4"/>
       <c r="U37" s="4"/>
       <c r="V37" s="4"/>
-    </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W37" s="4"/>
+      <c r="X37" s="4"/>
+      <c r="Y37" s="4"/>
+      <c r="Z37" s="4"/>
+    </row>
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="4"/>
       <c r="D38" s="4"/>
       <c r="E38" s="4"/>
@@ -2928,8 +3174,12 @@
       <c r="T38" s="4"/>
       <c r="U38" s="4"/>
       <c r="V38" s="4"/>
-    </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W38" s="4"/>
+      <c r="X38" s="4"/>
+      <c r="Y38" s="4"/>
+      <c r="Z38" s="4"/>
+    </row>
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="4"/>
       <c r="D39" s="4"/>
       <c r="E39" s="4"/>
@@ -2950,8 +3200,12 @@
       <c r="T39" s="4"/>
       <c r="U39" s="4"/>
       <c r="V39" s="4"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="4"/>
+      <c r="X39" s="4"/>
+      <c r="Y39" s="4"/>
+      <c r="Z39" s="4"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="4"/>
       <c r="D40" s="4"/>
       <c r="E40" s="4"/>
@@ -2972,8 +3226,12 @@
       <c r="T40" s="4"/>
       <c r="U40" s="4"/>
       <c r="V40" s="4"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="4"/>
+      <c r="X40" s="4"/>
+      <c r="Y40" s="4"/>
+      <c r="Z40" s="4"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="4"/>
       <c r="D41" s="4"/>
       <c r="E41" s="4"/>
@@ -2994,8 +3252,12 @@
       <c r="T41" s="4"/>
       <c r="U41" s="4"/>
       <c r="V41" s="4"/>
-    </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W41" s="4"/>
+      <c r="X41" s="4"/>
+      <c r="Y41" s="4"/>
+      <c r="Z41" s="4"/>
+    </row>
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="4"/>
       <c r="D42" s="4"/>
       <c r="E42" s="4"/>
@@ -3016,8 +3278,12 @@
       <c r="T42" s="4"/>
       <c r="U42" s="4"/>
       <c r="V42" s="4"/>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="4"/>
+      <c r="X42" s="4"/>
+      <c r="Y42" s="4"/>
+      <c r="Z42" s="4"/>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="4"/>
       <c r="D43" s="4"/>
       <c r="E43" s="4"/>
@@ -3038,8 +3304,12 @@
       <c r="T43" s="4"/>
       <c r="U43" s="4"/>
       <c r="V43" s="4"/>
-    </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W43" s="4"/>
+      <c r="X43" s="4"/>
+      <c r="Y43" s="4"/>
+      <c r="Z43" s="4"/>
+    </row>
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="4"/>
       <c r="D44" s="4"/>
       <c r="E44" s="4"/>
@@ -3060,8 +3330,12 @@
       <c r="T44" s="4"/>
       <c r="U44" s="4"/>
       <c r="V44" s="4"/>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W44" s="4"/>
+      <c r="X44" s="4"/>
+      <c r="Y44" s="4"/>
+      <c r="Z44" s="4"/>
+    </row>
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="4"/>
       <c r="D45" s="4"/>
       <c r="E45" s="4"/>
@@ -3082,8 +3356,12 @@
       <c r="T45" s="4"/>
       <c r="U45" s="4"/>
       <c r="V45" s="4"/>
-    </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W45" s="4"/>
+      <c r="X45" s="4"/>
+      <c r="Y45" s="4"/>
+      <c r="Z45" s="4"/>
+    </row>
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="4"/>
       <c r="D46" s="4"/>
       <c r="E46" s="4"/>
@@ -3104,8 +3382,12 @@
       <c r="T46" s="4"/>
       <c r="U46" s="4"/>
       <c r="V46" s="4"/>
-    </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W46" s="4"/>
+      <c r="X46" s="4"/>
+      <c r="Y46" s="4"/>
+      <c r="Z46" s="4"/>
+    </row>
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="4"/>
       <c r="D47" s="4"/>
       <c r="E47" s="4"/>
@@ -3126,8 +3408,12 @@
       <c r="T47" s="4"/>
       <c r="U47" s="4"/>
       <c r="V47" s="4"/>
-    </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W47" s="4"/>
+      <c r="X47" s="4"/>
+      <c r="Y47" s="4"/>
+      <c r="Z47" s="4"/>
+    </row>
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="4"/>
       <c r="D48" s="4"/>
       <c r="E48" s="4"/>
@@ -3148,8 +3434,12 @@
       <c r="T48" s="4"/>
       <c r="U48" s="4"/>
       <c r="V48" s="4"/>
-    </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W48" s="4"/>
+      <c r="X48" s="4"/>
+      <c r="Y48" s="4"/>
+      <c r="Z48" s="4"/>
+    </row>
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="4"/>
       <c r="D49" s="4"/>
       <c r="E49" s="4"/>
@@ -3170,8 +3460,12 @@
       <c r="T49" s="4"/>
       <c r="U49" s="4"/>
       <c r="V49" s="4"/>
-    </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W49" s="4"/>
+      <c r="X49" s="4"/>
+      <c r="Y49" s="4"/>
+      <c r="Z49" s="4"/>
+    </row>
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="4"/>
       <c r="D50" s="4"/>
       <c r="E50" s="4"/>
@@ -3192,8 +3486,12 @@
       <c r="T50" s="4"/>
       <c r="U50" s="4"/>
       <c r="V50" s="4"/>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="4"/>
+      <c r="X50" s="4"/>
+      <c r="Y50" s="4"/>
+      <c r="Z50" s="4"/>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="4"/>
       <c r="D51" s="4"/>
       <c r="E51" s="4"/>
@@ -3214,8 +3512,12 @@
       <c r="T51" s="4"/>
       <c r="U51" s="4"/>
       <c r="V51" s="4"/>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="4"/>
+      <c r="X51" s="4"/>
+      <c r="Y51" s="4"/>
+      <c r="Z51" s="4"/>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="4"/>
       <c r="D52" s="4"/>
       <c r="E52" s="4"/>
@@ -3236,8 +3538,12 @@
       <c r="T52" s="4"/>
       <c r="U52" s="4"/>
       <c r="V52" s="4"/>
-    </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W52" s="4"/>
+      <c r="X52" s="4"/>
+      <c r="Y52" s="4"/>
+      <c r="Z52" s="4"/>
+    </row>
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="4"/>
       <c r="D53" s="4"/>
       <c r="E53" s="4"/>
@@ -3258,8 +3564,12 @@
       <c r="T53" s="4"/>
       <c r="U53" s="4"/>
       <c r="V53" s="4"/>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="4"/>
+      <c r="X53" s="4"/>
+      <c r="Y53" s="4"/>
+      <c r="Z53" s="4"/>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="4"/>
       <c r="D54" s="4"/>
       <c r="E54" s="4"/>
@@ -3280,8 +3590,12 @@
       <c r="T54" s="4"/>
       <c r="U54" s="4"/>
       <c r="V54" s="4"/>
-    </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W54" s="4"/>
+      <c r="X54" s="4"/>
+      <c r="Y54" s="4"/>
+      <c r="Z54" s="4"/>
+    </row>
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="4"/>
       <c r="D55" s="4"/>
       <c r="E55" s="4"/>
@@ -3302,8 +3616,12 @@
       <c r="T55" s="4"/>
       <c r="U55" s="4"/>
       <c r="V55" s="4"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="4"/>
+      <c r="X55" s="4"/>
+      <c r="Y55" s="4"/>
+      <c r="Z55" s="4"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="4"/>
       <c r="D56" s="4"/>
       <c r="E56" s="4"/>
@@ -3324,8 +3642,12 @@
       <c r="T56" s="4"/>
       <c r="U56" s="4"/>
       <c r="V56" s="4"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="4"/>
+      <c r="X56" s="4"/>
+      <c r="Y56" s="4"/>
+      <c r="Z56" s="4"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="4"/>
       <c r="D57" s="4"/>
       <c r="E57" s="4"/>
@@ -3346,8 +3668,12 @@
       <c r="T57" s="4"/>
       <c r="U57" s="4"/>
       <c r="V57" s="4"/>
-    </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W57" s="4"/>
+      <c r="X57" s="4"/>
+      <c r="Y57" s="4"/>
+      <c r="Z57" s="4"/>
+    </row>
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="4"/>
       <c r="D58" s="4"/>
       <c r="E58" s="4"/>
@@ -3368,8 +3694,12 @@
       <c r="T58" s="4"/>
       <c r="U58" s="4"/>
       <c r="V58" s="4"/>
-    </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W58" s="4"/>
+      <c r="X58" s="4"/>
+      <c r="Y58" s="4"/>
+      <c r="Z58" s="4"/>
+    </row>
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="4"/>
       <c r="D59" s="4"/>
       <c r="E59" s="4"/>
@@ -3390,8 +3720,12 @@
       <c r="T59" s="4"/>
       <c r="U59" s="4"/>
       <c r="V59" s="4"/>
-    </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W59" s="4"/>
+      <c r="X59" s="4"/>
+      <c r="Y59" s="4"/>
+      <c r="Z59" s="4"/>
+    </row>
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="4"/>
       <c r="D60" s="4"/>
       <c r="E60" s="4"/>
@@ -3412,8 +3746,12 @@
       <c r="T60" s="4"/>
       <c r="U60" s="4"/>
       <c r="V60" s="4"/>
-    </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W60" s="4"/>
+      <c r="X60" s="4"/>
+      <c r="Y60" s="4"/>
+      <c r="Z60" s="4"/>
+    </row>
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="4"/>
       <c r="D61" s="4"/>
       <c r="E61" s="4"/>
@@ -3434,8 +3772,12 @@
       <c r="T61" s="4"/>
       <c r="U61" s="4"/>
       <c r="V61" s="4"/>
-    </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W61" s="4"/>
+      <c r="X61" s="4"/>
+      <c r="Y61" s="4"/>
+      <c r="Z61" s="4"/>
+    </row>
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="4"/>
       <c r="D62" s="4"/>
       <c r="E62" s="4"/>
@@ -3456,8 +3798,12 @@
       <c r="T62" s="4"/>
       <c r="U62" s="4"/>
       <c r="V62" s="4"/>
-    </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W62" s="4"/>
+      <c r="X62" s="4"/>
+      <c r="Y62" s="4"/>
+      <c r="Z62" s="4"/>
+    </row>
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="4"/>
       <c r="D63" s="4"/>
       <c r="E63" s="4"/>
@@ -3478,8 +3824,12 @@
       <c r="T63" s="4"/>
       <c r="U63" s="4"/>
       <c r="V63" s="4"/>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="4"/>
+      <c r="X63" s="4"/>
+      <c r="Y63" s="4"/>
+      <c r="Z63" s="4"/>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="4"/>
       <c r="D64" s="4"/>
       <c r="E64" s="4"/>
@@ -3500,8 +3850,12 @@
       <c r="T64" s="4"/>
       <c r="U64" s="4"/>
       <c r="V64" s="4"/>
-    </row>
-    <row r="65" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="4"/>
+      <c r="X64" s="4"/>
+      <c r="Y64" s="4"/>
+      <c r="Z64" s="4"/>
+    </row>
+    <row r="65" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C65" s="4"/>
       <c r="D65" s="4"/>
       <c r="E65" s="4"/>
@@ -3522,8 +3876,12 @@
       <c r="T65" s="4"/>
       <c r="U65" s="4"/>
       <c r="V65" s="4"/>
-    </row>
-    <row r="66" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="4"/>
+      <c r="X65" s="4"/>
+      <c r="Y65" s="4"/>
+      <c r="Z65" s="4"/>
+    </row>
+    <row r="66" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C66" s="4"/>
       <c r="D66" s="4"/>
       <c r="E66" s="4"/>
@@ -3544,8 +3902,12 @@
       <c r="T66" s="4"/>
       <c r="U66" s="4"/>
       <c r="V66" s="4"/>
-    </row>
-    <row r="67" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W66" s="4"/>
+      <c r="X66" s="4"/>
+      <c r="Y66" s="4"/>
+      <c r="Z66" s="4"/>
+    </row>
+    <row r="67" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C67" s="4"/>
       <c r="D67" s="4"/>
       <c r="E67" s="4"/>
@@ -3566,8 +3928,12 @@
       <c r="T67" s="4"/>
       <c r="U67" s="4"/>
       <c r="V67" s="4"/>
-    </row>
-    <row r="68" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="4"/>
+      <c r="X67" s="4"/>
+      <c r="Y67" s="4"/>
+      <c r="Z67" s="4"/>
+    </row>
+    <row r="68" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C68" s="4"/>
       <c r="D68" s="4"/>
       <c r="E68" s="4"/>
@@ -3588,8 +3954,12 @@
       <c r="T68" s="4"/>
       <c r="U68" s="4"/>
       <c r="V68" s="4"/>
-    </row>
-    <row r="69" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="4"/>
+      <c r="X68" s="4"/>
+      <c r="Y68" s="4"/>
+      <c r="Z68" s="4"/>
+    </row>
+    <row r="69" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C69" s="4"/>
       <c r="D69" s="4"/>
       <c r="E69" s="4"/>
@@ -3610,8 +3980,12 @@
       <c r="T69" s="4"/>
       <c r="U69" s="4"/>
       <c r="V69" s="4"/>
-    </row>
-    <row r="70" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="4"/>
+      <c r="X69" s="4"/>
+      <c r="Y69" s="4"/>
+      <c r="Z69" s="4"/>
+    </row>
+    <row r="70" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C70" s="4"/>
       <c r="D70" s="4"/>
       <c r="E70" s="4"/>
@@ -3632,8 +4006,12 @@
       <c r="T70" s="4"/>
       <c r="U70" s="4"/>
       <c r="V70" s="4"/>
-    </row>
-    <row r="71" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="4"/>
+      <c r="X70" s="4"/>
+      <c r="Y70" s="4"/>
+      <c r="Z70" s="4"/>
+    </row>
+    <row r="71" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C71" s="4"/>
       <c r="D71" s="4"/>
       <c r="E71" s="4"/>
@@ -3654,8 +4032,12 @@
       <c r="T71" s="4"/>
       <c r="U71" s="4"/>
       <c r="V71" s="4"/>
-    </row>
-    <row r="72" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="4"/>
+      <c r="X71" s="4"/>
+      <c r="Y71" s="4"/>
+      <c r="Z71" s="4"/>
+    </row>
+    <row r="72" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C72" s="4"/>
       <c r="D72" s="4"/>
       <c r="E72" s="4"/>
@@ -3676,8 +4058,12 @@
       <c r="T72" s="4"/>
       <c r="U72" s="4"/>
       <c r="V72" s="4"/>
-    </row>
-    <row r="73" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W72" s="4"/>
+      <c r="X72" s="4"/>
+      <c r="Y72" s="4"/>
+      <c r="Z72" s="4"/>
+    </row>
+    <row r="73" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C73" s="4"/>
       <c r="D73" s="4"/>
       <c r="E73" s="4"/>
@@ -3698,8 +4084,12 @@
       <c r="T73" s="4"/>
       <c r="U73" s="4"/>
       <c r="V73" s="4"/>
-    </row>
-    <row r="74" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="4"/>
+      <c r="X73" s="4"/>
+      <c r="Y73" s="4"/>
+      <c r="Z73" s="4"/>
+    </row>
+    <row r="74" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C74" s="4"/>
       <c r="D74" s="4"/>
       <c r="E74" s="4"/>
@@ -3720,8 +4110,12 @@
       <c r="T74" s="4"/>
       <c r="U74" s="4"/>
       <c r="V74" s="4"/>
-    </row>
-    <row r="75" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="4"/>
+      <c r="X74" s="4"/>
+      <c r="Y74" s="4"/>
+      <c r="Z74" s="4"/>
+    </row>
+    <row r="75" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C75" s="4"/>
       <c r="D75" s="4"/>
       <c r="E75" s="4"/>
@@ -3742,8 +4136,12 @@
       <c r="T75" s="4"/>
       <c r="U75" s="4"/>
       <c r="V75" s="4"/>
-    </row>
-    <row r="76" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="4"/>
+      <c r="X75" s="4"/>
+      <c r="Y75" s="4"/>
+      <c r="Z75" s="4"/>
+    </row>
+    <row r="76" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C76" s="4"/>
       <c r="D76" s="4"/>
       <c r="E76" s="4"/>
@@ -3764,8 +4162,12 @@
       <c r="T76" s="4"/>
       <c r="U76" s="4"/>
       <c r="V76" s="4"/>
-    </row>
-    <row r="77" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W76" s="4"/>
+      <c r="X76" s="4"/>
+      <c r="Y76" s="4"/>
+      <c r="Z76" s="4"/>
+    </row>
+    <row r="77" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C77" s="4"/>
       <c r="D77" s="4"/>
       <c r="E77" s="4"/>
@@ -3786,8 +4188,12 @@
       <c r="T77" s="4"/>
       <c r="U77" s="4"/>
       <c r="V77" s="4"/>
-    </row>
-    <row r="78" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="4"/>
+      <c r="X77" s="4"/>
+      <c r="Y77" s="4"/>
+      <c r="Z77" s="4"/>
+    </row>
+    <row r="78" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C78" s="4"/>
       <c r="D78" s="4"/>
       <c r="E78" s="4"/>
@@ -3808,8 +4214,12 @@
       <c r="T78" s="4"/>
       <c r="U78" s="4"/>
       <c r="V78" s="4"/>
-    </row>
-    <row r="79" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W78" s="4"/>
+      <c r="X78" s="4"/>
+      <c r="Y78" s="4"/>
+      <c r="Z78" s="4"/>
+    </row>
+    <row r="79" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C79" s="4"/>
       <c r="D79" s="4"/>
       <c r="E79" s="4"/>
@@ -3830,8 +4240,12 @@
       <c r="T79" s="4"/>
       <c r="U79" s="4"/>
       <c r="V79" s="4"/>
-    </row>
-    <row r="80" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W79" s="4"/>
+      <c r="X79" s="4"/>
+      <c r="Y79" s="4"/>
+      <c r="Z79" s="4"/>
+    </row>
+    <row r="80" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C80" s="4"/>
       <c r="D80" s="4"/>
       <c r="E80" s="4"/>
@@ -3852,8 +4266,12 @@
       <c r="T80" s="4"/>
       <c r="U80" s="4"/>
       <c r="V80" s="4"/>
-    </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W80" s="4"/>
+      <c r="X80" s="4"/>
+      <c r="Y80" s="4"/>
+      <c r="Z80" s="4"/>
+    </row>
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="4"/>
       <c r="D81" s="4"/>
       <c r="E81" s="4"/>
@@ -3874,8 +4292,12 @@
       <c r="T81" s="4"/>
       <c r="U81" s="4"/>
       <c r="V81" s="4"/>
-    </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W81" s="4"/>
+      <c r="X81" s="4"/>
+      <c r="Y81" s="4"/>
+      <c r="Z81" s="4"/>
+    </row>
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="4"/>
       <c r="D82" s="4"/>
       <c r="E82" s="4"/>
@@ -3896,8 +4318,12 @@
       <c r="T82" s="4"/>
       <c r="U82" s="4"/>
       <c r="V82" s="4"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="4"/>
+      <c r="X82" s="4"/>
+      <c r="Y82" s="4"/>
+      <c r="Z82" s="4"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="4"/>
       <c r="D83" s="4"/>
       <c r="E83" s="4"/>
@@ -3918,8 +4344,12 @@
       <c r="T83" s="4"/>
       <c r="U83" s="4"/>
       <c r="V83" s="4"/>
-    </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W83" s="4"/>
+      <c r="X83" s="4"/>
+      <c r="Y83" s="4"/>
+      <c r="Z83" s="4"/>
+    </row>
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="4"/>
       <c r="D84" s="4"/>
       <c r="E84" s="4"/>
@@ -3940,8 +4370,12 @@
       <c r="T84" s="4"/>
       <c r="U84" s="4"/>
       <c r="V84" s="4"/>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="4"/>
+      <c r="X84" s="4"/>
+      <c r="Y84" s="4"/>
+      <c r="Z84" s="4"/>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="4"/>
       <c r="D85" s="4"/>
       <c r="E85" s="4"/>
@@ -3962,8 +4396,12 @@
       <c r="T85" s="4"/>
       <c r="U85" s="4"/>
       <c r="V85" s="4"/>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="4"/>
+      <c r="X85" s="4"/>
+      <c r="Y85" s="4"/>
+      <c r="Z85" s="4"/>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="4"/>
       <c r="D86" s="4"/>
       <c r="E86" s="4"/>
@@ -3984,8 +4422,12 @@
       <c r="T86" s="4"/>
       <c r="U86" s="4"/>
       <c r="V86" s="4"/>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="4"/>
+      <c r="X86" s="4"/>
+      <c r="Y86" s="4"/>
+      <c r="Z86" s="4"/>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="4"/>
       <c r="D87" s="4"/>
       <c r="E87" s="4"/>
@@ -4006,8 +4448,12 @@
       <c r="T87" s="4"/>
       <c r="U87" s="4"/>
       <c r="V87" s="4"/>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="4"/>
+      <c r="X87" s="4"/>
+      <c r="Y87" s="4"/>
+      <c r="Z87" s="4"/>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="4"/>
       <c r="D88" s="4"/>
       <c r="E88" s="4"/>
@@ -4028,8 +4474,12 @@
       <c r="T88" s="4"/>
       <c r="U88" s="4"/>
       <c r="V88" s="4"/>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="4"/>
+      <c r="X88" s="4"/>
+      <c r="Y88" s="4"/>
+      <c r="Z88" s="4"/>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="4"/>
       <c r="D89" s="4"/>
       <c r="E89" s="4"/>
@@ -4050,8 +4500,12 @@
       <c r="T89" s="4"/>
       <c r="U89" s="4"/>
       <c r="V89" s="4"/>
-    </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W89" s="4"/>
+      <c r="X89" s="4"/>
+      <c r="Y89" s="4"/>
+      <c r="Z89" s="4"/>
+    </row>
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="4"/>
       <c r="D90" s="4"/>
       <c r="E90" s="4"/>
@@ -4072,8 +4526,12 @@
       <c r="T90" s="4"/>
       <c r="U90" s="4"/>
       <c r="V90" s="4"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="4"/>
+      <c r="X90" s="4"/>
+      <c r="Y90" s="4"/>
+      <c r="Z90" s="4"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="4"/>
       <c r="D91" s="4"/>
       <c r="E91" s="4"/>
@@ -4094,8 +4552,12 @@
       <c r="T91" s="4"/>
       <c r="U91" s="4"/>
       <c r="V91" s="4"/>
-    </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W91" s="4"/>
+      <c r="X91" s="4"/>
+      <c r="Y91" s="4"/>
+      <c r="Z91" s="4"/>
+    </row>
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="4"/>
       <c r="D92" s="4"/>
       <c r="E92" s="4"/>
@@ -4116,8 +4578,12 @@
       <c r="T92" s="4"/>
       <c r="U92" s="4"/>
       <c r="V92" s="4"/>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="4"/>
+      <c r="X92" s="4"/>
+      <c r="Y92" s="4"/>
+      <c r="Z92" s="4"/>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="4"/>
       <c r="D93" s="4"/>
       <c r="E93" s="4"/>
@@ -4138,8 +4604,12 @@
       <c r="T93" s="4"/>
       <c r="U93" s="4"/>
       <c r="V93" s="4"/>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="4"/>
+      <c r="X93" s="4"/>
+      <c r="Y93" s="4"/>
+      <c r="Z93" s="4"/>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="4"/>
       <c r="D94" s="4"/>
       <c r="E94" s="4"/>
@@ -4160,8 +4630,12 @@
       <c r="T94" s="4"/>
       <c r="U94" s="4"/>
       <c r="V94" s="4"/>
-    </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W94" s="4"/>
+      <c r="X94" s="4"/>
+      <c r="Y94" s="4"/>
+      <c r="Z94" s="4"/>
+    </row>
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="4"/>
       <c r="D95" s="4"/>
       <c r="E95" s="4"/>
@@ -4182,8 +4656,12 @@
       <c r="T95" s="4"/>
       <c r="U95" s="4"/>
       <c r="V95" s="4"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="4"/>
+      <c r="X95" s="4"/>
+      <c r="Y95" s="4"/>
+      <c r="Z95" s="4"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="4"/>
       <c r="D96" s="4"/>
       <c r="E96" s="4"/>
@@ -4204,8 +4682,12 @@
       <c r="T96" s="4"/>
       <c r="U96" s="4"/>
       <c r="V96" s="4"/>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="4"/>
+      <c r="X96" s="4"/>
+      <c r="Y96" s="4"/>
+      <c r="Z96" s="4"/>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="4"/>
       <c r="D97" s="4"/>
       <c r="E97" s="4"/>
@@ -4226,8 +4708,12 @@
       <c r="T97" s="4"/>
       <c r="U97" s="4"/>
       <c r="V97" s="4"/>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="4"/>
+      <c r="X97" s="4"/>
+      <c r="Y97" s="4"/>
+      <c r="Z97" s="4"/>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="4"/>
       <c r="D98" s="4"/>
       <c r="E98" s="4"/>
@@ -4248,8 +4734,12 @@
       <c r="T98" s="4"/>
       <c r="U98" s="4"/>
       <c r="V98" s="4"/>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="4"/>
+      <c r="X98" s="4"/>
+      <c r="Y98" s="4"/>
+      <c r="Z98" s="4"/>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="4"/>
       <c r="D99" s="4"/>
       <c r="E99" s="4"/>
@@ -4270,8 +4760,12 @@
       <c r="T99" s="4"/>
       <c r="U99" s="4"/>
       <c r="V99" s="4"/>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="4"/>
+      <c r="X99" s="4"/>
+      <c r="Y99" s="4"/>
+      <c r="Z99" s="4"/>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="4"/>
       <c r="D100" s="4"/>
       <c r="E100" s="4"/>
@@ -4292,8 +4786,12 @@
       <c r="T100" s="4"/>
       <c r="U100" s="4"/>
       <c r="V100" s="4"/>
-    </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W100" s="4"/>
+      <c r="X100" s="4"/>
+      <c r="Y100" s="4"/>
+      <c r="Z100" s="4"/>
+    </row>
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="4"/>
       <c r="D101" s="4"/>
       <c r="E101" s="4"/>
@@ -4314,8 +4812,12 @@
       <c r="T101" s="4"/>
       <c r="U101" s="4"/>
       <c r="V101" s="4"/>
-    </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W101" s="4"/>
+      <c r="X101" s="4"/>
+      <c r="Y101" s="4"/>
+      <c r="Z101" s="4"/>
+    </row>
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="4"/>
       <c r="D102" s="4"/>
       <c r="E102" s="4"/>
@@ -4336,8 +4838,12 @@
       <c r="T102" s="4"/>
       <c r="U102" s="4"/>
       <c r="V102" s="4"/>
-    </row>
-    <row r="103" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W102" s="4"/>
+      <c r="X102" s="4"/>
+      <c r="Y102" s="4"/>
+      <c r="Z102" s="4"/>
+    </row>
+    <row r="103" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C103" s="4"/>
       <c r="D103" s="4"/>
       <c r="E103" s="4"/>
@@ -4358,8 +4864,12 @@
       <c r="T103" s="4"/>
       <c r="U103" s="4"/>
       <c r="V103" s="4"/>
-    </row>
-    <row r="104" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W103" s="4"/>
+      <c r="X103" s="4"/>
+      <c r="Y103" s="4"/>
+      <c r="Z103" s="4"/>
+    </row>
+    <row r="104" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C104" s="4"/>
       <c r="D104" s="4"/>
       <c r="E104" s="4"/>
@@ -4380,8 +4890,12 @@
       <c r="T104" s="4"/>
       <c r="U104" s="4"/>
       <c r="V104" s="4"/>
-    </row>
-    <row r="105" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W104" s="4"/>
+      <c r="X104" s="4"/>
+      <c r="Y104" s="4"/>
+      <c r="Z104" s="4"/>
+    </row>
+    <row r="105" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C105" s="4"/>
       <c r="D105" s="4"/>
       <c r="E105" s="4"/>
@@ -4402,8 +4916,12 @@
       <c r="T105" s="4"/>
       <c r="U105" s="4"/>
       <c r="V105" s="4"/>
-    </row>
-    <row r="106" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W105" s="4"/>
+      <c r="X105" s="4"/>
+      <c r="Y105" s="4"/>
+      <c r="Z105" s="4"/>
+    </row>
+    <row r="106" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C106" s="4"/>
       <c r="D106" s="4"/>
       <c r="E106" s="4"/>
@@ -4424,8 +4942,12 @@
       <c r="T106" s="4"/>
       <c r="U106" s="4"/>
       <c r="V106" s="4"/>
-    </row>
-    <row r="107" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W106" s="4"/>
+      <c r="X106" s="4"/>
+      <c r="Y106" s="4"/>
+      <c r="Z106" s="4"/>
+    </row>
+    <row r="107" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C107" s="4"/>
       <c r="D107" s="4"/>
       <c r="E107" s="4"/>
@@ -4446,8 +4968,12 @@
       <c r="T107" s="4"/>
       <c r="U107" s="4"/>
       <c r="V107" s="4"/>
-    </row>
-    <row r="108" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W107" s="4"/>
+      <c r="X107" s="4"/>
+      <c r="Y107" s="4"/>
+      <c r="Z107" s="4"/>
+    </row>
+    <row r="108" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C108" s="4"/>
       <c r="D108" s="4"/>
       <c r="E108" s="4"/>
@@ -4468,8 +4994,12 @@
       <c r="T108" s="4"/>
       <c r="U108" s="4"/>
       <c r="V108" s="4"/>
-    </row>
-    <row r="109" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W108" s="4"/>
+      <c r="X108" s="4"/>
+      <c r="Y108" s="4"/>
+      <c r="Z108" s="4"/>
+    </row>
+    <row r="109" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C109" s="4"/>
       <c r="D109" s="4"/>
       <c r="E109" s="4"/>
@@ -4490,8 +5020,12 @@
       <c r="T109" s="4"/>
       <c r="U109" s="4"/>
       <c r="V109" s="4"/>
-    </row>
-    <row r="110" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W109" s="4"/>
+      <c r="X109" s="4"/>
+      <c r="Y109" s="4"/>
+      <c r="Z109" s="4"/>
+    </row>
+    <row r="110" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C110" s="4"/>
       <c r="D110" s="4"/>
       <c r="E110" s="4"/>
@@ -4512,8 +5046,12 @@
       <c r="T110" s="4"/>
       <c r="U110" s="4"/>
       <c r="V110" s="4"/>
-    </row>
-    <row r="111" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W110" s="4"/>
+      <c r="X110" s="4"/>
+      <c r="Y110" s="4"/>
+      <c r="Z110" s="4"/>
+    </row>
+    <row r="111" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C111" s="4"/>
       <c r="D111" s="4"/>
       <c r="E111" s="4"/>
@@ -4534,8 +5072,12 @@
       <c r="T111" s="4"/>
       <c r="U111" s="4"/>
       <c r="V111" s="4"/>
-    </row>
-    <row r="112" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W111" s="4"/>
+      <c r="X111" s="4"/>
+      <c r="Y111" s="4"/>
+      <c r="Z111" s="4"/>
+    </row>
+    <row r="112" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C112" s="4"/>
       <c r="D112" s="4"/>
       <c r="E112" s="4"/>
@@ -4556,8 +5098,12 @@
       <c r="T112" s="4"/>
       <c r="U112" s="4"/>
       <c r="V112" s="4"/>
-    </row>
-    <row r="113" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W112" s="4"/>
+      <c r="X112" s="4"/>
+      <c r="Y112" s="4"/>
+      <c r="Z112" s="4"/>
+    </row>
+    <row r="113" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C113" s="4"/>
       <c r="D113" s="4"/>
       <c r="E113" s="4"/>
@@ -4578,8 +5124,12 @@
       <c r="T113" s="4"/>
       <c r="U113" s="4"/>
       <c r="V113" s="4"/>
-    </row>
-    <row r="114" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W113" s="4"/>
+      <c r="X113" s="4"/>
+      <c r="Y113" s="4"/>
+      <c r="Z113" s="4"/>
+    </row>
+    <row r="114" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C114" s="4"/>
       <c r="D114" s="4"/>
       <c r="E114" s="4"/>
@@ -4600,8 +5150,12 @@
       <c r="T114" s="4"/>
       <c r="U114" s="4"/>
       <c r="V114" s="4"/>
-    </row>
-    <row r="115" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W114" s="4"/>
+      <c r="X114" s="4"/>
+      <c r="Y114" s="4"/>
+      <c r="Z114" s="4"/>
+    </row>
+    <row r="115" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C115" s="4"/>
       <c r="D115" s="4"/>
       <c r="E115" s="4"/>
@@ -4622,8 +5176,12 @@
       <c r="T115" s="4"/>
       <c r="U115" s="4"/>
       <c r="V115" s="4"/>
-    </row>
-    <row r="116" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W115" s="4"/>
+      <c r="X115" s="4"/>
+      <c r="Y115" s="4"/>
+      <c r="Z115" s="4"/>
+    </row>
+    <row r="116" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C116" s="4"/>
       <c r="D116" s="4"/>
       <c r="E116" s="4"/>
@@ -4644,8 +5202,12 @@
       <c r="T116" s="4"/>
       <c r="U116" s="4"/>
       <c r="V116" s="4"/>
-    </row>
-    <row r="117" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W116" s="4"/>
+      <c r="X116" s="4"/>
+      <c r="Y116" s="4"/>
+      <c r="Z116" s="4"/>
+    </row>
+    <row r="117" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C117" s="4"/>
       <c r="D117" s="4"/>
       <c r="E117" s="4"/>
@@ -4666,8 +5228,12 @@
       <c r="T117" s="4"/>
       <c r="U117" s="4"/>
       <c r="V117" s="4"/>
-    </row>
-    <row r="118" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W117" s="4"/>
+      <c r="X117" s="4"/>
+      <c r="Y117" s="4"/>
+      <c r="Z117" s="4"/>
+    </row>
+    <row r="118" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C118" s="4"/>
       <c r="D118" s="4"/>
       <c r="E118" s="4"/>
@@ -4688,8 +5254,12 @@
       <c r="T118" s="4"/>
       <c r="U118" s="4"/>
       <c r="V118" s="4"/>
-    </row>
-    <row r="119" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W118" s="4"/>
+      <c r="X118" s="4"/>
+      <c r="Y118" s="4"/>
+      <c r="Z118" s="4"/>
+    </row>
+    <row r="119" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C119" s="4"/>
       <c r="D119" s="4"/>
       <c r="E119" s="4"/>
@@ -4710,8 +5280,12 @@
       <c r="T119" s="4"/>
       <c r="U119" s="4"/>
       <c r="V119" s="4"/>
-    </row>
-    <row r="120" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W119" s="4"/>
+      <c r="X119" s="4"/>
+      <c r="Y119" s="4"/>
+      <c r="Z119" s="4"/>
+    </row>
+    <row r="120" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C120" s="4"/>
       <c r="D120" s="4"/>
       <c r="E120" s="4"/>
@@ -4732,8 +5306,12 @@
       <c r="T120" s="4"/>
       <c r="U120" s="4"/>
       <c r="V120" s="4"/>
-    </row>
-    <row r="121" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W120" s="4"/>
+      <c r="X120" s="4"/>
+      <c r="Y120" s="4"/>
+      <c r="Z120" s="4"/>
+    </row>
+    <row r="121" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C121" s="4"/>
       <c r="D121" s="4"/>
       <c r="E121" s="4"/>
@@ -4754,8 +5332,12 @@
       <c r="T121" s="4"/>
       <c r="U121" s="4"/>
       <c r="V121" s="4"/>
-    </row>
-    <row r="122" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W121" s="4"/>
+      <c r="X121" s="4"/>
+      <c r="Y121" s="4"/>
+      <c r="Z121" s="4"/>
+    </row>
+    <row r="122" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C122" s="4"/>
       <c r="D122" s="4"/>
       <c r="E122" s="4"/>
@@ -4776,8 +5358,12 @@
       <c r="T122" s="4"/>
       <c r="U122" s="4"/>
       <c r="V122" s="4"/>
-    </row>
-    <row r="123" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W122" s="4"/>
+      <c r="X122" s="4"/>
+      <c r="Y122" s="4"/>
+      <c r="Z122" s="4"/>
+    </row>
+    <row r="123" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C123" s="4"/>
       <c r="D123" s="4"/>
       <c r="E123" s="4"/>
@@ -4798,8 +5384,12 @@
       <c r="T123" s="4"/>
       <c r="U123" s="4"/>
       <c r="V123" s="4"/>
-    </row>
-    <row r="124" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W123" s="4"/>
+      <c r="X123" s="4"/>
+      <c r="Y123" s="4"/>
+      <c r="Z123" s="4"/>
+    </row>
+    <row r="124" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C124" s="4"/>
       <c r="D124" s="4"/>
       <c r="E124" s="4"/>
@@ -4820,8 +5410,12 @@
       <c r="T124" s="4"/>
       <c r="U124" s="4"/>
       <c r="V124" s="4"/>
-    </row>
-    <row r="125" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W124" s="4"/>
+      <c r="X124" s="4"/>
+      <c r="Y124" s="4"/>
+      <c r="Z124" s="4"/>
+    </row>
+    <row r="125" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C125" s="4"/>
       <c r="D125" s="4"/>
       <c r="E125" s="4"/>
@@ -4842,8 +5436,12 @@
       <c r="T125" s="4"/>
       <c r="U125" s="4"/>
       <c r="V125" s="4"/>
-    </row>
-    <row r="126" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W125" s="4"/>
+      <c r="X125" s="4"/>
+      <c r="Y125" s="4"/>
+      <c r="Z125" s="4"/>
+    </row>
+    <row r="126" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C126" s="4"/>
       <c r="D126" s="4"/>
       <c r="E126" s="4"/>
@@ -4864,8 +5462,12 @@
       <c r="T126" s="4"/>
       <c r="U126" s="4"/>
       <c r="V126" s="4"/>
-    </row>
-    <row r="127" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W126" s="4"/>
+      <c r="X126" s="4"/>
+      <c r="Y126" s="4"/>
+      <c r="Z126" s="4"/>
+    </row>
+    <row r="127" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C127" s="4"/>
       <c r="D127" s="4"/>
       <c r="E127" s="4"/>
@@ -4886,8 +5488,12 @@
       <c r="T127" s="4"/>
       <c r="U127" s="4"/>
       <c r="V127" s="4"/>
-    </row>
-    <row r="128" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W127" s="4"/>
+      <c r="X127" s="4"/>
+      <c r="Y127" s="4"/>
+      <c r="Z127" s="4"/>
+    </row>
+    <row r="128" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C128" s="4"/>
       <c r="D128" s="4"/>
       <c r="E128" s="4"/>
@@ -4908,8 +5514,12 @@
       <c r="T128" s="4"/>
       <c r="U128" s="4"/>
       <c r="V128" s="4"/>
-    </row>
-    <row r="129" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W128" s="4"/>
+      <c r="X128" s="4"/>
+      <c r="Y128" s="4"/>
+      <c r="Z128" s="4"/>
+    </row>
+    <row r="129" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C129" s="4"/>
       <c r="D129" s="4"/>
       <c r="E129" s="4"/>
@@ -4930,8 +5540,12 @@
       <c r="T129" s="4"/>
       <c r="U129" s="4"/>
       <c r="V129" s="4"/>
-    </row>
-    <row r="130" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W129" s="4"/>
+      <c r="X129" s="4"/>
+      <c r="Y129" s="4"/>
+      <c r="Z129" s="4"/>
+    </row>
+    <row r="130" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C130" s="4"/>
       <c r="D130" s="4"/>
       <c r="E130" s="4"/>
@@ -4952,8 +5566,12 @@
       <c r="T130" s="4"/>
       <c r="U130" s="4"/>
       <c r="V130" s="4"/>
-    </row>
-    <row r="131" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W130" s="4"/>
+      <c r="X130" s="4"/>
+      <c r="Y130" s="4"/>
+      <c r="Z130" s="4"/>
+    </row>
+    <row r="131" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C131" s="4"/>
       <c r="D131" s="4"/>
       <c r="E131" s="4"/>
@@ -4974,8 +5592,12 @@
       <c r="T131" s="4"/>
       <c r="U131" s="4"/>
       <c r="V131" s="4"/>
-    </row>
-    <row r="132" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W131" s="4"/>
+      <c r="X131" s="4"/>
+      <c r="Y131" s="4"/>
+      <c r="Z131" s="4"/>
+    </row>
+    <row r="132" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C132" s="4"/>
       <c r="D132" s="4"/>
       <c r="E132" s="4"/>
@@ -4996,8 +5618,12 @@
       <c r="T132" s="4"/>
       <c r="U132" s="4"/>
       <c r="V132" s="4"/>
-    </row>
-    <row r="133" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W132" s="4"/>
+      <c r="X132" s="4"/>
+      <c r="Y132" s="4"/>
+      <c r="Z132" s="4"/>
+    </row>
+    <row r="133" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C133" s="4"/>
       <c r="D133" s="4"/>
       <c r="E133" s="4"/>
@@ -5018,8 +5644,12 @@
       <c r="T133" s="4"/>
       <c r="U133" s="4"/>
       <c r="V133" s="4"/>
-    </row>
-    <row r="134" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W133" s="4"/>
+      <c r="X133" s="4"/>
+      <c r="Y133" s="4"/>
+      <c r="Z133" s="4"/>
+    </row>
+    <row r="134" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C134" s="4"/>
       <c r="D134" s="4"/>
       <c r="E134" s="4"/>
@@ -5040,8 +5670,12 @@
       <c r="T134" s="4"/>
       <c r="U134" s="4"/>
       <c r="V134" s="4"/>
-    </row>
-    <row r="135" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W134" s="4"/>
+      <c r="X134" s="4"/>
+      <c r="Y134" s="4"/>
+      <c r="Z134" s="4"/>
+    </row>
+    <row r="135" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C135" s="4"/>
       <c r="D135" s="4"/>
       <c r="E135" s="4"/>
@@ -5062,8 +5696,12 @@
       <c r="T135" s="4"/>
       <c r="U135" s="4"/>
       <c r="V135" s="4"/>
-    </row>
-    <row r="136" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W135" s="4"/>
+      <c r="X135" s="4"/>
+      <c r="Y135" s="4"/>
+      <c r="Z135" s="4"/>
+    </row>
+    <row r="136" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C136" s="4"/>
       <c r="D136" s="4"/>
       <c r="E136" s="4"/>
@@ -5084,8 +5722,12 @@
       <c r="T136" s="4"/>
       <c r="U136" s="4"/>
       <c r="V136" s="4"/>
-    </row>
-    <row r="137" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W136" s="4"/>
+      <c r="X136" s="4"/>
+      <c r="Y136" s="4"/>
+      <c r="Z136" s="4"/>
+    </row>
+    <row r="137" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C137" s="4"/>
       <c r="D137" s="4"/>
       <c r="E137" s="4"/>
@@ -5106,8 +5748,12 @@
       <c r="T137" s="4"/>
       <c r="U137" s="4"/>
       <c r="V137" s="4"/>
-    </row>
-    <row r="138" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W137" s="4"/>
+      <c r="X137" s="4"/>
+      <c r="Y137" s="4"/>
+      <c r="Z137" s="4"/>
+    </row>
+    <row r="138" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C138" s="4"/>
       <c r="D138" s="4"/>
       <c r="E138" s="4"/>
@@ -5128,8 +5774,12 @@
       <c r="T138" s="4"/>
       <c r="U138" s="4"/>
       <c r="V138" s="4"/>
-    </row>
-    <row r="139" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W138" s="4"/>
+      <c r="X138" s="4"/>
+      <c r="Y138" s="4"/>
+      <c r="Z138" s="4"/>
+    </row>
+    <row r="139" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C139" s="4"/>
       <c r="D139" s="4"/>
       <c r="E139" s="4"/>
@@ -5150,8 +5800,12 @@
       <c r="T139" s="4"/>
       <c r="U139" s="4"/>
       <c r="V139" s="4"/>
-    </row>
-    <row r="140" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W139" s="4"/>
+      <c r="X139" s="4"/>
+      <c r="Y139" s="4"/>
+      <c r="Z139" s="4"/>
+    </row>
+    <row r="140" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C140" s="4"/>
       <c r="D140" s="4"/>
       <c r="E140" s="4"/>
@@ -5172,8 +5826,12 @@
       <c r="T140" s="4"/>
       <c r="U140" s="4"/>
       <c r="V140" s="4"/>
-    </row>
-    <row r="141" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W140" s="4"/>
+      <c r="X140" s="4"/>
+      <c r="Y140" s="4"/>
+      <c r="Z140" s="4"/>
+    </row>
+    <row r="141" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C141" s="4"/>
       <c r="D141" s="4"/>
       <c r="E141" s="4"/>
@@ -5194,8 +5852,12 @@
       <c r="T141" s="4"/>
       <c r="U141" s="4"/>
       <c r="V141" s="4"/>
-    </row>
-    <row r="142" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W141" s="4"/>
+      <c r="X141" s="4"/>
+      <c r="Y141" s="4"/>
+      <c r="Z141" s="4"/>
+    </row>
+    <row r="142" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C142" s="4"/>
       <c r="D142" s="4"/>
       <c r="E142" s="4"/>
@@ -5216,8 +5878,12 @@
       <c r="T142" s="4"/>
       <c r="U142" s="4"/>
       <c r="V142" s="4"/>
-    </row>
-    <row r="143" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W142" s="4"/>
+      <c r="X142" s="4"/>
+      <c r="Y142" s="4"/>
+      <c r="Z142" s="4"/>
+    </row>
+    <row r="143" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C143" s="4"/>
       <c r="D143" s="4"/>
       <c r="E143" s="4"/>
@@ -5238,8 +5904,12 @@
       <c r="T143" s="4"/>
       <c r="U143" s="4"/>
       <c r="V143" s="4"/>
-    </row>
-    <row r="144" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W143" s="4"/>
+      <c r="X143" s="4"/>
+      <c r="Y143" s="4"/>
+      <c r="Z143" s="4"/>
+    </row>
+    <row r="144" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C144" s="4"/>
       <c r="D144" s="4"/>
       <c r="E144" s="4"/>
@@ -5260,8 +5930,12 @@
       <c r="T144" s="4"/>
       <c r="U144" s="4"/>
       <c r="V144" s="4"/>
-    </row>
-    <row r="145" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W144" s="4"/>
+      <c r="X144" s="4"/>
+      <c r="Y144" s="4"/>
+      <c r="Z144" s="4"/>
+    </row>
+    <row r="145" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C145" s="4"/>
       <c r="D145" s="4"/>
       <c r="E145" s="4"/>
@@ -5282,8 +5956,12 @@
       <c r="T145" s="4"/>
       <c r="U145" s="4"/>
       <c r="V145" s="4"/>
-    </row>
-    <row r="146" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W145" s="4"/>
+      <c r="X145" s="4"/>
+      <c r="Y145" s="4"/>
+      <c r="Z145" s="4"/>
+    </row>
+    <row r="146" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C146" s="4"/>
       <c r="D146" s="4"/>
       <c r="E146" s="4"/>
@@ -5304,8 +5982,12 @@
       <c r="T146" s="4"/>
       <c r="U146" s="4"/>
       <c r="V146" s="4"/>
-    </row>
-    <row r="147" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W146" s="4"/>
+      <c r="X146" s="4"/>
+      <c r="Y146" s="4"/>
+      <c r="Z146" s="4"/>
+    </row>
+    <row r="147" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C147" s="4"/>
       <c r="D147" s="4"/>
       <c r="E147" s="4"/>
@@ -5326,8 +6008,12 @@
       <c r="T147" s="4"/>
       <c r="U147" s="4"/>
       <c r="V147" s="4"/>
-    </row>
-    <row r="148" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W147" s="4"/>
+      <c r="X147" s="4"/>
+      <c r="Y147" s="4"/>
+      <c r="Z147" s="4"/>
+    </row>
+    <row r="148" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C148" s="4"/>
       <c r="D148" s="4"/>
       <c r="E148" s="4"/>
@@ -5348,8 +6034,12 @@
       <c r="T148" s="4"/>
       <c r="U148" s="4"/>
       <c r="V148" s="4"/>
-    </row>
-    <row r="149" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W148" s="4"/>
+      <c r="X148" s="4"/>
+      <c r="Y148" s="4"/>
+      <c r="Z148" s="4"/>
+    </row>
+    <row r="149" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C149" s="4"/>
       <c r="D149" s="4"/>
       <c r="E149" s="4"/>
@@ -5370,8 +6060,12 @@
       <c r="T149" s="4"/>
       <c r="U149" s="4"/>
       <c r="V149" s="4"/>
-    </row>
-    <row r="150" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W149" s="4"/>
+      <c r="X149" s="4"/>
+      <c r="Y149" s="4"/>
+      <c r="Z149" s="4"/>
+    </row>
+    <row r="150" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C150" s="4"/>
       <c r="D150" s="4"/>
       <c r="E150" s="4"/>
@@ -5392,8 +6086,12 @@
       <c r="T150" s="4"/>
       <c r="U150" s="4"/>
       <c r="V150" s="4"/>
-    </row>
-    <row r="151" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W150" s="4"/>
+      <c r="X150" s="4"/>
+      <c r="Y150" s="4"/>
+      <c r="Z150" s="4"/>
+    </row>
+    <row r="151" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C151" s="4"/>
       <c r="D151" s="4"/>
       <c r="E151" s="4"/>
@@ -5414,8 +6112,12 @@
       <c r="T151" s="4"/>
       <c r="U151" s="4"/>
       <c r="V151" s="4"/>
-    </row>
-    <row r="152" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W151" s="4"/>
+      <c r="X151" s="4"/>
+      <c r="Y151" s="4"/>
+      <c r="Z151" s="4"/>
+    </row>
+    <row r="152" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C152" s="4"/>
       <c r="D152" s="4"/>
       <c r="E152" s="4"/>
@@ -5436,8 +6138,12 @@
       <c r="T152" s="4"/>
       <c r="U152" s="4"/>
       <c r="V152" s="4"/>
-    </row>
-    <row r="153" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W152" s="4"/>
+      <c r="X152" s="4"/>
+      <c r="Y152" s="4"/>
+      <c r="Z152" s="4"/>
+    </row>
+    <row r="153" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C153" s="4"/>
       <c r="D153" s="4"/>
       <c r="E153" s="4"/>
@@ -5458,8 +6164,12 @@
       <c r="T153" s="4"/>
       <c r="U153" s="4"/>
       <c r="V153" s="4"/>
-    </row>
-    <row r="154" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W153" s="4"/>
+      <c r="X153" s="4"/>
+      <c r="Y153" s="4"/>
+      <c r="Z153" s="4"/>
+    </row>
+    <row r="154" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C154" s="4"/>
       <c r="D154" s="4"/>
       <c r="E154" s="4"/>
@@ -5480,8 +6190,12 @@
       <c r="T154" s="4"/>
       <c r="U154" s="4"/>
       <c r="V154" s="4"/>
-    </row>
-    <row r="155" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W154" s="4"/>
+      <c r="X154" s="4"/>
+      <c r="Y154" s="4"/>
+      <c r="Z154" s="4"/>
+    </row>
+    <row r="155" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C155" s="4"/>
       <c r="D155" s="4"/>
       <c r="E155" s="4"/>
@@ -5502,8 +6216,12 @@
       <c r="T155" s="4"/>
       <c r="U155" s="4"/>
       <c r="V155" s="4"/>
-    </row>
-    <row r="156" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W155" s="4"/>
+      <c r="X155" s="4"/>
+      <c r="Y155" s="4"/>
+      <c r="Z155" s="4"/>
+    </row>
+    <row r="156" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C156" s="4"/>
       <c r="D156" s="4"/>
       <c r="E156" s="4"/>
@@ -5524,8 +6242,12 @@
       <c r="T156" s="4"/>
       <c r="U156" s="4"/>
       <c r="V156" s="4"/>
-    </row>
-    <row r="157" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W156" s="4"/>
+      <c r="X156" s="4"/>
+      <c r="Y156" s="4"/>
+      <c r="Z156" s="4"/>
+    </row>
+    <row r="157" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C157" s="4"/>
       <c r="D157" s="4"/>
       <c r="E157" s="4"/>
@@ -5546,8 +6268,12 @@
       <c r="T157" s="4"/>
       <c r="U157" s="4"/>
       <c r="V157" s="4"/>
-    </row>
-    <row r="158" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W157" s="4"/>
+      <c r="X157" s="4"/>
+      <c r="Y157" s="4"/>
+      <c r="Z157" s="4"/>
+    </row>
+    <row r="158" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C158" s="4"/>
       <c r="D158" s="4"/>
       <c r="E158" s="4"/>
@@ -5568,8 +6294,12 @@
       <c r="T158" s="4"/>
       <c r="U158" s="4"/>
       <c r="V158" s="4"/>
-    </row>
-    <row r="159" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W158" s="4"/>
+      <c r="X158" s="4"/>
+      <c r="Y158" s="4"/>
+      <c r="Z158" s="4"/>
+    </row>
+    <row r="159" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C159" s="4"/>
       <c r="D159" s="4"/>
       <c r="E159" s="4"/>
@@ -5590,8 +6320,12 @@
       <c r="T159" s="4"/>
       <c r="U159" s="4"/>
       <c r="V159" s="4"/>
-    </row>
-    <row r="160" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W159" s="4"/>
+      <c r="X159" s="4"/>
+      <c r="Y159" s="4"/>
+      <c r="Z159" s="4"/>
+    </row>
+    <row r="160" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C160" s="4"/>
       <c r="D160" s="4"/>
       <c r="E160" s="4"/>
@@ -5612,8 +6346,12 @@
       <c r="T160" s="4"/>
       <c r="U160" s="4"/>
       <c r="V160" s="4"/>
-    </row>
-    <row r="161" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W160" s="4"/>
+      <c r="X160" s="4"/>
+      <c r="Y160" s="4"/>
+      <c r="Z160" s="4"/>
+    </row>
+    <row r="161" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C161" s="4"/>
       <c r="D161" s="4"/>
       <c r="E161" s="4"/>
@@ -5634,8 +6372,12 @@
       <c r="T161" s="4"/>
       <c r="U161" s="4"/>
       <c r="V161" s="4"/>
-    </row>
-    <row r="162" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W161" s="4"/>
+      <c r="X161" s="4"/>
+      <c r="Y161" s="4"/>
+      <c r="Z161" s="4"/>
+    </row>
+    <row r="162" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C162" s="4"/>
       <c r="D162" s="4"/>
       <c r="E162" s="4"/>
@@ -5656,8 +6398,12 @@
       <c r="T162" s="4"/>
       <c r="U162" s="4"/>
       <c r="V162" s="4"/>
-    </row>
-    <row r="163" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W162" s="4"/>
+      <c r="X162" s="4"/>
+      <c r="Y162" s="4"/>
+      <c r="Z162" s="4"/>
+    </row>
+    <row r="163" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C163" s="4"/>
       <c r="D163" s="4"/>
       <c r="E163" s="4"/>
@@ -5678,8 +6424,12 @@
       <c r="T163" s="4"/>
       <c r="U163" s="4"/>
       <c r="V163" s="4"/>
-    </row>
-    <row r="164" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W163" s="4"/>
+      <c r="X163" s="4"/>
+      <c r="Y163" s="4"/>
+      <c r="Z163" s="4"/>
+    </row>
+    <row r="164" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C164" s="4"/>
       <c r="D164" s="4"/>
       <c r="E164" s="4"/>
@@ -5700,8 +6450,12 @@
       <c r="T164" s="4"/>
       <c r="U164" s="4"/>
       <c r="V164" s="4"/>
-    </row>
-    <row r="165" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W164" s="4"/>
+      <c r="X164" s="4"/>
+      <c r="Y164" s="4"/>
+      <c r="Z164" s="4"/>
+    </row>
+    <row r="165" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C165" s="4"/>
       <c r="D165" s="4"/>
       <c r="E165" s="4"/>
@@ -5722,8 +6476,12 @@
       <c r="T165" s="4"/>
       <c r="U165" s="4"/>
       <c r="V165" s="4"/>
-    </row>
-    <row r="166" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W165" s="4"/>
+      <c r="X165" s="4"/>
+      <c r="Y165" s="4"/>
+      <c r="Z165" s="4"/>
+    </row>
+    <row r="166" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C166" s="4"/>
       <c r="D166" s="4"/>
       <c r="E166" s="4"/>
@@ -5744,8 +6502,12 @@
       <c r="T166" s="4"/>
       <c r="U166" s="4"/>
       <c r="V166" s="4"/>
-    </row>
-    <row r="167" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W166" s="4"/>
+      <c r="X166" s="4"/>
+      <c r="Y166" s="4"/>
+      <c r="Z166" s="4"/>
+    </row>
+    <row r="167" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C167" s="4"/>
       <c r="D167" s="4"/>
       <c r="E167" s="4"/>
@@ -5766,8 +6528,12 @@
       <c r="T167" s="4"/>
       <c r="U167" s="4"/>
       <c r="V167" s="4"/>
-    </row>
-    <row r="168" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W167" s="4"/>
+      <c r="X167" s="4"/>
+      <c r="Y167" s="4"/>
+      <c r="Z167" s="4"/>
+    </row>
+    <row r="168" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C168" s="4"/>
       <c r="D168" s="4"/>
       <c r="E168" s="4"/>
@@ -5788,8 +6554,12 @@
       <c r="T168" s="4"/>
       <c r="U168" s="4"/>
       <c r="V168" s="4"/>
-    </row>
-    <row r="169" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W168" s="4"/>
+      <c r="X168" s="4"/>
+      <c r="Y168" s="4"/>
+      <c r="Z168" s="4"/>
+    </row>
+    <row r="169" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C169" s="4"/>
       <c r="D169" s="4"/>
       <c r="E169" s="4"/>
@@ -5810,8 +6580,12 @@
       <c r="T169" s="4"/>
       <c r="U169" s="4"/>
       <c r="V169" s="4"/>
-    </row>
-    <row r="170" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W169" s="4"/>
+      <c r="X169" s="4"/>
+      <c r="Y169" s="4"/>
+      <c r="Z169" s="4"/>
+    </row>
+    <row r="170" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C170" s="4"/>
       <c r="D170" s="4"/>
       <c r="E170" s="4"/>
@@ -5832,8 +6606,12 @@
       <c r="T170" s="4"/>
       <c r="U170" s="4"/>
       <c r="V170" s="4"/>
-    </row>
-    <row r="171" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W170" s="4"/>
+      <c r="X170" s="4"/>
+      <c r="Y170" s="4"/>
+      <c r="Z170" s="4"/>
+    </row>
+    <row r="171" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C171" s="4"/>
       <c r="D171" s="4"/>
       <c r="E171" s="4"/>
@@ -5854,8 +6632,12 @@
       <c r="T171" s="4"/>
       <c r="U171" s="4"/>
       <c r="V171" s="4"/>
-    </row>
-    <row r="172" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W171" s="4"/>
+      <c r="X171" s="4"/>
+      <c r="Y171" s="4"/>
+      <c r="Z171" s="4"/>
+    </row>
+    <row r="172" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C172" s="4"/>
       <c r="D172" s="4"/>
       <c r="E172" s="4"/>
@@ -5876,8 +6658,12 @@
       <c r="T172" s="4"/>
       <c r="U172" s="4"/>
       <c r="V172" s="4"/>
-    </row>
-    <row r="173" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W172" s="4"/>
+      <c r="X172" s="4"/>
+      <c r="Y172" s="4"/>
+      <c r="Z172" s="4"/>
+    </row>
+    <row r="173" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C173" s="4"/>
       <c r="D173" s="4"/>
       <c r="E173" s="4"/>
@@ -5898,8 +6684,12 @@
       <c r="T173" s="4"/>
       <c r="U173" s="4"/>
       <c r="V173" s="4"/>
-    </row>
-    <row r="174" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W173" s="4"/>
+      <c r="X173" s="4"/>
+      <c r="Y173" s="4"/>
+      <c r="Z173" s="4"/>
+    </row>
+    <row r="174" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C174" s="4"/>
       <c r="D174" s="4"/>
       <c r="E174" s="4"/>
@@ -5920,8 +6710,12 @@
       <c r="T174" s="4"/>
       <c r="U174" s="4"/>
       <c r="V174" s="4"/>
-    </row>
-    <row r="175" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W174" s="4"/>
+      <c r="X174" s="4"/>
+      <c r="Y174" s="4"/>
+      <c r="Z174" s="4"/>
+    </row>
+    <row r="175" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C175" s="4"/>
       <c r="D175" s="4"/>
       <c r="E175" s="4"/>
@@ -5942,8 +6736,12 @@
       <c r="T175" s="4"/>
       <c r="U175" s="4"/>
       <c r="V175" s="4"/>
-    </row>
-    <row r="176" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W175" s="4"/>
+      <c r="X175" s="4"/>
+      <c r="Y175" s="4"/>
+      <c r="Z175" s="4"/>
+    </row>
+    <row r="176" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C176" s="4"/>
       <c r="D176" s="4"/>
       <c r="E176" s="4"/>
@@ -5964,8 +6762,12 @@
       <c r="T176" s="4"/>
       <c r="U176" s="4"/>
       <c r="V176" s="4"/>
-    </row>
-    <row r="177" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W176" s="4"/>
+      <c r="X176" s="4"/>
+      <c r="Y176" s="4"/>
+      <c r="Z176" s="4"/>
+    </row>
+    <row r="177" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C177" s="4"/>
       <c r="D177" s="4"/>
       <c r="E177" s="4"/>
@@ -5986,8 +6788,12 @@
       <c r="T177" s="4"/>
       <c r="U177" s="4"/>
       <c r="V177" s="4"/>
-    </row>
-    <row r="178" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W177" s="4"/>
+      <c r="X177" s="4"/>
+      <c r="Y177" s="4"/>
+      <c r="Z177" s="4"/>
+    </row>
+    <row r="178" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C178" s="4"/>
       <c r="D178" s="4"/>
       <c r="E178" s="4"/>
@@ -6008,8 +6814,12 @@
       <c r="T178" s="4"/>
       <c r="U178" s="4"/>
       <c r="V178" s="4"/>
-    </row>
-    <row r="179" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W178" s="4"/>
+      <c r="X178" s="4"/>
+      <c r="Y178" s="4"/>
+      <c r="Z178" s="4"/>
+    </row>
+    <row r="179" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C179" s="4"/>
       <c r="D179" s="4"/>
       <c r="E179" s="4"/>
@@ -6030,8 +6840,12 @@
       <c r="T179" s="4"/>
       <c r="U179" s="4"/>
       <c r="V179" s="4"/>
-    </row>
-    <row r="180" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W179" s="4"/>
+      <c r="X179" s="4"/>
+      <c r="Y179" s="4"/>
+      <c r="Z179" s="4"/>
+    </row>
+    <row r="180" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C180" s="4"/>
       <c r="D180" s="4"/>
       <c r="E180" s="4"/>
@@ -6052,8 +6866,12 @@
       <c r="T180" s="4"/>
       <c r="U180" s="4"/>
       <c r="V180" s="4"/>
-    </row>
-    <row r="181" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W180" s="4"/>
+      <c r="X180" s="4"/>
+      <c r="Y180" s="4"/>
+      <c r="Z180" s="4"/>
+    </row>
+    <row r="181" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C181" s="4"/>
       <c r="D181" s="4"/>
       <c r="E181" s="4"/>
@@ -6074,8 +6892,12 @@
       <c r="T181" s="4"/>
       <c r="U181" s="4"/>
       <c r="V181" s="4"/>
-    </row>
-    <row r="182" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W181" s="4"/>
+      <c r="X181" s="4"/>
+      <c r="Y181" s="4"/>
+      <c r="Z181" s="4"/>
+    </row>
+    <row r="182" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C182" s="4"/>
       <c r="D182" s="4"/>
       <c r="E182" s="4"/>
@@ -6096,8 +6918,12 @@
       <c r="T182" s="4"/>
       <c r="U182" s="4"/>
       <c r="V182" s="4"/>
-    </row>
-    <row r="183" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W182" s="4"/>
+      <c r="X182" s="4"/>
+      <c r="Y182" s="4"/>
+      <c r="Z182" s="4"/>
+    </row>
+    <row r="183" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C183" s="4"/>
       <c r="D183" s="4"/>
       <c r="E183" s="4"/>
@@ -6118,8 +6944,12 @@
       <c r="T183" s="4"/>
       <c r="U183" s="4"/>
       <c r="V183" s="4"/>
-    </row>
-    <row r="184" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W183" s="4"/>
+      <c r="X183" s="4"/>
+      <c r="Y183" s="4"/>
+      <c r="Z183" s="4"/>
+    </row>
+    <row r="184" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C184" s="4"/>
       <c r="D184" s="4"/>
       <c r="E184" s="4"/>
@@ -6140,8 +6970,12 @@
       <c r="T184" s="4"/>
       <c r="U184" s="4"/>
       <c r="V184" s="4"/>
-    </row>
-    <row r="185" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W184" s="4"/>
+      <c r="X184" s="4"/>
+      <c r="Y184" s="4"/>
+      <c r="Z184" s="4"/>
+    </row>
+    <row r="185" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C185" s="4"/>
       <c r="D185" s="4"/>
       <c r="E185" s="4"/>
@@ -6162,8 +6996,12 @@
       <c r="T185" s="4"/>
       <c r="U185" s="4"/>
       <c r="V185" s="4"/>
-    </row>
-    <row r="186" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W185" s="4"/>
+      <c r="X185" s="4"/>
+      <c r="Y185" s="4"/>
+      <c r="Z185" s="4"/>
+    </row>
+    <row r="186" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C186" s="4"/>
       <c r="D186" s="4"/>
       <c r="E186" s="4"/>
@@ -6184,8 +7022,12 @@
       <c r="T186" s="4"/>
       <c r="U186" s="4"/>
       <c r="V186" s="4"/>
-    </row>
-    <row r="187" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W186" s="4"/>
+      <c r="X186" s="4"/>
+      <c r="Y186" s="4"/>
+      <c r="Z186" s="4"/>
+    </row>
+    <row r="187" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C187" s="4"/>
       <c r="D187" s="4"/>
       <c r="E187" s="4"/>
@@ -6206,8 +7048,12 @@
       <c r="T187" s="4"/>
       <c r="U187" s="4"/>
       <c r="V187" s="4"/>
-    </row>
-    <row r="188" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W187" s="4"/>
+      <c r="X187" s="4"/>
+      <c r="Y187" s="4"/>
+      <c r="Z187" s="4"/>
+    </row>
+    <row r="188" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C188" s="4"/>
       <c r="D188" s="4"/>
       <c r="E188" s="4"/>
@@ -6228,8 +7074,12 @@
       <c r="T188" s="4"/>
       <c r="U188" s="4"/>
       <c r="V188" s="4"/>
-    </row>
-    <row r="189" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W188" s="4"/>
+      <c r="X188" s="4"/>
+      <c r="Y188" s="4"/>
+      <c r="Z188" s="4"/>
+    </row>
+    <row r="189" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C189" s="4"/>
       <c r="D189" s="4"/>
       <c r="E189" s="4"/>
@@ -6250,8 +7100,12 @@
       <c r="T189" s="4"/>
       <c r="U189" s="4"/>
       <c r="V189" s="4"/>
-    </row>
-    <row r="190" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W189" s="4"/>
+      <c r="X189" s="4"/>
+      <c r="Y189" s="4"/>
+      <c r="Z189" s="4"/>
+    </row>
+    <row r="190" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C190" s="4"/>
       <c r="D190" s="4"/>
       <c r="E190" s="4"/>
@@ -6272,8 +7126,12 @@
       <c r="T190" s="4"/>
       <c r="U190" s="4"/>
       <c r="V190" s="4"/>
-    </row>
-    <row r="191" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W190" s="4"/>
+      <c r="X190" s="4"/>
+      <c r="Y190" s="4"/>
+      <c r="Z190" s="4"/>
+    </row>
+    <row r="191" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C191" s="4"/>
       <c r="D191" s="4"/>
       <c r="E191" s="4"/>
@@ -6294,8 +7152,12 @@
       <c r="T191" s="4"/>
       <c r="U191" s="4"/>
       <c r="V191" s="4"/>
-    </row>
-    <row r="192" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W191" s="4"/>
+      <c r="X191" s="4"/>
+      <c r="Y191" s="4"/>
+      <c r="Z191" s="4"/>
+    </row>
+    <row r="192" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C192" s="4"/>
       <c r="D192" s="4"/>
       <c r="E192" s="4"/>
@@ -6316,8 +7178,12 @@
       <c r="T192" s="4"/>
       <c r="U192" s="4"/>
       <c r="V192" s="4"/>
-    </row>
-    <row r="193" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W192" s="4"/>
+      <c r="X192" s="4"/>
+      <c r="Y192" s="4"/>
+      <c r="Z192" s="4"/>
+    </row>
+    <row r="193" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C193" s="4"/>
       <c r="D193" s="4"/>
       <c r="E193" s="4"/>
@@ -6338,8 +7204,12 @@
       <c r="T193" s="4"/>
       <c r="U193" s="4"/>
       <c r="V193" s="4"/>
-    </row>
-    <row r="194" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W193" s="4"/>
+      <c r="X193" s="4"/>
+      <c r="Y193" s="4"/>
+      <c r="Z193" s="4"/>
+    </row>
+    <row r="194" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C194" s="4"/>
       <c r="D194" s="4"/>
       <c r="E194" s="4"/>
@@ -6360,8 +7230,12 @@
       <c r="T194" s="4"/>
       <c r="U194" s="4"/>
       <c r="V194" s="4"/>
-    </row>
-    <row r="195" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W194" s="4"/>
+      <c r="X194" s="4"/>
+      <c r="Y194" s="4"/>
+      <c r="Z194" s="4"/>
+    </row>
+    <row r="195" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C195" s="4"/>
       <c r="D195" s="4"/>
       <c r="E195" s="4"/>
@@ -6382,8 +7256,12 @@
       <c r="T195" s="4"/>
       <c r="U195" s="4"/>
       <c r="V195" s="4"/>
-    </row>
-    <row r="196" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W195" s="4"/>
+      <c r="X195" s="4"/>
+      <c r="Y195" s="4"/>
+      <c r="Z195" s="4"/>
+    </row>
+    <row r="196" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C196" s="4"/>
       <c r="D196" s="4"/>
       <c r="E196" s="4"/>
@@ -6404,8 +7282,12 @@
       <c r="T196" s="4"/>
       <c r="U196" s="4"/>
       <c r="V196" s="4"/>
-    </row>
-    <row r="197" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W196" s="4"/>
+      <c r="X196" s="4"/>
+      <c r="Y196" s="4"/>
+      <c r="Z196" s="4"/>
+    </row>
+    <row r="197" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C197" s="4"/>
       <c r="D197" s="4"/>
       <c r="E197" s="4"/>
@@ -6426,8 +7308,12 @@
       <c r="T197" s="4"/>
       <c r="U197" s="4"/>
       <c r="V197" s="4"/>
-    </row>
-    <row r="198" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W197" s="4"/>
+      <c r="X197" s="4"/>
+      <c r="Y197" s="4"/>
+      <c r="Z197" s="4"/>
+    </row>
+    <row r="198" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C198" s="4"/>
       <c r="D198" s="4"/>
       <c r="E198" s="4"/>
@@ -6448,8 +7334,12 @@
       <c r="T198" s="4"/>
       <c r="U198" s="4"/>
       <c r="V198" s="4"/>
-    </row>
-    <row r="199" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W198" s="4"/>
+      <c r="X198" s="4"/>
+      <c r="Y198" s="4"/>
+      <c r="Z198" s="4"/>
+    </row>
+    <row r="199" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C199" s="4"/>
       <c r="D199" s="4"/>
       <c r="E199" s="4"/>
@@ -6470,8 +7360,12 @@
       <c r="T199" s="4"/>
       <c r="U199" s="4"/>
       <c r="V199" s="4"/>
-    </row>
-    <row r="200" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W199" s="4"/>
+      <c r="X199" s="4"/>
+      <c r="Y199" s="4"/>
+      <c r="Z199" s="4"/>
+    </row>
+    <row r="200" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C200" s="4"/>
       <c r="D200" s="4"/>
       <c r="E200" s="4"/>
@@ -6492,8 +7386,12 @@
       <c r="T200" s="4"/>
       <c r="U200" s="4"/>
       <c r="V200" s="4"/>
-    </row>
-    <row r="201" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W200" s="4"/>
+      <c r="X200" s="4"/>
+      <c r="Y200" s="4"/>
+      <c r="Z200" s="4"/>
+    </row>
+    <row r="201" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C201" s="4"/>
       <c r="D201" s="4"/>
       <c r="E201" s="4"/>
@@ -6514,8 +7412,12 @@
       <c r="T201" s="4"/>
       <c r="U201" s="4"/>
       <c r="V201" s="4"/>
-    </row>
-    <row r="202" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W201" s="4"/>
+      <c r="X201" s="4"/>
+      <c r="Y201" s="4"/>
+      <c r="Z201" s="4"/>
+    </row>
+    <row r="202" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C202" s="4"/>
       <c r="D202" s="4"/>
       <c r="E202" s="4"/>
@@ -6536,8 +7438,12 @@
       <c r="T202" s="4"/>
       <c r="U202" s="4"/>
       <c r="V202" s="4"/>
-    </row>
-    <row r="203" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W202" s="4"/>
+      <c r="X202" s="4"/>
+      <c r="Y202" s="4"/>
+      <c r="Z202" s="4"/>
+    </row>
+    <row r="203" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C203" s="4"/>
       <c r="D203" s="4"/>
       <c r="E203" s="4"/>
@@ -6558,8 +7464,12 @@
       <c r="T203" s="4"/>
       <c r="U203" s="4"/>
       <c r="V203" s="4"/>
-    </row>
-    <row r="204" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W203" s="4"/>
+      <c r="X203" s="4"/>
+      <c r="Y203" s="4"/>
+      <c r="Z203" s="4"/>
+    </row>
+    <row r="204" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C204" s="4"/>
       <c r="D204" s="4"/>
       <c r="E204" s="4"/>
@@ -6580,8 +7490,12 @@
       <c r="T204" s="4"/>
       <c r="U204" s="4"/>
       <c r="V204" s="4"/>
-    </row>
-    <row r="205" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W204" s="4"/>
+      <c r="X204" s="4"/>
+      <c r="Y204" s="4"/>
+      <c r="Z204" s="4"/>
+    </row>
+    <row r="205" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C205" s="4"/>
       <c r="D205" s="4"/>
       <c r="E205" s="4"/>
@@ -6602,8 +7516,12 @@
       <c r="T205" s="4"/>
       <c r="U205" s="4"/>
       <c r="V205" s="4"/>
-    </row>
-    <row r="206" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W205" s="4"/>
+      <c r="X205" s="4"/>
+      <c r="Y205" s="4"/>
+      <c r="Z205" s="4"/>
+    </row>
+    <row r="206" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C206" s="4"/>
       <c r="D206" s="4"/>
       <c r="E206" s="4"/>
@@ -6624,8 +7542,12 @@
       <c r="T206" s="4"/>
       <c r="U206" s="4"/>
       <c r="V206" s="4"/>
-    </row>
-    <row r="207" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W206" s="4"/>
+      <c r="X206" s="4"/>
+      <c r="Y206" s="4"/>
+      <c r="Z206" s="4"/>
+    </row>
+    <row r="207" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C207" s="4"/>
       <c r="D207" s="4"/>
       <c r="E207" s="4"/>
@@ -6646,8 +7568,12 @@
       <c r="T207" s="4"/>
       <c r="U207" s="4"/>
       <c r="V207" s="4"/>
-    </row>
-    <row r="208" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W207" s="4"/>
+      <c r="X207" s="4"/>
+      <c r="Y207" s="4"/>
+      <c r="Z207" s="4"/>
+    </row>
+    <row r="208" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C208" s="4"/>
       <c r="D208" s="4"/>
       <c r="E208" s="4"/>
@@ -6668,8 +7594,12 @@
       <c r="T208" s="4"/>
       <c r="U208" s="4"/>
       <c r="V208" s="4"/>
-    </row>
-    <row r="209" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W208" s="4"/>
+      <c r="X208" s="4"/>
+      <c r="Y208" s="4"/>
+      <c r="Z208" s="4"/>
+    </row>
+    <row r="209" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C209" s="4"/>
       <c r="D209" s="4"/>
       <c r="E209" s="4"/>
@@ -6690,8 +7620,12 @@
       <c r="T209" s="4"/>
       <c r="U209" s="4"/>
       <c r="V209" s="4"/>
-    </row>
-    <row r="210" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W209" s="4"/>
+      <c r="X209" s="4"/>
+      <c r="Y209" s="4"/>
+      <c r="Z209" s="4"/>
+    </row>
+    <row r="210" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C210" s="4"/>
       <c r="D210" s="4"/>
       <c r="E210" s="4"/>
@@ -6712,8 +7646,12 @@
       <c r="T210" s="4"/>
       <c r="U210" s="4"/>
       <c r="V210" s="4"/>
-    </row>
-    <row r="211" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W210" s="4"/>
+      <c r="X210" s="4"/>
+      <c r="Y210" s="4"/>
+      <c r="Z210" s="4"/>
+    </row>
+    <row r="211" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C211" s="4"/>
       <c r="D211" s="4"/>
       <c r="E211" s="4"/>
@@ -6734,8 +7672,12 @@
       <c r="T211" s="4"/>
       <c r="U211" s="4"/>
       <c r="V211" s="4"/>
-    </row>
-    <row r="212" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W211" s="4"/>
+      <c r="X211" s="4"/>
+      <c r="Y211" s="4"/>
+      <c r="Z211" s="4"/>
+    </row>
+    <row r="212" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C212" s="4"/>
       <c r="D212" s="4"/>
       <c r="E212" s="4"/>
@@ -6756,8 +7698,12 @@
       <c r="T212" s="4"/>
       <c r="U212" s="4"/>
       <c r="V212" s="4"/>
-    </row>
-    <row r="213" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W212" s="4"/>
+      <c r="X212" s="4"/>
+      <c r="Y212" s="4"/>
+      <c r="Z212" s="4"/>
+    </row>
+    <row r="213" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C213" s="4"/>
       <c r="D213" s="4"/>
       <c r="E213" s="4"/>
@@ -6778,8 +7724,12 @@
       <c r="T213" s="4"/>
       <c r="U213" s="4"/>
       <c r="V213" s="4"/>
-    </row>
-    <row r="214" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W213" s="4"/>
+      <c r="X213" s="4"/>
+      <c r="Y213" s="4"/>
+      <c r="Z213" s="4"/>
+    </row>
+    <row r="214" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C214" s="4"/>
       <c r="D214" s="4"/>
       <c r="E214" s="4"/>
@@ -6800,8 +7750,12 @@
       <c r="T214" s="4"/>
       <c r="U214" s="4"/>
       <c r="V214" s="4"/>
-    </row>
-    <row r="215" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W214" s="4"/>
+      <c r="X214" s="4"/>
+      <c r="Y214" s="4"/>
+      <c r="Z214" s="4"/>
+    </row>
+    <row r="215" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C215" s="4"/>
       <c r="D215" s="4"/>
       <c r="E215" s="4"/>
@@ -6822,8 +7776,12 @@
       <c r="T215" s="4"/>
       <c r="U215" s="4"/>
       <c r="V215" s="4"/>
-    </row>
-    <row r="216" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W215" s="4"/>
+      <c r="X215" s="4"/>
+      <c r="Y215" s="4"/>
+      <c r="Z215" s="4"/>
+    </row>
+    <row r="216" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C216" s="4"/>
       <c r="D216" s="4"/>
       <c r="E216" s="4"/>
@@ -6844,8 +7802,12 @@
       <c r="T216" s="4"/>
       <c r="U216" s="4"/>
       <c r="V216" s="4"/>
-    </row>
-    <row r="217" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W216" s="4"/>
+      <c r="X216" s="4"/>
+      <c r="Y216" s="4"/>
+      <c r="Z216" s="4"/>
+    </row>
+    <row r="217" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C217" s="4"/>
       <c r="D217" s="4"/>
       <c r="E217" s="4"/>
@@ -6866,8 +7828,12 @@
       <c r="T217" s="4"/>
       <c r="U217" s="4"/>
       <c r="V217" s="4"/>
-    </row>
-    <row r="218" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W217" s="4"/>
+      <c r="X217" s="4"/>
+      <c r="Y217" s="4"/>
+      <c r="Z217" s="4"/>
+    </row>
+    <row r="218" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C218" s="4"/>
       <c r="D218" s="4"/>
       <c r="E218" s="4"/>
@@ -6888,8 +7854,12 @@
       <c r="T218" s="4"/>
       <c r="U218" s="4"/>
       <c r="V218" s="4"/>
-    </row>
-    <row r="219" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W218" s="4"/>
+      <c r="X218" s="4"/>
+      <c r="Y218" s="4"/>
+      <c r="Z218" s="4"/>
+    </row>
+    <row r="219" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C219" s="4"/>
       <c r="D219" s="4"/>
       <c r="E219" s="4"/>
@@ -6910,8 +7880,12 @@
       <c r="T219" s="4"/>
       <c r="U219" s="4"/>
       <c r="V219" s="4"/>
-    </row>
-    <row r="220" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W219" s="4"/>
+      <c r="X219" s="4"/>
+      <c r="Y219" s="4"/>
+      <c r="Z219" s="4"/>
+    </row>
+    <row r="220" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C220" s="4"/>
       <c r="D220" s="4"/>
       <c r="E220" s="4"/>
@@ -6932,8 +7906,12 @@
       <c r="T220" s="4"/>
       <c r="U220" s="4"/>
       <c r="V220" s="4"/>
-    </row>
-    <row r="221" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W220" s="4"/>
+      <c r="X220" s="4"/>
+      <c r="Y220" s="4"/>
+      <c r="Z220" s="4"/>
+    </row>
+    <row r="221" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C221" s="4"/>
       <c r="D221" s="4"/>
       <c r="E221" s="4"/>
@@ -6954,8 +7932,12 @@
       <c r="T221" s="4"/>
       <c r="U221" s="4"/>
       <c r="V221" s="4"/>
-    </row>
-    <row r="222" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W221" s="4"/>
+      <c r="X221" s="4"/>
+      <c r="Y221" s="4"/>
+      <c r="Z221" s="4"/>
+    </row>
+    <row r="222" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C222" s="4"/>
       <c r="D222" s="4"/>
       <c r="E222" s="4"/>
@@ -6976,8 +7958,12 @@
       <c r="T222" s="4"/>
       <c r="U222" s="4"/>
       <c r="V222" s="4"/>
-    </row>
-    <row r="223" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W222" s="4"/>
+      <c r="X222" s="4"/>
+      <c r="Y222" s="4"/>
+      <c r="Z222" s="4"/>
+    </row>
+    <row r="223" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C223" s="4"/>
       <c r="D223" s="4"/>
       <c r="E223" s="4"/>
@@ -6998,8 +7984,12 @@
       <c r="T223" s="4"/>
       <c r="U223" s="4"/>
       <c r="V223" s="4"/>
-    </row>
-    <row r="224" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W223" s="4"/>
+      <c r="X223" s="4"/>
+      <c r="Y223" s="4"/>
+      <c r="Z223" s="4"/>
+    </row>
+    <row r="224" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C224" s="4"/>
       <c r="D224" s="4"/>
       <c r="E224" s="4"/>
@@ -7020,8 +8010,12 @@
       <c r="T224" s="4"/>
       <c r="U224" s="4"/>
       <c r="V224" s="4"/>
-    </row>
-    <row r="225" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W224" s="4"/>
+      <c r="X224" s="4"/>
+      <c r="Y224" s="4"/>
+      <c r="Z224" s="4"/>
+    </row>
+    <row r="225" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C225" s="4"/>
       <c r="D225" s="4"/>
       <c r="E225" s="4"/>
@@ -7042,8 +8036,12 @@
       <c r="T225" s="4"/>
       <c r="U225" s="4"/>
       <c r="V225" s="4"/>
-    </row>
-    <row r="226" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W225" s="4"/>
+      <c r="X225" s="4"/>
+      <c r="Y225" s="4"/>
+      <c r="Z225" s="4"/>
+    </row>
+    <row r="226" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C226" s="4"/>
       <c r="D226" s="4"/>
       <c r="E226" s="4"/>
@@ -7064,8 +8062,12 @@
       <c r="T226" s="4"/>
       <c r="U226" s="4"/>
       <c r="V226" s="4"/>
-    </row>
-    <row r="227" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W226" s="4"/>
+      <c r="X226" s="4"/>
+      <c r="Y226" s="4"/>
+      <c r="Z226" s="4"/>
+    </row>
+    <row r="227" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C227" s="4"/>
       <c r="D227" s="4"/>
       <c r="E227" s="4"/>
@@ -7086,8 +8088,12 @@
       <c r="T227" s="4"/>
       <c r="U227" s="4"/>
       <c r="V227" s="4"/>
-    </row>
-    <row r="228" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W227" s="4"/>
+      <c r="X227" s="4"/>
+      <c r="Y227" s="4"/>
+      <c r="Z227" s="4"/>
+    </row>
+    <row r="228" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C228" s="4"/>
       <c r="D228" s="4"/>
       <c r="E228" s="4"/>
@@ -7108,8 +8114,12 @@
       <c r="T228" s="4"/>
       <c r="U228" s="4"/>
       <c r="V228" s="4"/>
-    </row>
-    <row r="229" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W228" s="4"/>
+      <c r="X228" s="4"/>
+      <c r="Y228" s="4"/>
+      <c r="Z228" s="4"/>
+    </row>
+    <row r="229" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C229" s="4"/>
       <c r="D229" s="4"/>
       <c r="E229" s="4"/>
@@ -7130,8 +8140,12 @@
       <c r="T229" s="4"/>
       <c r="U229" s="4"/>
       <c r="V229" s="4"/>
-    </row>
-    <row r="230" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W229" s="4"/>
+      <c r="X229" s="4"/>
+      <c r="Y229" s="4"/>
+      <c r="Z229" s="4"/>
+    </row>
+    <row r="230" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C230" s="4"/>
       <c r="D230" s="4"/>
       <c r="E230" s="4"/>
@@ -7152,8 +8166,12 @@
       <c r="T230" s="4"/>
       <c r="U230" s="4"/>
       <c r="V230" s="4"/>
-    </row>
-    <row r="231" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W230" s="4"/>
+      <c r="X230" s="4"/>
+      <c r="Y230" s="4"/>
+      <c r="Z230" s="4"/>
+    </row>
+    <row r="231" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C231" s="4"/>
       <c r="D231" s="4"/>
       <c r="E231" s="4"/>
@@ -7174,8 +8192,12 @@
       <c r="T231" s="4"/>
       <c r="U231" s="4"/>
       <c r="V231" s="4"/>
-    </row>
-    <row r="232" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W231" s="4"/>
+      <c r="X231" s="4"/>
+      <c r="Y231" s="4"/>
+      <c r="Z231" s="4"/>
+    </row>
+    <row r="232" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C232" s="4"/>
       <c r="D232" s="4"/>
       <c r="E232" s="4"/>
@@ -7196,8 +8218,12 @@
       <c r="T232" s="4"/>
       <c r="U232" s="4"/>
       <c r="V232" s="4"/>
-    </row>
-    <row r="233" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W232" s="4"/>
+      <c r="X232" s="4"/>
+      <c r="Y232" s="4"/>
+      <c r="Z232" s="4"/>
+    </row>
+    <row r="233" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C233" s="4"/>
       <c r="D233" s="4"/>
       <c r="E233" s="4"/>
@@ -7218,8 +8244,12 @@
       <c r="T233" s="4"/>
       <c r="U233" s="4"/>
       <c r="V233" s="4"/>
-    </row>
-    <row r="234" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W233" s="4"/>
+      <c r="X233" s="4"/>
+      <c r="Y233" s="4"/>
+      <c r="Z233" s="4"/>
+    </row>
+    <row r="234" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C234" s="4"/>
       <c r="D234" s="4"/>
       <c r="E234" s="4"/>
@@ -7240,8 +8270,12 @@
       <c r="T234" s="4"/>
       <c r="U234" s="4"/>
       <c r="V234" s="4"/>
-    </row>
-    <row r="235" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W234" s="4"/>
+      <c r="X234" s="4"/>
+      <c r="Y234" s="4"/>
+      <c r="Z234" s="4"/>
+    </row>
+    <row r="235" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C235" s="4"/>
       <c r="D235" s="4"/>
       <c r="E235" s="4"/>
@@ -7262,8 +8296,12 @@
       <c r="T235" s="4"/>
       <c r="U235" s="4"/>
       <c r="V235" s="4"/>
-    </row>
-    <row r="236" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W235" s="4"/>
+      <c r="X235" s="4"/>
+      <c r="Y235" s="4"/>
+      <c r="Z235" s="4"/>
+    </row>
+    <row r="236" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C236" s="4"/>
       <c r="D236" s="4"/>
       <c r="E236" s="4"/>
@@ -7284,8 +8322,12 @@
       <c r="T236" s="4"/>
       <c r="U236" s="4"/>
       <c r="V236" s="4"/>
-    </row>
-    <row r="237" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W236" s="4"/>
+      <c r="X236" s="4"/>
+      <c r="Y236" s="4"/>
+      <c r="Z236" s="4"/>
+    </row>
+    <row r="237" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C237" s="4"/>
       <c r="D237" s="4"/>
       <c r="E237" s="4"/>
@@ -7306,8 +8348,12 @@
       <c r="T237" s="4"/>
       <c r="U237" s="4"/>
       <c r="V237" s="4"/>
-    </row>
-    <row r="238" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W237" s="4"/>
+      <c r="X237" s="4"/>
+      <c r="Y237" s="4"/>
+      <c r="Z237" s="4"/>
+    </row>
+    <row r="238" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C238" s="4"/>
       <c r="D238" s="4"/>
       <c r="E238" s="4"/>
@@ -7328,8 +8374,12 @@
       <c r="T238" s="4"/>
       <c r="U238" s="4"/>
       <c r="V238" s="4"/>
-    </row>
-    <row r="239" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W238" s="4"/>
+      <c r="X238" s="4"/>
+      <c r="Y238" s="4"/>
+      <c r="Z238" s="4"/>
+    </row>
+    <row r="239" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C239" s="4"/>
       <c r="D239" s="4"/>
       <c r="E239" s="4"/>
@@ -7350,8 +8400,12 @@
       <c r="T239" s="4"/>
       <c r="U239" s="4"/>
       <c r="V239" s="4"/>
-    </row>
-    <row r="240" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W239" s="4"/>
+      <c r="X239" s="4"/>
+      <c r="Y239" s="4"/>
+      <c r="Z239" s="4"/>
+    </row>
+    <row r="240" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C240" s="4"/>
       <c r="D240" s="4"/>
       <c r="E240" s="4"/>
@@ -7372,8 +8426,12 @@
       <c r="T240" s="4"/>
       <c r="U240" s="4"/>
       <c r="V240" s="4"/>
-    </row>
-    <row r="241" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W240" s="4"/>
+      <c r="X240" s="4"/>
+      <c r="Y240" s="4"/>
+      <c r="Z240" s="4"/>
+    </row>
+    <row r="241" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C241" s="4"/>
       <c r="D241" s="4"/>
       <c r="E241" s="4"/>
@@ -7394,8 +8452,12 @@
       <c r="T241" s="4"/>
       <c r="U241" s="4"/>
       <c r="V241" s="4"/>
-    </row>
-    <row r="242" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W241" s="4"/>
+      <c r="X241" s="4"/>
+      <c r="Y241" s="4"/>
+      <c r="Z241" s="4"/>
+    </row>
+    <row r="242" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C242" s="4"/>
       <c r="D242" s="4"/>
       <c r="E242" s="4"/>
@@ -7416,8 +8478,12 @@
       <c r="T242" s="4"/>
       <c r="U242" s="4"/>
       <c r="V242" s="4"/>
-    </row>
-    <row r="243" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W242" s="4"/>
+      <c r="X242" s="4"/>
+      <c r="Y242" s="4"/>
+      <c r="Z242" s="4"/>
+    </row>
+    <row r="243" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C243" s="4"/>
       <c r="D243" s="4"/>
       <c r="E243" s="4"/>
@@ -7438,8 +8504,12 @@
       <c r="T243" s="4"/>
       <c r="U243" s="4"/>
       <c r="V243" s="4"/>
-    </row>
-    <row r="244" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W243" s="4"/>
+      <c r="X243" s="4"/>
+      <c r="Y243" s="4"/>
+      <c r="Z243" s="4"/>
+    </row>
+    <row r="244" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C244" s="4"/>
       <c r="D244" s="4"/>
       <c r="E244" s="4"/>
@@ -7460,8 +8530,12 @@
       <c r="T244" s="4"/>
       <c r="U244" s="4"/>
       <c r="V244" s="4"/>
-    </row>
-    <row r="245" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W244" s="4"/>
+      <c r="X244" s="4"/>
+      <c r="Y244" s="4"/>
+      <c r="Z244" s="4"/>
+    </row>
+    <row r="245" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C245" s="4"/>
       <c r="D245" s="4"/>
       <c r="E245" s="4"/>
@@ -7482,8 +8556,12 @@
       <c r="T245" s="4"/>
       <c r="U245" s="4"/>
       <c r="V245" s="4"/>
-    </row>
-    <row r="246" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W245" s="4"/>
+      <c r="X245" s="4"/>
+      <c r="Y245" s="4"/>
+      <c r="Z245" s="4"/>
+    </row>
+    <row r="246" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C246" s="4"/>
       <c r="D246" s="4"/>
       <c r="E246" s="4"/>
@@ -7504,8 +8582,12 @@
       <c r="T246" s="4"/>
       <c r="U246" s="4"/>
       <c r="V246" s="4"/>
-    </row>
-    <row r="247" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W246" s="4"/>
+      <c r="X246" s="4"/>
+      <c r="Y246" s="4"/>
+      <c r="Z246" s="4"/>
+    </row>
+    <row r="247" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C247" s="4"/>
       <c r="D247" s="4"/>
       <c r="E247" s="4"/>
@@ -7526,8 +8608,12 @@
       <c r="T247" s="4"/>
       <c r="U247" s="4"/>
       <c r="V247" s="4"/>
-    </row>
-    <row r="248" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W247" s="4"/>
+      <c r="X247" s="4"/>
+      <c r="Y247" s="4"/>
+      <c r="Z247" s="4"/>
+    </row>
+    <row r="248" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C248" s="4"/>
       <c r="D248" s="4"/>
       <c r="E248" s="4"/>
@@ -7548,8 +8634,12 @@
       <c r="T248" s="4"/>
       <c r="U248" s="4"/>
       <c r="V248" s="4"/>
-    </row>
-    <row r="249" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W248" s="4"/>
+      <c r="X248" s="4"/>
+      <c r="Y248" s="4"/>
+      <c r="Z248" s="4"/>
+    </row>
+    <row r="249" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C249" s="4"/>
       <c r="D249" s="4"/>
       <c r="E249" s="4"/>
@@ -7570,8 +8660,12 @@
       <c r="T249" s="4"/>
       <c r="U249" s="4"/>
       <c r="V249" s="4"/>
-    </row>
-    <row r="250" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W249" s="4"/>
+      <c r="X249" s="4"/>
+      <c r="Y249" s="4"/>
+      <c r="Z249" s="4"/>
+    </row>
+    <row r="250" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C250" s="4"/>
       <c r="D250" s="4"/>
       <c r="E250" s="4"/>
@@ -7592,8 +8686,12 @@
       <c r="T250" s="4"/>
       <c r="U250" s="4"/>
       <c r="V250" s="4"/>
-    </row>
-    <row r="251" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W250" s="4"/>
+      <c r="X250" s="4"/>
+      <c r="Y250" s="4"/>
+      <c r="Z250" s="4"/>
+    </row>
+    <row r="251" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C251" s="4"/>
       <c r="D251" s="4"/>
       <c r="E251" s="4"/>
@@ -7614,8 +8712,12 @@
       <c r="T251" s="4"/>
       <c r="U251" s="4"/>
       <c r="V251" s="4"/>
-    </row>
-    <row r="252" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W251" s="4"/>
+      <c r="X251" s="4"/>
+      <c r="Y251" s="4"/>
+      <c r="Z251" s="4"/>
+    </row>
+    <row r="252" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C252" s="4"/>
       <c r="D252" s="4"/>
       <c r="E252" s="4"/>
@@ -7636,8 +8738,12 @@
       <c r="T252" s="4"/>
       <c r="U252" s="4"/>
       <c r="V252" s="4"/>
-    </row>
-    <row r="253" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W252" s="4"/>
+      <c r="X252" s="4"/>
+      <c r="Y252" s="4"/>
+      <c r="Z252" s="4"/>
+    </row>
+    <row r="253" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C253" s="4"/>
       <c r="D253" s="4"/>
       <c r="E253" s="4"/>
@@ -7658,8 +8764,12 @@
       <c r="T253" s="4"/>
       <c r="U253" s="4"/>
       <c r="V253" s="4"/>
-    </row>
-    <row r="254" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W253" s="4"/>
+      <c r="X253" s="4"/>
+      <c r="Y253" s="4"/>
+      <c r="Z253" s="4"/>
+    </row>
+    <row r="254" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C254" s="4"/>
       <c r="D254" s="4"/>
       <c r="E254" s="4"/>
@@ -7680,8 +8790,12 @@
       <c r="T254" s="4"/>
       <c r="U254" s="4"/>
       <c r="V254" s="4"/>
-    </row>
-    <row r="255" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W254" s="4"/>
+      <c r="X254" s="4"/>
+      <c r="Y254" s="4"/>
+      <c r="Z254" s="4"/>
+    </row>
+    <row r="255" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C255" s="4"/>
       <c r="D255" s="4"/>
       <c r="E255" s="4"/>
@@ -7702,8 +8816,12 @@
       <c r="T255" s="4"/>
       <c r="U255" s="4"/>
       <c r="V255" s="4"/>
-    </row>
-    <row r="256" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W255" s="4"/>
+      <c r="X255" s="4"/>
+      <c r="Y255" s="4"/>
+      <c r="Z255" s="4"/>
+    </row>
+    <row r="256" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C256" s="4"/>
       <c r="D256" s="4"/>
       <c r="E256" s="4"/>
@@ -7724,8 +8842,12 @@
       <c r="T256" s="4"/>
       <c r="U256" s="4"/>
       <c r="V256" s="4"/>
-    </row>
-    <row r="257" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W256" s="4"/>
+      <c r="X256" s="4"/>
+      <c r="Y256" s="4"/>
+      <c r="Z256" s="4"/>
+    </row>
+    <row r="257" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C257" s="4"/>
       <c r="D257" s="4"/>
       <c r="E257" s="4"/>
@@ -7746,8 +8868,12 @@
       <c r="T257" s="4"/>
       <c r="U257" s="4"/>
       <c r="V257" s="4"/>
-    </row>
-    <row r="258" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W257" s="4"/>
+      <c r="X257" s="4"/>
+      <c r="Y257" s="4"/>
+      <c r="Z257" s="4"/>
+    </row>
+    <row r="258" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C258" s="4"/>
       <c r="D258" s="4"/>
       <c r="E258" s="4"/>
@@ -7768,8 +8894,12 @@
       <c r="T258" s="4"/>
       <c r="U258" s="4"/>
       <c r="V258" s="4"/>
-    </row>
-    <row r="259" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W258" s="4"/>
+      <c r="X258" s="4"/>
+      <c r="Y258" s="4"/>
+      <c r="Z258" s="4"/>
+    </row>
+    <row r="259" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C259" s="4"/>
       <c r="D259" s="4"/>
       <c r="E259" s="4"/>
@@ -7790,8 +8920,12 @@
       <c r="T259" s="4"/>
       <c r="U259" s="4"/>
       <c r="V259" s="4"/>
-    </row>
-    <row r="260" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W259" s="4"/>
+      <c r="X259" s="4"/>
+      <c r="Y259" s="4"/>
+      <c r="Z259" s="4"/>
+    </row>
+    <row r="260" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C260" s="4"/>
       <c r="D260" s="4"/>
       <c r="E260" s="4"/>
@@ -7812,8 +8946,12 @@
       <c r="T260" s="4"/>
       <c r="U260" s="4"/>
       <c r="V260" s="4"/>
-    </row>
-    <row r="261" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W260" s="4"/>
+      <c r="X260" s="4"/>
+      <c r="Y260" s="4"/>
+      <c r="Z260" s="4"/>
+    </row>
+    <row r="261" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C261" s="4"/>
       <c r="D261" s="4"/>
       <c r="E261" s="4"/>
@@ -7834,8 +8972,12 @@
       <c r="T261" s="4"/>
       <c r="U261" s="4"/>
       <c r="V261" s="4"/>
-    </row>
-    <row r="262" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W261" s="4"/>
+      <c r="X261" s="4"/>
+      <c r="Y261" s="4"/>
+      <c r="Z261" s="4"/>
+    </row>
+    <row r="262" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C262" s="4"/>
       <c r="D262" s="4"/>
       <c r="E262" s="4"/>
@@ -7856,8 +8998,12 @@
       <c r="T262" s="4"/>
       <c r="U262" s="4"/>
       <c r="V262" s="4"/>
-    </row>
-    <row r="263" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W262" s="4"/>
+      <c r="X262" s="4"/>
+      <c r="Y262" s="4"/>
+      <c r="Z262" s="4"/>
+    </row>
+    <row r="263" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C263" s="4"/>
       <c r="D263" s="4"/>
       <c r="E263" s="4"/>
@@ -7878,8 +9024,12 @@
       <c r="T263" s="4"/>
       <c r="U263" s="4"/>
       <c r="V263" s="4"/>
-    </row>
-    <row r="264" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W263" s="4"/>
+      <c r="X263" s="4"/>
+      <c r="Y263" s="4"/>
+      <c r="Z263" s="4"/>
+    </row>
+    <row r="264" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C264" s="4"/>
       <c r="D264" s="4"/>
       <c r="E264" s="4"/>
@@ -7900,8 +9050,12 @@
       <c r="T264" s="4"/>
       <c r="U264" s="4"/>
       <c r="V264" s="4"/>
-    </row>
-    <row r="265" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W264" s="4"/>
+      <c r="X264" s="4"/>
+      <c r="Y264" s="4"/>
+      <c r="Z264" s="4"/>
+    </row>
+    <row r="265" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C265" s="4"/>
       <c r="D265" s="4"/>
       <c r="E265" s="4"/>
@@ -7922,8 +9076,12 @@
       <c r="T265" s="4"/>
       <c r="U265" s="4"/>
       <c r="V265" s="4"/>
-    </row>
-    <row r="266" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W265" s="4"/>
+      <c r="X265" s="4"/>
+      <c r="Y265" s="4"/>
+      <c r="Z265" s="4"/>
+    </row>
+    <row r="266" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C266" s="4"/>
       <c r="D266" s="4"/>
       <c r="E266" s="4"/>
@@ -7944,8 +9102,12 @@
       <c r="T266" s="4"/>
       <c r="U266" s="4"/>
       <c r="V266" s="4"/>
-    </row>
-    <row r="267" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W266" s="4"/>
+      <c r="X266" s="4"/>
+      <c r="Y266" s="4"/>
+      <c r="Z266" s="4"/>
+    </row>
+    <row r="267" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C267" s="4"/>
       <c r="D267" s="4"/>
       <c r="E267" s="4"/>
@@ -7966,8 +9128,12 @@
       <c r="T267" s="4"/>
       <c r="U267" s="4"/>
       <c r="V267" s="4"/>
-    </row>
-    <row r="268" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W267" s="4"/>
+      <c r="X267" s="4"/>
+      <c r="Y267" s="4"/>
+      <c r="Z267" s="4"/>
+    </row>
+    <row r="268" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C268" s="4"/>
       <c r="D268" s="4"/>
       <c r="E268" s="4"/>
@@ -7988,8 +9154,12 @@
       <c r="T268" s="4"/>
       <c r="U268" s="4"/>
       <c r="V268" s="4"/>
-    </row>
-    <row r="269" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W268" s="4"/>
+      <c r="X268" s="4"/>
+      <c r="Y268" s="4"/>
+      <c r="Z268" s="4"/>
+    </row>
+    <row r="269" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C269" s="4"/>
       <c r="D269" s="4"/>
       <c r="E269" s="4"/>
@@ -8010,8 +9180,12 @@
       <c r="T269" s="4"/>
       <c r="U269" s="4"/>
       <c r="V269" s="4"/>
-    </row>
-    <row r="270" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W269" s="4"/>
+      <c r="X269" s="4"/>
+      <c r="Y269" s="4"/>
+      <c r="Z269" s="4"/>
+    </row>
+    <row r="270" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C270" s="4"/>
       <c r="D270" s="4"/>
       <c r="E270" s="4"/>
@@ -8032,8 +9206,12 @@
       <c r="T270" s="4"/>
       <c r="U270" s="4"/>
       <c r="V270" s="4"/>
-    </row>
-    <row r="271" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W270" s="4"/>
+      <c r="X270" s="4"/>
+      <c r="Y270" s="4"/>
+      <c r="Z270" s="4"/>
+    </row>
+    <row r="271" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C271" s="4"/>
       <c r="D271" s="4"/>
       <c r="E271" s="4"/>
@@ -8054,8 +9232,12 @@
       <c r="T271" s="4"/>
       <c r="U271" s="4"/>
       <c r="V271" s="4"/>
-    </row>
-    <row r="272" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W271" s="4"/>
+      <c r="X271" s="4"/>
+      <c r="Y271" s="4"/>
+      <c r="Z271" s="4"/>
+    </row>
+    <row r="272" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C272" s="4"/>
       <c r="D272" s="4"/>
       <c r="E272" s="4"/>
@@ -8076,8 +9258,12 @@
       <c r="T272" s="4"/>
       <c r="U272" s="4"/>
       <c r="V272" s="4"/>
-    </row>
-    <row r="273" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W272" s="4"/>
+      <c r="X272" s="4"/>
+      <c r="Y272" s="4"/>
+      <c r="Z272" s="4"/>
+    </row>
+    <row r="273" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C273" s="4"/>
       <c r="D273" s="4"/>
       <c r="E273" s="4"/>
@@ -8098,8 +9284,12 @@
       <c r="T273" s="4"/>
       <c r="U273" s="4"/>
       <c r="V273" s="4"/>
-    </row>
-    <row r="274" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W273" s="4"/>
+      <c r="X273" s="4"/>
+      <c r="Y273" s="4"/>
+      <c r="Z273" s="4"/>
+    </row>
+    <row r="274" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C274" s="4"/>
       <c r="D274" s="4"/>
       <c r="E274" s="4"/>
@@ -8120,8 +9310,12 @@
       <c r="T274" s="4"/>
       <c r="U274" s="4"/>
       <c r="V274" s="4"/>
-    </row>
-    <row r="275" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W274" s="4"/>
+      <c r="X274" s="4"/>
+      <c r="Y274" s="4"/>
+      <c r="Z274" s="4"/>
+    </row>
+    <row r="275" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C275" s="4"/>
       <c r="D275" s="4"/>
       <c r="E275" s="4"/>
@@ -8142,8 +9336,12 @@
       <c r="T275" s="4"/>
       <c r="U275" s="4"/>
       <c r="V275" s="4"/>
-    </row>
-    <row r="276" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W275" s="4"/>
+      <c r="X275" s="4"/>
+      <c r="Y275" s="4"/>
+      <c r="Z275" s="4"/>
+    </row>
+    <row r="276" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C276" s="4"/>
       <c r="D276" s="4"/>
       <c r="E276" s="4"/>
@@ -8164,8 +9362,12 @@
       <c r="T276" s="4"/>
       <c r="U276" s="4"/>
       <c r="V276" s="4"/>
-    </row>
-    <row r="277" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W276" s="4"/>
+      <c r="X276" s="4"/>
+      <c r="Y276" s="4"/>
+      <c r="Z276" s="4"/>
+    </row>
+    <row r="277" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C277" s="4"/>
       <c r="D277" s="4"/>
       <c r="E277" s="4"/>
@@ -8186,8 +9388,12 @@
       <c r="T277" s="4"/>
       <c r="U277" s="4"/>
       <c r="V277" s="4"/>
-    </row>
-    <row r="278" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W277" s="4"/>
+      <c r="X277" s="4"/>
+      <c r="Y277" s="4"/>
+      <c r="Z277" s="4"/>
+    </row>
+    <row r="278" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C278" s="4"/>
       <c r="D278" s="4"/>
       <c r="E278" s="4"/>
@@ -8208,8 +9414,12 @@
       <c r="T278" s="4"/>
       <c r="U278" s="4"/>
       <c r="V278" s="4"/>
-    </row>
-    <row r="279" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W278" s="4"/>
+      <c r="X278" s="4"/>
+      <c r="Y278" s="4"/>
+      <c r="Z278" s="4"/>
+    </row>
+    <row r="279" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C279" s="4"/>
       <c r="D279" s="4"/>
       <c r="E279" s="4"/>
@@ -8230,8 +9440,12 @@
       <c r="T279" s="4"/>
       <c r="U279" s="4"/>
       <c r="V279" s="4"/>
-    </row>
-    <row r="280" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W279" s="4"/>
+      <c r="X279" s="4"/>
+      <c r="Y279" s="4"/>
+      <c r="Z279" s="4"/>
+    </row>
+    <row r="280" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C280" s="4"/>
       <c r="D280" s="4"/>
       <c r="E280" s="4"/>
@@ -8252,8 +9466,12 @@
       <c r="T280" s="4"/>
       <c r="U280" s="4"/>
       <c r="V280" s="4"/>
-    </row>
-    <row r="281" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W280" s="4"/>
+      <c r="X280" s="4"/>
+      <c r="Y280" s="4"/>
+      <c r="Z280" s="4"/>
+    </row>
+    <row r="281" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C281" s="4"/>
       <c r="D281" s="4"/>
       <c r="E281" s="4"/>
@@ -8274,8 +9492,12 @@
       <c r="T281" s="4"/>
       <c r="U281" s="4"/>
       <c r="V281" s="4"/>
-    </row>
-    <row r="282" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W281" s="4"/>
+      <c r="X281" s="4"/>
+      <c r="Y281" s="4"/>
+      <c r="Z281" s="4"/>
+    </row>
+    <row r="282" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C282" s="4"/>
       <c r="D282" s="4"/>
       <c r="E282" s="4"/>
@@ -8296,8 +9518,12 @@
       <c r="T282" s="4"/>
       <c r="U282" s="4"/>
       <c r="V282" s="4"/>
-    </row>
-    <row r="283" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W282" s="4"/>
+      <c r="X282" s="4"/>
+      <c r="Y282" s="4"/>
+      <c r="Z282" s="4"/>
+    </row>
+    <row r="283" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C283" s="4"/>
       <c r="D283" s="4"/>
       <c r="E283" s="4"/>
@@ -8318,8 +9544,12 @@
       <c r="T283" s="4"/>
       <c r="U283" s="4"/>
       <c r="V283" s="4"/>
-    </row>
-    <row r="284" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W283" s="4"/>
+      <c r="X283" s="4"/>
+      <c r="Y283" s="4"/>
+      <c r="Z283" s="4"/>
+    </row>
+    <row r="284" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C284" s="4"/>
       <c r="D284" s="4"/>
       <c r="E284" s="4"/>
@@ -8340,8 +9570,12 @@
       <c r="T284" s="4"/>
       <c r="U284" s="4"/>
       <c r="V284" s="4"/>
-    </row>
-    <row r="285" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W284" s="4"/>
+      <c r="X284" s="4"/>
+      <c r="Y284" s="4"/>
+      <c r="Z284" s="4"/>
+    </row>
+    <row r="285" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C285" s="4"/>
       <c r="D285" s="4"/>
       <c r="E285" s="4"/>
@@ -8362,8 +9596,12 @@
       <c r="T285" s="4"/>
       <c r="U285" s="4"/>
       <c r="V285" s="4"/>
-    </row>
-    <row r="286" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W285" s="4"/>
+      <c r="X285" s="4"/>
+      <c r="Y285" s="4"/>
+      <c r="Z285" s="4"/>
+    </row>
+    <row r="286" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C286" s="4"/>
       <c r="D286" s="4"/>
       <c r="E286" s="4"/>
@@ -8384,8 +9622,12 @@
       <c r="T286" s="4"/>
       <c r="U286" s="4"/>
       <c r="V286" s="4"/>
-    </row>
-    <row r="287" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W286" s="4"/>
+      <c r="X286" s="4"/>
+      <c r="Y286" s="4"/>
+      <c r="Z286" s="4"/>
+    </row>
+    <row r="287" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C287" s="4"/>
       <c r="D287" s="4"/>
       <c r="E287" s="4"/>
@@ -8406,8 +9648,12 @@
       <c r="T287" s="4"/>
       <c r="U287" s="4"/>
       <c r="V287" s="4"/>
-    </row>
-    <row r="288" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W287" s="4"/>
+      <c r="X287" s="4"/>
+      <c r="Y287" s="4"/>
+      <c r="Z287" s="4"/>
+    </row>
+    <row r="288" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C288" s="4"/>
       <c r="D288" s="4"/>
       <c r="E288" s="4"/>
@@ -8428,8 +9674,12 @@
       <c r="T288" s="4"/>
       <c r="U288" s="4"/>
       <c r="V288" s="4"/>
-    </row>
-    <row r="289" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W288" s="4"/>
+      <c r="X288" s="4"/>
+      <c r="Y288" s="4"/>
+      <c r="Z288" s="4"/>
+    </row>
+    <row r="289" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C289" s="4"/>
       <c r="D289" s="4"/>
       <c r="E289" s="4"/>
@@ -8450,8 +9700,12 @@
       <c r="T289" s="4"/>
       <c r="U289" s="4"/>
       <c r="V289" s="4"/>
-    </row>
-    <row r="290" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W289" s="4"/>
+      <c r="X289" s="4"/>
+      <c r="Y289" s="4"/>
+      <c r="Z289" s="4"/>
+    </row>
+    <row r="290" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C290" s="4"/>
       <c r="D290" s="4"/>
       <c r="E290" s="4"/>
@@ -8472,8 +9726,12 @@
       <c r="T290" s="4"/>
       <c r="U290" s="4"/>
       <c r="V290" s="4"/>
-    </row>
-    <row r="291" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W290" s="4"/>
+      <c r="X290" s="4"/>
+      <c r="Y290" s="4"/>
+      <c r="Z290" s="4"/>
+    </row>
+    <row r="291" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C291" s="4"/>
       <c r="D291" s="4"/>
       <c r="E291" s="4"/>
@@ -8494,8 +9752,12 @@
       <c r="T291" s="4"/>
       <c r="U291" s="4"/>
       <c r="V291" s="4"/>
-    </row>
-    <row r="292" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W291" s="4"/>
+      <c r="X291" s="4"/>
+      <c r="Y291" s="4"/>
+      <c r="Z291" s="4"/>
+    </row>
+    <row r="292" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C292" s="4"/>
       <c r="D292" s="4"/>
       <c r="E292" s="4"/>
@@ -8516,8 +9778,12 @@
       <c r="T292" s="4"/>
       <c r="U292" s="4"/>
       <c r="V292" s="4"/>
-    </row>
-    <row r="293" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W292" s="4"/>
+      <c r="X292" s="4"/>
+      <c r="Y292" s="4"/>
+      <c r="Z292" s="4"/>
+    </row>
+    <row r="293" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C293" s="4"/>
       <c r="D293" s="4"/>
       <c r="E293" s="4"/>
@@ -8538,8 +9804,12 @@
       <c r="T293" s="4"/>
       <c r="U293" s="4"/>
       <c r="V293" s="4"/>
-    </row>
-    <row r="294" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W293" s="4"/>
+      <c r="X293" s="4"/>
+      <c r="Y293" s="4"/>
+      <c r="Z293" s="4"/>
+    </row>
+    <row r="294" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C294" s="4"/>
       <c r="D294" s="4"/>
       <c r="E294" s="4"/>
@@ -8560,8 +9830,12 @@
       <c r="T294" s="4"/>
       <c r="U294" s="4"/>
       <c r="V294" s="4"/>
-    </row>
-    <row r="295" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W294" s="4"/>
+      <c r="X294" s="4"/>
+      <c r="Y294" s="4"/>
+      <c r="Z294" s="4"/>
+    </row>
+    <row r="295" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C295" s="4"/>
       <c r="D295" s="4"/>
       <c r="E295" s="4"/>
@@ -8582,8 +9856,12 @@
       <c r="T295" s="4"/>
       <c r="U295" s="4"/>
       <c r="V295" s="4"/>
-    </row>
-    <row r="296" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W295" s="4"/>
+      <c r="X295" s="4"/>
+      <c r="Y295" s="4"/>
+      <c r="Z295" s="4"/>
+    </row>
+    <row r="296" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C296" s="4"/>
       <c r="D296" s="4"/>
       <c r="E296" s="4"/>
@@ -8604,8 +9882,12 @@
       <c r="T296" s="4"/>
       <c r="U296" s="4"/>
       <c r="V296" s="4"/>
-    </row>
-    <row r="297" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W296" s="4"/>
+      <c r="X296" s="4"/>
+      <c r="Y296" s="4"/>
+      <c r="Z296" s="4"/>
+    </row>
+    <row r="297" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C297" s="4"/>
       <c r="D297" s="4"/>
       <c r="E297" s="4"/>
@@ -8626,8 +9908,12 @@
       <c r="T297" s="4"/>
       <c r="U297" s="4"/>
       <c r="V297" s="4"/>
-    </row>
-    <row r="298" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W297" s="4"/>
+      <c r="X297" s="4"/>
+      <c r="Y297" s="4"/>
+      <c r="Z297" s="4"/>
+    </row>
+    <row r="298" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C298" s="4"/>
       <c r="D298" s="4"/>
       <c r="E298" s="4"/>
@@ -8648,8 +9934,12 @@
       <c r="T298" s="4"/>
       <c r="U298" s="4"/>
       <c r="V298" s="4"/>
-    </row>
-    <row r="299" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W298" s="4"/>
+      <c r="X298" s="4"/>
+      <c r="Y298" s="4"/>
+      <c r="Z298" s="4"/>
+    </row>
+    <row r="299" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C299" s="4"/>
       <c r="D299" s="4"/>
       <c r="E299" s="4"/>
@@ -8670,8 +9960,12 @@
       <c r="T299" s="4"/>
       <c r="U299" s="4"/>
       <c r="V299" s="4"/>
-    </row>
-    <row r="300" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W299" s="4"/>
+      <c r="X299" s="4"/>
+      <c r="Y299" s="4"/>
+      <c r="Z299" s="4"/>
+    </row>
+    <row r="300" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C300" s="4"/>
       <c r="D300" s="4"/>
       <c r="E300" s="4"/>
@@ -8692,8 +9986,12 @@
       <c r="T300" s="4"/>
       <c r="U300" s="4"/>
       <c r="V300" s="4"/>
-    </row>
-    <row r="301" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W300" s="4"/>
+      <c r="X300" s="4"/>
+      <c r="Y300" s="4"/>
+      <c r="Z300" s="4"/>
+    </row>
+    <row r="301" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C301" s="4"/>
       <c r="D301" s="4"/>
       <c r="E301" s="4"/>
@@ -8714,8 +10012,12 @@
       <c r="T301" s="4"/>
       <c r="U301" s="4"/>
       <c r="V301" s="4"/>
-    </row>
-    <row r="302" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W301" s="4"/>
+      <c r="X301" s="4"/>
+      <c r="Y301" s="4"/>
+      <c r="Z301" s="4"/>
+    </row>
+    <row r="302" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C302" s="4"/>
       <c r="D302" s="4"/>
       <c r="E302" s="4"/>
@@ -8736,8 +10038,12 @@
       <c r="T302" s="4"/>
       <c r="U302" s="4"/>
       <c r="V302" s="4"/>
-    </row>
-    <row r="303" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W302" s="4"/>
+      <c r="X302" s="4"/>
+      <c r="Y302" s="4"/>
+      <c r="Z302" s="4"/>
+    </row>
+    <row r="303" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C303" s="4"/>
       <c r="D303" s="4"/>
       <c r="E303" s="4"/>
@@ -8758,8 +10064,12 @@
       <c r="T303" s="4"/>
       <c r="U303" s="4"/>
       <c r="V303" s="4"/>
-    </row>
-    <row r="304" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W303" s="4"/>
+      <c r="X303" s="4"/>
+      <c r="Y303" s="4"/>
+      <c r="Z303" s="4"/>
+    </row>
+    <row r="304" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C304" s="4"/>
       <c r="D304" s="4"/>
       <c r="E304" s="4"/>
@@ -8780,8 +10090,12 @@
       <c r="T304" s="4"/>
       <c r="U304" s="4"/>
       <c r="V304" s="4"/>
-    </row>
-    <row r="305" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W304" s="4"/>
+      <c r="X304" s="4"/>
+      <c r="Y304" s="4"/>
+      <c r="Z304" s="4"/>
+    </row>
+    <row r="305" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C305" s="4"/>
       <c r="D305" s="4"/>
       <c r="E305" s="4"/>
@@ -8802,8 +10116,12 @@
       <c r="T305" s="4"/>
       <c r="U305" s="4"/>
       <c r="V305" s="4"/>
-    </row>
-    <row r="306" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W305" s="4"/>
+      <c r="X305" s="4"/>
+      <c r="Y305" s="4"/>
+      <c r="Z305" s="4"/>
+    </row>
+    <row r="306" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C306" s="4"/>
       <c r="D306" s="4"/>
       <c r="E306" s="4"/>
@@ -8824,8 +10142,12 @@
       <c r="T306" s="4"/>
       <c r="U306" s="4"/>
       <c r="V306" s="4"/>
-    </row>
-    <row r="307" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W306" s="4"/>
+      <c r="X306" s="4"/>
+      <c r="Y306" s="4"/>
+      <c r="Z306" s="4"/>
+    </row>
+    <row r="307" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C307" s="4"/>
       <c r="D307" s="4"/>
       <c r="E307" s="4"/>
@@ -8846,8 +10168,12 @@
       <c r="T307" s="4"/>
       <c r="U307" s="4"/>
       <c r="V307" s="4"/>
-    </row>
-    <row r="308" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W307" s="4"/>
+      <c r="X307" s="4"/>
+      <c r="Y307" s="4"/>
+      <c r="Z307" s="4"/>
+    </row>
+    <row r="308" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C308" s="4"/>
       <c r="D308" s="4"/>
       <c r="E308" s="4"/>
@@ -8868,8 +10194,12 @@
       <c r="T308" s="4"/>
       <c r="U308" s="4"/>
       <c r="V308" s="4"/>
-    </row>
-    <row r="309" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W308" s="4"/>
+      <c r="X308" s="4"/>
+      <c r="Y308" s="4"/>
+      <c r="Z308" s="4"/>
+    </row>
+    <row r="309" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C309" s="4"/>
       <c r="D309" s="4"/>
       <c r="E309" s="4"/>
@@ -8890,8 +10220,12 @@
       <c r="T309" s="4"/>
       <c r="U309" s="4"/>
       <c r="V309" s="4"/>
-    </row>
-    <row r="310" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W309" s="4"/>
+      <c r="X309" s="4"/>
+      <c r="Y309" s="4"/>
+      <c r="Z309" s="4"/>
+    </row>
+    <row r="310" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C310" s="4"/>
       <c r="D310" s="4"/>
       <c r="E310" s="4"/>
@@ -8912,8 +10246,12 @@
       <c r="T310" s="4"/>
       <c r="U310" s="4"/>
       <c r="V310" s="4"/>
-    </row>
-    <row r="311" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W310" s="4"/>
+      <c r="X310" s="4"/>
+      <c r="Y310" s="4"/>
+      <c r="Z310" s="4"/>
+    </row>
+    <row r="311" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C311" s="4"/>
       <c r="D311" s="4"/>
       <c r="E311" s="4"/>
@@ -8934,8 +10272,12 @@
       <c r="T311" s="4"/>
       <c r="U311" s="4"/>
       <c r="V311" s="4"/>
-    </row>
-    <row r="312" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W311" s="4"/>
+      <c r="X311" s="4"/>
+      <c r="Y311" s="4"/>
+      <c r="Z311" s="4"/>
+    </row>
+    <row r="312" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C312" s="4"/>
       <c r="D312" s="4"/>
       <c r="E312" s="4"/>
@@ -8956,8 +10298,12 @@
       <c r="T312" s="4"/>
       <c r="U312" s="4"/>
       <c r="V312" s="4"/>
-    </row>
-    <row r="313" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W312" s="4"/>
+      <c r="X312" s="4"/>
+      <c r="Y312" s="4"/>
+      <c r="Z312" s="4"/>
+    </row>
+    <row r="313" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C313" s="4"/>
       <c r="D313" s="4"/>
       <c r="E313" s="4"/>
@@ -8978,8 +10324,12 @@
       <c r="T313" s="4"/>
       <c r="U313" s="4"/>
       <c r="V313" s="4"/>
-    </row>
-    <row r="314" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W313" s="4"/>
+      <c r="X313" s="4"/>
+      <c r="Y313" s="4"/>
+      <c r="Z313" s="4"/>
+    </row>
+    <row r="314" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C314" s="4"/>
       <c r="D314" s="4"/>
       <c r="E314" s="4"/>
@@ -9000,8 +10350,12 @@
       <c r="T314" s="4"/>
       <c r="U314" s="4"/>
       <c r="V314" s="4"/>
-    </row>
-    <row r="315" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W314" s="4"/>
+      <c r="X314" s="4"/>
+      <c r="Y314" s="4"/>
+      <c r="Z314" s="4"/>
+    </row>
+    <row r="315" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C315" s="4"/>
       <c r="D315" s="4"/>
       <c r="E315" s="4"/>
@@ -9022,8 +10376,12 @@
       <c r="T315" s="4"/>
       <c r="U315" s="4"/>
       <c r="V315" s="4"/>
-    </row>
-    <row r="316" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W315" s="4"/>
+      <c r="X315" s="4"/>
+      <c r="Y315" s="4"/>
+      <c r="Z315" s="4"/>
+    </row>
+    <row r="316" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C316" s="4"/>
       <c r="D316" s="4"/>
       <c r="E316" s="4"/>
@@ -9044,8 +10402,12 @@
       <c r="T316" s="4"/>
       <c r="U316" s="4"/>
       <c r="V316" s="4"/>
-    </row>
-    <row r="317" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W316" s="4"/>
+      <c r="X316" s="4"/>
+      <c r="Y316" s="4"/>
+      <c r="Z316" s="4"/>
+    </row>
+    <row r="317" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C317" s="4"/>
       <c r="D317" s="4"/>
       <c r="E317" s="4"/>
@@ -9066,8 +10428,12 @@
       <c r="T317" s="4"/>
       <c r="U317" s="4"/>
       <c r="V317" s="4"/>
-    </row>
-    <row r="318" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W317" s="4"/>
+      <c r="X317" s="4"/>
+      <c r="Y317" s="4"/>
+      <c r="Z317" s="4"/>
+    </row>
+    <row r="318" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C318" s="4"/>
       <c r="D318" s="4"/>
       <c r="E318" s="4"/>
@@ -9088,8 +10454,12 @@
       <c r="T318" s="4"/>
       <c r="U318" s="4"/>
       <c r="V318" s="4"/>
-    </row>
-    <row r="319" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W318" s="4"/>
+      <c r="X318" s="4"/>
+      <c r="Y318" s="4"/>
+      <c r="Z318" s="4"/>
+    </row>
+    <row r="319" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C319" s="4"/>
       <c r="D319" s="4"/>
       <c r="E319" s="4"/>
@@ -9110,8 +10480,12 @@
       <c r="T319" s="4"/>
       <c r="U319" s="4"/>
       <c r="V319" s="4"/>
-    </row>
-    <row r="320" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W319" s="4"/>
+      <c r="X319" s="4"/>
+      <c r="Y319" s="4"/>
+      <c r="Z319" s="4"/>
+    </row>
+    <row r="320" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C320" s="4"/>
       <c r="D320" s="4"/>
       <c r="E320" s="4"/>
@@ -9132,8 +10506,12 @@
       <c r="T320" s="4"/>
       <c r="U320" s="4"/>
       <c r="V320" s="4"/>
-    </row>
-    <row r="321" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W320" s="4"/>
+      <c r="X320" s="4"/>
+      <c r="Y320" s="4"/>
+      <c r="Z320" s="4"/>
+    </row>
+    <row r="321" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C321" s="4"/>
       <c r="D321" s="4"/>
       <c r="E321" s="4"/>
@@ -9154,8 +10532,12 @@
       <c r="T321" s="4"/>
       <c r="U321" s="4"/>
       <c r="V321" s="4"/>
-    </row>
-    <row r="322" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W321" s="4"/>
+      <c r="X321" s="4"/>
+      <c r="Y321" s="4"/>
+      <c r="Z321" s="4"/>
+    </row>
+    <row r="322" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C322" s="4"/>
       <c r="D322" s="4"/>
       <c r="E322" s="4"/>
@@ -9176,8 +10558,12 @@
       <c r="T322" s="4"/>
       <c r="U322" s="4"/>
       <c r="V322" s="4"/>
-    </row>
-    <row r="323" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W322" s="4"/>
+      <c r="X322" s="4"/>
+      <c r="Y322" s="4"/>
+      <c r="Z322" s="4"/>
+    </row>
+    <row r="323" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C323" s="4"/>
       <c r="D323" s="4"/>
       <c r="E323" s="4"/>
@@ -9198,8 +10584,12 @@
       <c r="T323" s="4"/>
       <c r="U323" s="4"/>
       <c r="V323" s="4"/>
-    </row>
-    <row r="324" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W323" s="4"/>
+      <c r="X323" s="4"/>
+      <c r="Y323" s="4"/>
+      <c r="Z323" s="4"/>
+    </row>
+    <row r="324" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C324" s="4"/>
       <c r="D324" s="4"/>
       <c r="E324" s="4"/>
@@ -9220,8 +10610,12 @@
       <c r="T324" s="4"/>
       <c r="U324" s="4"/>
       <c r="V324" s="4"/>
-    </row>
-    <row r="325" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W324" s="4"/>
+      <c r="X324" s="4"/>
+      <c r="Y324" s="4"/>
+      <c r="Z324" s="4"/>
+    </row>
+    <row r="325" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C325" s="4"/>
       <c r="D325" s="4"/>
       <c r="E325" s="4"/>
@@ -9242,8 +10636,12 @@
       <c r="T325" s="4"/>
       <c r="U325" s="4"/>
       <c r="V325" s="4"/>
-    </row>
-    <row r="326" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W325" s="4"/>
+      <c r="X325" s="4"/>
+      <c r="Y325" s="4"/>
+      <c r="Z325" s="4"/>
+    </row>
+    <row r="326" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C326" s="4"/>
       <c r="D326" s="4"/>
       <c r="E326" s="4"/>
@@ -9264,8 +10662,12 @@
       <c r="T326" s="4"/>
       <c r="U326" s="4"/>
       <c r="V326" s="4"/>
-    </row>
-    <row r="327" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W326" s="4"/>
+      <c r="X326" s="4"/>
+      <c r="Y326" s="4"/>
+      <c r="Z326" s="4"/>
+    </row>
+    <row r="327" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C327" s="4"/>
       <c r="D327" s="4"/>
       <c r="E327" s="4"/>
@@ -9286,8 +10688,12 @@
       <c r="T327" s="4"/>
       <c r="U327" s="4"/>
       <c r="V327" s="4"/>
-    </row>
-    <row r="328" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W327" s="4"/>
+      <c r="X327" s="4"/>
+      <c r="Y327" s="4"/>
+      <c r="Z327" s="4"/>
+    </row>
+    <row r="328" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C328" s="4"/>
       <c r="D328" s="4"/>
       <c r="E328" s="4"/>
@@ -9308,8 +10714,12 @@
       <c r="T328" s="4"/>
       <c r="U328" s="4"/>
       <c r="V328" s="4"/>
-    </row>
-    <row r="329" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W328" s="4"/>
+      <c r="X328" s="4"/>
+      <c r="Y328" s="4"/>
+      <c r="Z328" s="4"/>
+    </row>
+    <row r="329" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C329" s="4"/>
       <c r="D329" s="4"/>
       <c r="E329" s="4"/>
@@ -9330,8 +10740,12 @@
       <c r="T329" s="4"/>
       <c r="U329" s="4"/>
       <c r="V329" s="4"/>
-    </row>
-    <row r="330" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W329" s="4"/>
+      <c r="X329" s="4"/>
+      <c r="Y329" s="4"/>
+      <c r="Z329" s="4"/>
+    </row>
+    <row r="330" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C330" s="4"/>
       <c r="D330" s="4"/>
       <c r="E330" s="4"/>
@@ -9352,8 +10766,12 @@
       <c r="T330" s="4"/>
       <c r="U330" s="4"/>
       <c r="V330" s="4"/>
-    </row>
-    <row r="331" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W330" s="4"/>
+      <c r="X330" s="4"/>
+      <c r="Y330" s="4"/>
+      <c r="Z330" s="4"/>
+    </row>
+    <row r="331" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C331" s="4"/>
       <c r="D331" s="4"/>
       <c r="E331" s="4"/>
@@ -9374,8 +10792,12 @@
       <c r="T331" s="4"/>
       <c r="U331" s="4"/>
       <c r="V331" s="4"/>
-    </row>
-    <row r="332" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W331" s="4"/>
+      <c r="X331" s="4"/>
+      <c r="Y331" s="4"/>
+      <c r="Z331" s="4"/>
+    </row>
+    <row r="332" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C332" s="4"/>
       <c r="D332" s="4"/>
       <c r="E332" s="4"/>
@@ -9396,8 +10818,12 @@
       <c r="T332" s="4"/>
       <c r="U332" s="4"/>
       <c r="V332" s="4"/>
-    </row>
-    <row r="333" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W332" s="4"/>
+      <c r="X332" s="4"/>
+      <c r="Y332" s="4"/>
+      <c r="Z332" s="4"/>
+    </row>
+    <row r="333" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C333" s="4"/>
       <c r="D333" s="4"/>
       <c r="E333" s="4"/>
@@ -9418,8 +10844,12 @@
       <c r="T333" s="4"/>
       <c r="U333" s="4"/>
       <c r="V333" s="4"/>
-    </row>
-    <row r="334" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W333" s="4"/>
+      <c r="X333" s="4"/>
+      <c r="Y333" s="4"/>
+      <c r="Z333" s="4"/>
+    </row>
+    <row r="334" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C334" s="4"/>
       <c r="D334" s="4"/>
       <c r="E334" s="4"/>
@@ -9440,8 +10870,12 @@
       <c r="T334" s="4"/>
       <c r="U334" s="4"/>
       <c r="V334" s="4"/>
-    </row>
-    <row r="335" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W334" s="4"/>
+      <c r="X334" s="4"/>
+      <c r="Y334" s="4"/>
+      <c r="Z334" s="4"/>
+    </row>
+    <row r="335" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C335" s="4"/>
       <c r="D335" s="4"/>
       <c r="E335" s="4"/>
@@ -9462,8 +10896,12 @@
       <c r="T335" s="4"/>
       <c r="U335" s="4"/>
       <c r="V335" s="4"/>
-    </row>
-    <row r="336" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W335" s="4"/>
+      <c r="X335" s="4"/>
+      <c r="Y335" s="4"/>
+      <c r="Z335" s="4"/>
+    </row>
+    <row r="336" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C336" s="4"/>
       <c r="D336" s="4"/>
       <c r="E336" s="4"/>
@@ -9484,8 +10922,12 @@
       <c r="T336" s="4"/>
       <c r="U336" s="4"/>
       <c r="V336" s="4"/>
-    </row>
-    <row r="337" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W336" s="4"/>
+      <c r="X336" s="4"/>
+      <c r="Y336" s="4"/>
+      <c r="Z336" s="4"/>
+    </row>
+    <row r="337" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C337" s="4"/>
       <c r="D337" s="4"/>
       <c r="E337" s="4"/>
@@ -9506,8 +10948,12 @@
       <c r="T337" s="4"/>
       <c r="U337" s="4"/>
       <c r="V337" s="4"/>
-    </row>
-    <row r="338" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W337" s="4"/>
+      <c r="X337" s="4"/>
+      <c r="Y337" s="4"/>
+      <c r="Z337" s="4"/>
+    </row>
+    <row r="338" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C338" s="4"/>
       <c r="D338" s="4"/>
       <c r="E338" s="4"/>
@@ -9528,8 +10974,12 @@
       <c r="T338" s="4"/>
       <c r="U338" s="4"/>
       <c r="V338" s="4"/>
-    </row>
-    <row r="339" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W338" s="4"/>
+      <c r="X338" s="4"/>
+      <c r="Y338" s="4"/>
+      <c r="Z338" s="4"/>
+    </row>
+    <row r="339" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C339" s="4"/>
       <c r="D339" s="4"/>
       <c r="E339" s="4"/>
@@ -9550,8 +11000,12 @@
       <c r="T339" s="4"/>
       <c r="U339" s="4"/>
       <c r="V339" s="4"/>
-    </row>
-    <row r="340" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W339" s="4"/>
+      <c r="X339" s="4"/>
+      <c r="Y339" s="4"/>
+      <c r="Z339" s="4"/>
+    </row>
+    <row r="340" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C340" s="4"/>
       <c r="D340" s="4"/>
       <c r="E340" s="4"/>
@@ -9572,8 +11026,12 @@
       <c r="T340" s="4"/>
       <c r="U340" s="4"/>
       <c r="V340" s="4"/>
-    </row>
-    <row r="341" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W340" s="4"/>
+      <c r="X340" s="4"/>
+      <c r="Y340" s="4"/>
+      <c r="Z340" s="4"/>
+    </row>
+    <row r="341" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C341" s="4"/>
       <c r="D341" s="4"/>
       <c r="E341" s="4"/>
@@ -9594,8 +11052,12 @@
       <c r="T341" s="4"/>
       <c r="U341" s="4"/>
       <c r="V341" s="4"/>
-    </row>
-    <row r="342" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W341" s="4"/>
+      <c r="X341" s="4"/>
+      <c r="Y341" s="4"/>
+      <c r="Z341" s="4"/>
+    </row>
+    <row r="342" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C342" s="4"/>
       <c r="D342" s="4"/>
       <c r="E342" s="4"/>
@@ -9616,8 +11078,12 @@
       <c r="T342" s="4"/>
       <c r="U342" s="4"/>
       <c r="V342" s="4"/>
-    </row>
-    <row r="343" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W342" s="4"/>
+      <c r="X342" s="4"/>
+      <c r="Y342" s="4"/>
+      <c r="Z342" s="4"/>
+    </row>
+    <row r="343" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C343" s="4"/>
       <c r="D343" s="4"/>
       <c r="E343" s="4"/>
@@ -9638,8 +11104,12 @@
       <c r="T343" s="4"/>
       <c r="U343" s="4"/>
       <c r="V343" s="4"/>
-    </row>
-    <row r="344" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W343" s="4"/>
+      <c r="X343" s="4"/>
+      <c r="Y343" s="4"/>
+      <c r="Z343" s="4"/>
+    </row>
+    <row r="344" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C344" s="4"/>
       <c r="D344" s="4"/>
       <c r="E344" s="4"/>
@@ -9660,8 +11130,12 @@
       <c r="T344" s="4"/>
       <c r="U344" s="4"/>
       <c r="V344" s="4"/>
-    </row>
-    <row r="345" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W344" s="4"/>
+      <c r="X344" s="4"/>
+      <c r="Y344" s="4"/>
+      <c r="Z344" s="4"/>
+    </row>
+    <row r="345" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C345" s="4"/>
       <c r="D345" s="4"/>
       <c r="E345" s="4"/>
@@ -9682,8 +11156,12 @@
       <c r="T345" s="4"/>
       <c r="U345" s="4"/>
       <c r="V345" s="4"/>
-    </row>
-    <row r="346" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W345" s="4"/>
+      <c r="X345" s="4"/>
+      <c r="Y345" s="4"/>
+      <c r="Z345" s="4"/>
+    </row>
+    <row r="346" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C346" s="4"/>
       <c r="D346" s="4"/>
       <c r="E346" s="4"/>
@@ -9704,8 +11182,12 @@
       <c r="T346" s="4"/>
       <c r="U346" s="4"/>
       <c r="V346" s="4"/>
-    </row>
-    <row r="347" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W346" s="4"/>
+      <c r="X346" s="4"/>
+      <c r="Y346" s="4"/>
+      <c r="Z346" s="4"/>
+    </row>
+    <row r="347" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C347" s="4"/>
       <c r="D347" s="4"/>
       <c r="E347" s="4"/>
@@ -9726,8 +11208,12 @@
       <c r="T347" s="4"/>
       <c r="U347" s="4"/>
       <c r="V347" s="4"/>
-    </row>
-    <row r="348" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W347" s="4"/>
+      <c r="X347" s="4"/>
+      <c r="Y347" s="4"/>
+      <c r="Z347" s="4"/>
+    </row>
+    <row r="348" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C348" s="4"/>
       <c r="D348" s="4"/>
       <c r="E348" s="4"/>
@@ -9748,8 +11234,12 @@
       <c r="T348" s="4"/>
       <c r="U348" s="4"/>
       <c r="V348" s="4"/>
-    </row>
-    <row r="349" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W348" s="4"/>
+      <c r="X348" s="4"/>
+      <c r="Y348" s="4"/>
+      <c r="Z348" s="4"/>
+    </row>
+    <row r="349" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C349" s="4"/>
       <c r="D349" s="4"/>
       <c r="E349" s="4"/>
@@ -9770,8 +11260,12 @@
       <c r="T349" s="4"/>
       <c r="U349" s="4"/>
       <c r="V349" s="4"/>
-    </row>
-    <row r="350" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W349" s="4"/>
+      <c r="X349" s="4"/>
+      <c r="Y349" s="4"/>
+      <c r="Z349" s="4"/>
+    </row>
+    <row r="350" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C350" s="4"/>
       <c r="D350" s="4"/>
       <c r="E350" s="4"/>
@@ -9792,8 +11286,12 @@
       <c r="T350" s="4"/>
       <c r="U350" s="4"/>
       <c r="V350" s="4"/>
-    </row>
-    <row r="351" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W350" s="4"/>
+      <c r="X350" s="4"/>
+      <c r="Y350" s="4"/>
+      <c r="Z350" s="4"/>
+    </row>
+    <row r="351" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C351" s="4"/>
       <c r="D351" s="4"/>
       <c r="E351" s="4"/>
@@ -9814,8 +11312,12 @@
       <c r="T351" s="4"/>
       <c r="U351" s="4"/>
       <c r="V351" s="4"/>
-    </row>
-    <row r="352" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W351" s="4"/>
+      <c r="X351" s="4"/>
+      <c r="Y351" s="4"/>
+      <c r="Z351" s="4"/>
+    </row>
+    <row r="352" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C352" s="4"/>
       <c r="D352" s="4"/>
       <c r="E352" s="4"/>
@@ -9836,8 +11338,12 @@
       <c r="T352" s="4"/>
       <c r="U352" s="4"/>
       <c r="V352" s="4"/>
-    </row>
-    <row r="353" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W352" s="4"/>
+      <c r="X352" s="4"/>
+      <c r="Y352" s="4"/>
+      <c r="Z352" s="4"/>
+    </row>
+    <row r="353" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C353" s="4"/>
       <c r="D353" s="4"/>
       <c r="E353" s="4"/>
@@ -9858,8 +11364,12 @@
       <c r="T353" s="4"/>
       <c r="U353" s="4"/>
       <c r="V353" s="4"/>
-    </row>
-    <row r="354" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W353" s="4"/>
+      <c r="X353" s="4"/>
+      <c r="Y353" s="4"/>
+      <c r="Z353" s="4"/>
+    </row>
+    <row r="354" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C354" s="4"/>
       <c r="D354" s="4"/>
       <c r="E354" s="4"/>
@@ -9880,8 +11390,12 @@
       <c r="T354" s="4"/>
       <c r="U354" s="4"/>
       <c r="V354" s="4"/>
-    </row>
-    <row r="355" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W354" s="4"/>
+      <c r="X354" s="4"/>
+      <c r="Y354" s="4"/>
+      <c r="Z354" s="4"/>
+    </row>
+    <row r="355" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C355" s="4"/>
       <c r="D355" s="4"/>
       <c r="E355" s="4"/>
@@ -9902,8 +11416,12 @@
       <c r="T355" s="4"/>
       <c r="U355" s="4"/>
       <c r="V355" s="4"/>
-    </row>
-    <row r="356" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W355" s="4"/>
+      <c r="X355" s="4"/>
+      <c r="Y355" s="4"/>
+      <c r="Z355" s="4"/>
+    </row>
+    <row r="356" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C356" s="4"/>
       <c r="D356" s="4"/>
       <c r="E356" s="4"/>
@@ -9924,8 +11442,12 @@
       <c r="T356" s="4"/>
       <c r="U356" s="4"/>
       <c r="V356" s="4"/>
-    </row>
-    <row r="357" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W356" s="4"/>
+      <c r="X356" s="4"/>
+      <c r="Y356" s="4"/>
+      <c r="Z356" s="4"/>
+    </row>
+    <row r="357" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C357" s="4"/>
       <c r="D357" s="4"/>
       <c r="E357" s="4"/>
@@ -9946,8 +11468,12 @@
       <c r="T357" s="4"/>
       <c r="U357" s="4"/>
       <c r="V357" s="4"/>
-    </row>
-    <row r="358" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W357" s="4"/>
+      <c r="X357" s="4"/>
+      <c r="Y357" s="4"/>
+      <c r="Z357" s="4"/>
+    </row>
+    <row r="358" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C358" s="4"/>
       <c r="D358" s="4"/>
       <c r="E358" s="4"/>
@@ -9968,8 +11494,12 @@
       <c r="T358" s="4"/>
       <c r="U358" s="4"/>
       <c r="V358" s="4"/>
-    </row>
-    <row r="359" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W358" s="4"/>
+      <c r="X358" s="4"/>
+      <c r="Y358" s="4"/>
+      <c r="Z358" s="4"/>
+    </row>
+    <row r="359" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C359" s="4"/>
       <c r="D359" s="4"/>
       <c r="E359" s="4"/>
@@ -9990,8 +11520,12 @@
       <c r="T359" s="4"/>
       <c r="U359" s="4"/>
       <c r="V359" s="4"/>
-    </row>
-    <row r="360" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W359" s="4"/>
+      <c r="X359" s="4"/>
+      <c r="Y359" s="4"/>
+      <c r="Z359" s="4"/>
+    </row>
+    <row r="360" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C360" s="4"/>
       <c r="D360" s="4"/>
       <c r="E360" s="4"/>
@@ -10012,8 +11546,12 @@
       <c r="T360" s="4"/>
       <c r="U360" s="4"/>
       <c r="V360" s="4"/>
-    </row>
-    <row r="361" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W360" s="4"/>
+      <c r="X360" s="4"/>
+      <c r="Y360" s="4"/>
+      <c r="Z360" s="4"/>
+    </row>
+    <row r="361" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C361" s="4"/>
       <c r="D361" s="4"/>
       <c r="E361" s="4"/>
@@ -10034,8 +11572,12 @@
       <c r="T361" s="4"/>
       <c r="U361" s="4"/>
       <c r="V361" s="4"/>
-    </row>
-    <row r="362" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W361" s="4"/>
+      <c r="X361" s="4"/>
+      <c r="Y361" s="4"/>
+      <c r="Z361" s="4"/>
+    </row>
+    <row r="362" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C362" s="4"/>
       <c r="D362" s="4"/>
       <c r="E362" s="4"/>
@@ -10056,8 +11598,12 @@
       <c r="T362" s="4"/>
       <c r="U362" s="4"/>
       <c r="V362" s="4"/>
-    </row>
-    <row r="363" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W362" s="4"/>
+      <c r="X362" s="4"/>
+      <c r="Y362" s="4"/>
+      <c r="Z362" s="4"/>
+    </row>
+    <row r="363" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C363" s="4"/>
       <c r="D363" s="4"/>
       <c r="E363" s="4"/>
@@ -10078,8 +11624,12 @@
       <c r="T363" s="4"/>
       <c r="U363" s="4"/>
       <c r="V363" s="4"/>
-    </row>
-    <row r="364" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W363" s="4"/>
+      <c r="X363" s="4"/>
+      <c r="Y363" s="4"/>
+      <c r="Z363" s="4"/>
+    </row>
+    <row r="364" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C364" s="4"/>
       <c r="D364" s="4"/>
       <c r="E364" s="4"/>
@@ -10100,8 +11650,12 @@
       <c r="T364" s="4"/>
       <c r="U364" s="4"/>
       <c r="V364" s="4"/>
-    </row>
-    <row r="365" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W364" s="4"/>
+      <c r="X364" s="4"/>
+      <c r="Y364" s="4"/>
+      <c r="Z364" s="4"/>
+    </row>
+    <row r="365" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C365" s="4"/>
       <c r="D365" s="4"/>
       <c r="E365" s="4"/>
@@ -10122,8 +11676,12 @@
       <c r="T365" s="4"/>
       <c r="U365" s="4"/>
       <c r="V365" s="4"/>
-    </row>
-    <row r="366" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W365" s="4"/>
+      <c r="X365" s="4"/>
+      <c r="Y365" s="4"/>
+      <c r="Z365" s="4"/>
+    </row>
+    <row r="366" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C366" s="4"/>
       <c r="D366" s="4"/>
       <c r="E366" s="4"/>
@@ -10144,8 +11702,12 @@
       <c r="T366" s="4"/>
       <c r="U366" s="4"/>
       <c r="V366" s="4"/>
-    </row>
-    <row r="367" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W366" s="4"/>
+      <c r="X366" s="4"/>
+      <c r="Y366" s="4"/>
+      <c r="Z366" s="4"/>
+    </row>
+    <row r="367" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C367" s="4"/>
       <c r="D367" s="4"/>
       <c r="E367" s="4"/>
@@ -10166,8 +11728,12 @@
       <c r="T367" s="4"/>
       <c r="U367" s="4"/>
       <c r="V367" s="4"/>
-    </row>
-    <row r="368" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W367" s="4"/>
+      <c r="X367" s="4"/>
+      <c r="Y367" s="4"/>
+      <c r="Z367" s="4"/>
+    </row>
+    <row r="368" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C368" s="4"/>
       <c r="D368" s="4"/>
       <c r="E368" s="4"/>
@@ -10188,8 +11754,12 @@
       <c r="T368" s="4"/>
       <c r="U368" s="4"/>
       <c r="V368" s="4"/>
-    </row>
-    <row r="369" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W368" s="4"/>
+      <c r="X368" s="4"/>
+      <c r="Y368" s="4"/>
+      <c r="Z368" s="4"/>
+    </row>
+    <row r="369" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C369" s="4"/>
       <c r="D369" s="4"/>
       <c r="E369" s="4"/>
@@ -10210,8 +11780,12 @@
       <c r="T369" s="4"/>
       <c r="U369" s="4"/>
       <c r="V369" s="4"/>
-    </row>
-    <row r="370" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W369" s="4"/>
+      <c r="X369" s="4"/>
+      <c r="Y369" s="4"/>
+      <c r="Z369" s="4"/>
+    </row>
+    <row r="370" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C370" s="4"/>
       <c r="D370" s="4"/>
       <c r="E370" s="4"/>
@@ -10232,8 +11806,12 @@
       <c r="T370" s="4"/>
       <c r="U370" s="4"/>
       <c r="V370" s="4"/>
-    </row>
-    <row r="371" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W370" s="4"/>
+      <c r="X370" s="4"/>
+      <c r="Y370" s="4"/>
+      <c r="Z370" s="4"/>
+    </row>
+    <row r="371" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C371" s="4"/>
       <c r="D371" s="4"/>
       <c r="E371" s="4"/>
@@ -10254,8 +11832,12 @@
       <c r="T371" s="4"/>
       <c r="U371" s="4"/>
       <c r="V371" s="4"/>
-    </row>
-    <row r="372" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W371" s="4"/>
+      <c r="X371" s="4"/>
+      <c r="Y371" s="4"/>
+      <c r="Z371" s="4"/>
+    </row>
+    <row r="372" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C372" s="4"/>
       <c r="D372" s="4"/>
       <c r="E372" s="4"/>
@@ -10276,8 +11858,12 @@
       <c r="T372" s="4"/>
       <c r="U372" s="4"/>
       <c r="V372" s="4"/>
-    </row>
-    <row r="373" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W372" s="4"/>
+      <c r="X372" s="4"/>
+      <c r="Y372" s="4"/>
+      <c r="Z372" s="4"/>
+    </row>
+    <row r="373" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C373" s="4"/>
       <c r="D373" s="4"/>
       <c r="E373" s="4"/>
@@ -10298,8 +11884,12 @@
       <c r="T373" s="4"/>
       <c r="U373" s="4"/>
       <c r="V373" s="4"/>
-    </row>
-    <row r="374" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W373" s="4"/>
+      <c r="X373" s="4"/>
+      <c r="Y373" s="4"/>
+      <c r="Z373" s="4"/>
+    </row>
+    <row r="374" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C374" s="4"/>
       <c r="D374" s="4"/>
       <c r="E374" s="4"/>
@@ -10320,8 +11910,12 @@
       <c r="T374" s="4"/>
       <c r="U374" s="4"/>
       <c r="V374" s="4"/>
-    </row>
-    <row r="375" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W374" s="4"/>
+      <c r="X374" s="4"/>
+      <c r="Y374" s="4"/>
+      <c r="Z374" s="4"/>
+    </row>
+    <row r="375" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C375" s="4"/>
       <c r="D375" s="4"/>
       <c r="E375" s="4"/>
@@ -10342,8 +11936,12 @@
       <c r="T375" s="4"/>
       <c r="U375" s="4"/>
       <c r="V375" s="4"/>
-    </row>
-    <row r="376" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W375" s="4"/>
+      <c r="X375" s="4"/>
+      <c r="Y375" s="4"/>
+      <c r="Z375" s="4"/>
+    </row>
+    <row r="376" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C376" s="4"/>
       <c r="D376" s="4"/>
       <c r="E376" s="4"/>
@@ -10364,8 +11962,12 @@
       <c r="T376" s="4"/>
       <c r="U376" s="4"/>
       <c r="V376" s="4"/>
-    </row>
-    <row r="377" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W376" s="4"/>
+      <c r="X376" s="4"/>
+      <c r="Y376" s="4"/>
+      <c r="Z376" s="4"/>
+    </row>
+    <row r="377" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C377" s="4"/>
       <c r="D377" s="4"/>
       <c r="E377" s="4"/>
@@ -10386,8 +11988,12 @@
       <c r="T377" s="4"/>
       <c r="U377" s="4"/>
       <c r="V377" s="4"/>
-    </row>
-    <row r="378" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W377" s="4"/>
+      <c r="X377" s="4"/>
+      <c r="Y377" s="4"/>
+      <c r="Z377" s="4"/>
+    </row>
+    <row r="378" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C378" s="4"/>
       <c r="D378" s="4"/>
       <c r="E378" s="4"/>
@@ -10408,8 +12014,12 @@
       <c r="T378" s="4"/>
       <c r="U378" s="4"/>
       <c r="V378" s="4"/>
-    </row>
-    <row r="379" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W378" s="4"/>
+      <c r="X378" s="4"/>
+      <c r="Y378" s="4"/>
+      <c r="Z378" s="4"/>
+    </row>
+    <row r="379" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C379" s="4"/>
       <c r="D379" s="4"/>
       <c r="E379" s="4"/>
@@ -10430,8 +12040,12 @@
       <c r="T379" s="4"/>
       <c r="U379" s="4"/>
       <c r="V379" s="4"/>
-    </row>
-    <row r="380" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W379" s="4"/>
+      <c r="X379" s="4"/>
+      <c r="Y379" s="4"/>
+      <c r="Z379" s="4"/>
+    </row>
+    <row r="380" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C380" s="4"/>
       <c r="D380" s="4"/>
       <c r="E380" s="4"/>
@@ -10452,8 +12066,12 @@
       <c r="T380" s="4"/>
       <c r="U380" s="4"/>
       <c r="V380" s="4"/>
-    </row>
-    <row r="381" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W380" s="4"/>
+      <c r="X380" s="4"/>
+      <c r="Y380" s="4"/>
+      <c r="Z380" s="4"/>
+    </row>
+    <row r="381" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C381" s="4"/>
       <c r="D381" s="4"/>
       <c r="E381" s="4"/>
@@ -10474,8 +12092,12 @@
       <c r="T381" s="4"/>
       <c r="U381" s="4"/>
       <c r="V381" s="4"/>
-    </row>
-    <row r="382" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W381" s="4"/>
+      <c r="X381" s="4"/>
+      <c r="Y381" s="4"/>
+      <c r="Z381" s="4"/>
+    </row>
+    <row r="382" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C382" s="4"/>
       <c r="D382" s="4"/>
       <c r="E382" s="4"/>
@@ -10496,8 +12118,12 @@
       <c r="T382" s="4"/>
       <c r="U382" s="4"/>
       <c r="V382" s="4"/>
-    </row>
-    <row r="383" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W382" s="4"/>
+      <c r="X382" s="4"/>
+      <c r="Y382" s="4"/>
+      <c r="Z382" s="4"/>
+    </row>
+    <row r="383" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C383" s="4"/>
       <c r="D383" s="4"/>
       <c r="E383" s="4"/>
@@ -10518,8 +12144,12 @@
       <c r="T383" s="4"/>
       <c r="U383" s="4"/>
       <c r="V383" s="4"/>
-    </row>
-    <row r="384" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W383" s="4"/>
+      <c r="X383" s="4"/>
+      <c r="Y383" s="4"/>
+      <c r="Z383" s="4"/>
+    </row>
+    <row r="384" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C384" s="4"/>
       <c r="D384" s="4"/>
       <c r="E384" s="4"/>
@@ -10540,8 +12170,12 @@
       <c r="T384" s="4"/>
       <c r="U384" s="4"/>
       <c r="V384" s="4"/>
-    </row>
-    <row r="385" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W384" s="4"/>
+      <c r="X384" s="4"/>
+      <c r="Y384" s="4"/>
+      <c r="Z384" s="4"/>
+    </row>
+    <row r="385" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C385" s="4"/>
       <c r="D385" s="4"/>
       <c r="E385" s="4"/>
@@ -10562,8 +12196,12 @@
       <c r="T385" s="4"/>
       <c r="U385" s="4"/>
       <c r="V385" s="4"/>
-    </row>
-    <row r="386" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W385" s="4"/>
+      <c r="X385" s="4"/>
+      <c r="Y385" s="4"/>
+      <c r="Z385" s="4"/>
+    </row>
+    <row r="386" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C386" s="4"/>
       <c r="D386" s="4"/>
       <c r="E386" s="4"/>
@@ -10584,8 +12222,12 @@
       <c r="T386" s="4"/>
       <c r="U386" s="4"/>
       <c r="V386" s="4"/>
-    </row>
-    <row r="387" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W386" s="4"/>
+      <c r="X386" s="4"/>
+      <c r="Y386" s="4"/>
+      <c r="Z386" s="4"/>
+    </row>
+    <row r="387" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C387" s="4"/>
       <c r="D387" s="4"/>
       <c r="E387" s="4"/>
@@ -10606,8 +12248,12 @@
       <c r="T387" s="4"/>
       <c r="U387" s="4"/>
       <c r="V387" s="4"/>
-    </row>
-    <row r="388" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W387" s="4"/>
+      <c r="X387" s="4"/>
+      <c r="Y387" s="4"/>
+      <c r="Z387" s="4"/>
+    </row>
+    <row r="388" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C388" s="4"/>
       <c r="D388" s="4"/>
       <c r="E388" s="4"/>
@@ -10628,8 +12274,12 @@
       <c r="T388" s="4"/>
       <c r="U388" s="4"/>
       <c r="V388" s="4"/>
-    </row>
-    <row r="389" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W388" s="4"/>
+      <c r="X388" s="4"/>
+      <c r="Y388" s="4"/>
+      <c r="Z388" s="4"/>
+    </row>
+    <row r="389" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C389" s="4"/>
       <c r="D389" s="4"/>
       <c r="E389" s="4"/>
@@ -10650,8 +12300,12 @@
       <c r="T389" s="4"/>
       <c r="U389" s="4"/>
       <c r="V389" s="4"/>
-    </row>
-    <row r="390" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W389" s="4"/>
+      <c r="X389" s="4"/>
+      <c r="Y389" s="4"/>
+      <c r="Z389" s="4"/>
+    </row>
+    <row r="390" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C390" s="4"/>
       <c r="D390" s="4"/>
       <c r="E390" s="4"/>
@@ -10672,8 +12326,12 @@
       <c r="T390" s="4"/>
       <c r="U390" s="4"/>
       <c r="V390" s="4"/>
-    </row>
-    <row r="391" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W390" s="4"/>
+      <c r="X390" s="4"/>
+      <c r="Y390" s="4"/>
+      <c r="Z390" s="4"/>
+    </row>
+    <row r="391" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C391" s="4"/>
       <c r="D391" s="4"/>
       <c r="E391" s="4"/>
@@ -10694,8 +12352,12 @@
       <c r="T391" s="4"/>
       <c r="U391" s="4"/>
       <c r="V391" s="4"/>
-    </row>
-    <row r="392" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W391" s="4"/>
+      <c r="X391" s="4"/>
+      <c r="Y391" s="4"/>
+      <c r="Z391" s="4"/>
+    </row>
+    <row r="392" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C392" s="4"/>
       <c r="D392" s="4"/>
       <c r="E392" s="4"/>
@@ -10716,8 +12378,12 @@
       <c r="T392" s="4"/>
       <c r="U392" s="4"/>
       <c r="V392" s="4"/>
-    </row>
-    <row r="393" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W392" s="4"/>
+      <c r="X392" s="4"/>
+      <c r="Y392" s="4"/>
+      <c r="Z392" s="4"/>
+    </row>
+    <row r="393" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C393" s="4"/>
       <c r="D393" s="4"/>
       <c r="E393" s="4"/>
@@ -10738,8 +12404,12 @@
       <c r="T393" s="4"/>
       <c r="U393" s="4"/>
       <c r="V393" s="4"/>
-    </row>
-    <row r="394" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W393" s="4"/>
+      <c r="X393" s="4"/>
+      <c r="Y393" s="4"/>
+      <c r="Z393" s="4"/>
+    </row>
+    <row r="394" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C394" s="4"/>
       <c r="D394" s="4"/>
       <c r="E394" s="4"/>
@@ -10760,8 +12430,12 @@
       <c r="T394" s="4"/>
       <c r="U394" s="4"/>
       <c r="V394" s="4"/>
-    </row>
-    <row r="395" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W394" s="4"/>
+      <c r="X394" s="4"/>
+      <c r="Y394" s="4"/>
+      <c r="Z394" s="4"/>
+    </row>
+    <row r="395" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C395" s="4"/>
       <c r="D395" s="4"/>
       <c r="E395" s="4"/>
@@ -10782,8 +12456,12 @@
       <c r="T395" s="4"/>
       <c r="U395" s="4"/>
       <c r="V395" s="4"/>
-    </row>
-    <row r="396" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W395" s="4"/>
+      <c r="X395" s="4"/>
+      <c r="Y395" s="4"/>
+      <c r="Z395" s="4"/>
+    </row>
+    <row r="396" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C396" s="4"/>
       <c r="D396" s="4"/>
       <c r="E396" s="4"/>
@@ -10804,8 +12482,12 @@
       <c r="T396" s="4"/>
       <c r="U396" s="4"/>
       <c r="V396" s="4"/>
-    </row>
-    <row r="397" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W396" s="4"/>
+      <c r="X396" s="4"/>
+      <c r="Y396" s="4"/>
+      <c r="Z396" s="4"/>
+    </row>
+    <row r="397" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C397" s="4"/>
       <c r="D397" s="4"/>
       <c r="E397" s="4"/>
@@ -10826,8 +12508,12 @@
       <c r="T397" s="4"/>
       <c r="U397" s="4"/>
       <c r="V397" s="4"/>
-    </row>
-    <row r="398" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W397" s="4"/>
+      <c r="X397" s="4"/>
+      <c r="Y397" s="4"/>
+      <c r="Z397" s="4"/>
+    </row>
+    <row r="398" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C398" s="4"/>
       <c r="D398" s="4"/>
       <c r="E398" s="4"/>
@@ -10848,8 +12534,12 @@
       <c r="T398" s="4"/>
       <c r="U398" s="4"/>
       <c r="V398" s="4"/>
-    </row>
-    <row r="399" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W398" s="4"/>
+      <c r="X398" s="4"/>
+      <c r="Y398" s="4"/>
+      <c r="Z398" s="4"/>
+    </row>
+    <row r="399" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C399" s="4"/>
       <c r="D399" s="4"/>
       <c r="E399" s="4"/>
@@ -10870,8 +12560,12 @@
       <c r="T399" s="4"/>
       <c r="U399" s="4"/>
       <c r="V399" s="4"/>
-    </row>
-    <row r="400" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W399" s="4"/>
+      <c r="X399" s="4"/>
+      <c r="Y399" s="4"/>
+      <c r="Z399" s="4"/>
+    </row>
+    <row r="400" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C400" s="4"/>
       <c r="D400" s="4"/>
       <c r="E400" s="4"/>
@@ -10892,8 +12586,12 @@
       <c r="T400" s="4"/>
       <c r="U400" s="4"/>
       <c r="V400" s="4"/>
-    </row>
-    <row r="401" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W400" s="4"/>
+      <c r="X400" s="4"/>
+      <c r="Y400" s="4"/>
+      <c r="Z400" s="4"/>
+    </row>
+    <row r="401" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C401" s="4"/>
       <c r="D401" s="4"/>
       <c r="E401" s="4"/>
@@ -10914,8 +12612,12 @@
       <c r="T401" s="4"/>
       <c r="U401" s="4"/>
       <c r="V401" s="4"/>
-    </row>
-    <row r="402" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W401" s="4"/>
+      <c r="X401" s="4"/>
+      <c r="Y401" s="4"/>
+      <c r="Z401" s="4"/>
+    </row>
+    <row r="402" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C402" s="4"/>
       <c r="D402" s="4"/>
       <c r="E402" s="4"/>
@@ -10936,8 +12638,12 @@
       <c r="T402" s="4"/>
       <c r="U402" s="4"/>
       <c r="V402" s="4"/>
-    </row>
-    <row r="403" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W402" s="4"/>
+      <c r="X402" s="4"/>
+      <c r="Y402" s="4"/>
+      <c r="Z402" s="4"/>
+    </row>
+    <row r="403" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C403" s="4"/>
       <c r="D403" s="4"/>
       <c r="E403" s="4"/>
@@ -10958,8 +12664,12 @@
       <c r="T403" s="4"/>
       <c r="U403" s="4"/>
       <c r="V403" s="4"/>
-    </row>
-    <row r="404" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W403" s="4"/>
+      <c r="X403" s="4"/>
+      <c r="Y403" s="4"/>
+      <c r="Z403" s="4"/>
+    </row>
+    <row r="404" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C404" s="4"/>
       <c r="D404" s="4"/>
       <c r="E404" s="4"/>
@@ -10980,8 +12690,12 @@
       <c r="T404" s="4"/>
       <c r="U404" s="4"/>
       <c r="V404" s="4"/>
-    </row>
-    <row r="405" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W404" s="4"/>
+      <c r="X404" s="4"/>
+      <c r="Y404" s="4"/>
+      <c r="Z404" s="4"/>
+    </row>
+    <row r="405" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C405" s="4"/>
       <c r="D405" s="4"/>
       <c r="E405" s="4"/>
@@ -11002,8 +12716,12 @@
       <c r="T405" s="4"/>
       <c r="U405" s="4"/>
       <c r="V405" s="4"/>
-    </row>
-    <row r="406" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W405" s="4"/>
+      <c r="X405" s="4"/>
+      <c r="Y405" s="4"/>
+      <c r="Z405" s="4"/>
+    </row>
+    <row r="406" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C406" s="4"/>
       <c r="D406" s="4"/>
       <c r="E406" s="4"/>
@@ -11024,8 +12742,12 @@
       <c r="T406" s="4"/>
       <c r="U406" s="4"/>
       <c r="V406" s="4"/>
-    </row>
-    <row r="407" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W406" s="4"/>
+      <c r="X406" s="4"/>
+      <c r="Y406" s="4"/>
+      <c r="Z406" s="4"/>
+    </row>
+    <row r="407" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C407" s="4"/>
       <c r="D407" s="4"/>
       <c r="E407" s="4"/>
@@ -11046,8 +12768,12 @@
       <c r="T407" s="4"/>
       <c r="U407" s="4"/>
       <c r="V407" s="4"/>
-    </row>
-    <row r="408" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W407" s="4"/>
+      <c r="X407" s="4"/>
+      <c r="Y407" s="4"/>
+      <c r="Z407" s="4"/>
+    </row>
+    <row r="408" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C408" s="4"/>
       <c r="D408" s="4"/>
       <c r="E408" s="4"/>
@@ -11068,8 +12794,12 @@
       <c r="T408" s="4"/>
       <c r="U408" s="4"/>
       <c r="V408" s="4"/>
-    </row>
-    <row r="409" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W408" s="4"/>
+      <c r="X408" s="4"/>
+      <c r="Y408" s="4"/>
+      <c r="Z408" s="4"/>
+    </row>
+    <row r="409" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C409" s="4"/>
       <c r="D409" s="4"/>
       <c r="E409" s="4"/>
@@ -11090,8 +12820,12 @@
       <c r="T409" s="4"/>
       <c r="U409" s="4"/>
       <c r="V409" s="4"/>
-    </row>
-    <row r="410" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W409" s="4"/>
+      <c r="X409" s="4"/>
+      <c r="Y409" s="4"/>
+      <c r="Z409" s="4"/>
+    </row>
+    <row r="410" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C410" s="4"/>
       <c r="D410" s="4"/>
       <c r="E410" s="4"/>
@@ -11112,8 +12846,12 @@
       <c r="T410" s="4"/>
       <c r="U410" s="4"/>
       <c r="V410" s="4"/>
-    </row>
-    <row r="411" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W410" s="4"/>
+      <c r="X410" s="4"/>
+      <c r="Y410" s="4"/>
+      <c r="Z410" s="4"/>
+    </row>
+    <row r="411" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C411" s="4"/>
       <c r="D411" s="4"/>
       <c r="E411" s="4"/>
@@ -11134,8 +12872,12 @@
       <c r="T411" s="4"/>
       <c r="U411" s="4"/>
       <c r="V411" s="4"/>
-    </row>
-    <row r="412" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W411" s="4"/>
+      <c r="X411" s="4"/>
+      <c r="Y411" s="4"/>
+      <c r="Z411" s="4"/>
+    </row>
+    <row r="412" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C412" s="4"/>
       <c r="D412" s="4"/>
       <c r="E412" s="4"/>
@@ -11156,8 +12898,12 @@
       <c r="T412" s="4"/>
       <c r="U412" s="4"/>
       <c r="V412" s="4"/>
-    </row>
-    <row r="413" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W412" s="4"/>
+      <c r="X412" s="4"/>
+      <c r="Y412" s="4"/>
+      <c r="Z412" s="4"/>
+    </row>
+    <row r="413" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C413" s="4"/>
       <c r="D413" s="4"/>
       <c r="E413" s="4"/>
@@ -11178,8 +12924,12 @@
       <c r="T413" s="4"/>
       <c r="U413" s="4"/>
       <c r="V413" s="4"/>
-    </row>
-    <row r="414" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W413" s="4"/>
+      <c r="X413" s="4"/>
+      <c r="Y413" s="4"/>
+      <c r="Z413" s="4"/>
+    </row>
+    <row r="414" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C414" s="4"/>
       <c r="D414" s="4"/>
       <c r="E414" s="4"/>
@@ -11200,8 +12950,12 @@
       <c r="T414" s="4"/>
       <c r="U414" s="4"/>
       <c r="V414" s="4"/>
-    </row>
-    <row r="415" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W414" s="4"/>
+      <c r="X414" s="4"/>
+      <c r="Y414" s="4"/>
+      <c r="Z414" s="4"/>
+    </row>
+    <row r="415" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C415" s="4"/>
       <c r="D415" s="4"/>
       <c r="E415" s="4"/>
@@ -11222,8 +12976,12 @@
       <c r="T415" s="4"/>
       <c r="U415" s="4"/>
       <c r="V415" s="4"/>
-    </row>
-    <row r="416" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W415" s="4"/>
+      <c r="X415" s="4"/>
+      <c r="Y415" s="4"/>
+      <c r="Z415" s="4"/>
+    </row>
+    <row r="416" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C416" s="4"/>
       <c r="D416" s="4"/>
       <c r="E416" s="4"/>
@@ -11244,8 +13002,12 @@
       <c r="T416" s="4"/>
       <c r="U416" s="4"/>
       <c r="V416" s="4"/>
-    </row>
-    <row r="417" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W416" s="4"/>
+      <c r="X416" s="4"/>
+      <c r="Y416" s="4"/>
+      <c r="Z416" s="4"/>
+    </row>
+    <row r="417" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C417" s="4"/>
       <c r="D417" s="4"/>
       <c r="E417" s="4"/>
@@ -11266,8 +13028,12 @@
       <c r="T417" s="4"/>
       <c r="U417" s="4"/>
       <c r="V417" s="4"/>
-    </row>
-    <row r="418" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W417" s="4"/>
+      <c r="X417" s="4"/>
+      <c r="Y417" s="4"/>
+      <c r="Z417" s="4"/>
+    </row>
+    <row r="418" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C418" s="4"/>
       <c r="D418" s="4"/>
       <c r="E418" s="4"/>
@@ -11288,8 +13054,12 @@
       <c r="T418" s="4"/>
       <c r="U418" s="4"/>
       <c r="V418" s="4"/>
-    </row>
-    <row r="419" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W418" s="4"/>
+      <c r="X418" s="4"/>
+      <c r="Y418" s="4"/>
+      <c r="Z418" s="4"/>
+    </row>
+    <row r="419" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C419" s="4"/>
       <c r="D419" s="4"/>
       <c r="E419" s="4"/>
@@ -11310,8 +13080,12 @@
       <c r="T419" s="4"/>
       <c r="U419" s="4"/>
       <c r="V419" s="4"/>
-    </row>
-    <row r="420" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W419" s="4"/>
+      <c r="X419" s="4"/>
+      <c r="Y419" s="4"/>
+      <c r="Z419" s="4"/>
+    </row>
+    <row r="420" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C420" s="4"/>
       <c r="D420" s="4"/>
       <c r="E420" s="4"/>
@@ -11332,8 +13106,12 @@
       <c r="T420" s="4"/>
       <c r="U420" s="4"/>
       <c r="V420" s="4"/>
-    </row>
-    <row r="421" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W420" s="4"/>
+      <c r="X420" s="4"/>
+      <c r="Y420" s="4"/>
+      <c r="Z420" s="4"/>
+    </row>
+    <row r="421" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C421" s="4"/>
       <c r="D421" s="4"/>
       <c r="E421" s="4"/>
@@ -11354,8 +13132,12 @@
       <c r="T421" s="4"/>
       <c r="U421" s="4"/>
       <c r="V421" s="4"/>
-    </row>
-    <row r="422" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W421" s="4"/>
+      <c r="X421" s="4"/>
+      <c r="Y421" s="4"/>
+      <c r="Z421" s="4"/>
+    </row>
+    <row r="422" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C422" s="4"/>
       <c r="D422" s="4"/>
       <c r="E422" s="4"/>
@@ -11376,8 +13158,12 @@
       <c r="T422" s="4"/>
       <c r="U422" s="4"/>
       <c r="V422" s="4"/>
-    </row>
-    <row r="423" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W422" s="4"/>
+      <c r="X422" s="4"/>
+      <c r="Y422" s="4"/>
+      <c r="Z422" s="4"/>
+    </row>
+    <row r="423" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C423" s="4"/>
       <c r="D423" s="4"/>
       <c r="E423" s="4"/>
@@ -11398,8 +13184,12 @@
       <c r="T423" s="4"/>
       <c r="U423" s="4"/>
       <c r="V423" s="4"/>
-    </row>
-    <row r="424" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W423" s="4"/>
+      <c r="X423" s="4"/>
+      <c r="Y423" s="4"/>
+      <c r="Z423" s="4"/>
+    </row>
+    <row r="424" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C424" s="4"/>
       <c r="D424" s="4"/>
       <c r="E424" s="4"/>
@@ -11420,8 +13210,12 @@
       <c r="T424" s="4"/>
       <c r="U424" s="4"/>
       <c r="V424" s="4"/>
-    </row>
-    <row r="425" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W424" s="4"/>
+      <c r="X424" s="4"/>
+      <c r="Y424" s="4"/>
+      <c r="Z424" s="4"/>
+    </row>
+    <row r="425" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C425" s="4"/>
       <c r="D425" s="4"/>
       <c r="E425" s="4"/>
@@ -11442,8 +13236,12 @@
       <c r="T425" s="4"/>
       <c r="U425" s="4"/>
       <c r="V425" s="4"/>
-    </row>
-    <row r="426" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W425" s="4"/>
+      <c r="X425" s="4"/>
+      <c r="Y425" s="4"/>
+      <c r="Z425" s="4"/>
+    </row>
+    <row r="426" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C426" s="4"/>
       <c r="D426" s="4"/>
       <c r="E426" s="4"/>
@@ -11464,8 +13262,12 @@
       <c r="T426" s="4"/>
       <c r="U426" s="4"/>
       <c r="V426" s="4"/>
-    </row>
-    <row r="427" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W426" s="4"/>
+      <c r="X426" s="4"/>
+      <c r="Y426" s="4"/>
+      <c r="Z426" s="4"/>
+    </row>
+    <row r="427" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C427" s="4"/>
       <c r="D427" s="4"/>
       <c r="E427" s="4"/>
@@ -11486,8 +13288,12 @@
       <c r="T427" s="4"/>
       <c r="U427" s="4"/>
       <c r="V427" s="4"/>
-    </row>
-    <row r="428" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W427" s="4"/>
+      <c r="X427" s="4"/>
+      <c r="Y427" s="4"/>
+      <c r="Z427" s="4"/>
+    </row>
+    <row r="428" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C428" s="4"/>
       <c r="D428" s="4"/>
       <c r="E428" s="4"/>
@@ -11508,8 +13314,12 @@
       <c r="T428" s="4"/>
       <c r="U428" s="4"/>
       <c r="V428" s="4"/>
-    </row>
-    <row r="429" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W428" s="4"/>
+      <c r="X428" s="4"/>
+      <c r="Y428" s="4"/>
+      <c r="Z428" s="4"/>
+    </row>
+    <row r="429" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C429" s="4"/>
       <c r="D429" s="4"/>
       <c r="E429" s="4"/>
@@ -11530,8 +13340,12 @@
       <c r="T429" s="4"/>
       <c r="U429" s="4"/>
       <c r="V429" s="4"/>
-    </row>
-    <row r="430" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W429" s="4"/>
+      <c r="X429" s="4"/>
+      <c r="Y429" s="4"/>
+      <c r="Z429" s="4"/>
+    </row>
+    <row r="430" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C430" s="4"/>
       <c r="D430" s="4"/>
       <c r="E430" s="4"/>
@@ -11552,8 +13366,12 @@
       <c r="T430" s="4"/>
       <c r="U430" s="4"/>
       <c r="V430" s="4"/>
-    </row>
-    <row r="431" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W430" s="4"/>
+      <c r="X430" s="4"/>
+      <c r="Y430" s="4"/>
+      <c r="Z430" s="4"/>
+    </row>
+    <row r="431" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C431" s="4"/>
       <c r="D431" s="4"/>
       <c r="E431" s="4"/>
@@ -11574,8 +13392,12 @@
       <c r="T431" s="4"/>
       <c r="U431" s="4"/>
       <c r="V431" s="4"/>
-    </row>
-    <row r="432" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W431" s="4"/>
+      <c r="X431" s="4"/>
+      <c r="Y431" s="4"/>
+      <c r="Z431" s="4"/>
+    </row>
+    <row r="432" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C432" s="4"/>
       <c r="D432" s="4"/>
       <c r="E432" s="4"/>
@@ -11596,8 +13418,12 @@
       <c r="T432" s="4"/>
       <c r="U432" s="4"/>
       <c r="V432" s="4"/>
-    </row>
-    <row r="433" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W432" s="4"/>
+      <c r="X432" s="4"/>
+      <c r="Y432" s="4"/>
+      <c r="Z432" s="4"/>
+    </row>
+    <row r="433" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C433" s="4"/>
       <c r="D433" s="4"/>
       <c r="E433" s="4"/>
@@ -11618,8 +13444,12 @@
       <c r="T433" s="4"/>
       <c r="U433" s="4"/>
       <c r="V433" s="4"/>
-    </row>
-    <row r="434" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W433" s="4"/>
+      <c r="X433" s="4"/>
+      <c r="Y433" s="4"/>
+      <c r="Z433" s="4"/>
+    </row>
+    <row r="434" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C434" s="4"/>
       <c r="D434" s="4"/>
       <c r="E434" s="4"/>
@@ -11640,8 +13470,12 @@
       <c r="T434" s="4"/>
       <c r="U434" s="4"/>
       <c r="V434" s="4"/>
-    </row>
-    <row r="435" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W434" s="4"/>
+      <c r="X434" s="4"/>
+      <c r="Y434" s="4"/>
+      <c r="Z434" s="4"/>
+    </row>
+    <row r="435" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C435" s="4"/>
       <c r="D435" s="4"/>
       <c r="E435" s="4"/>
@@ -11662,8 +13496,12 @@
       <c r="T435" s="4"/>
       <c r="U435" s="4"/>
       <c r="V435" s="4"/>
-    </row>
-    <row r="436" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W435" s="4"/>
+      <c r="X435" s="4"/>
+      <c r="Y435" s="4"/>
+      <c r="Z435" s="4"/>
+    </row>
+    <row r="436" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C436" s="4"/>
       <c r="D436" s="4"/>
       <c r="E436" s="4"/>
@@ -11684,8 +13522,12 @@
       <c r="T436" s="4"/>
       <c r="U436" s="4"/>
       <c r="V436" s="4"/>
-    </row>
-    <row r="437" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W436" s="4"/>
+      <c r="X436" s="4"/>
+      <c r="Y436" s="4"/>
+      <c r="Z436" s="4"/>
+    </row>
+    <row r="437" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C437" s="4"/>
       <c r="D437" s="4"/>
       <c r="E437" s="4"/>
@@ -11706,8 +13548,12 @@
       <c r="T437" s="4"/>
       <c r="U437" s="4"/>
       <c r="V437" s="4"/>
-    </row>
-    <row r="438" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W437" s="4"/>
+      <c r="X437" s="4"/>
+      <c r="Y437" s="4"/>
+      <c r="Z437" s="4"/>
+    </row>
+    <row r="438" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C438" s="4"/>
       <c r="D438" s="4"/>
       <c r="E438" s="4"/>
@@ -11728,8 +13574,12 @@
       <c r="T438" s="4"/>
       <c r="U438" s="4"/>
       <c r="V438" s="4"/>
-    </row>
-    <row r="439" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W438" s="4"/>
+      <c r="X438" s="4"/>
+      <c r="Y438" s="4"/>
+      <c r="Z438" s="4"/>
+    </row>
+    <row r="439" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C439" s="4"/>
       <c r="D439" s="4"/>
       <c r="E439" s="4"/>
@@ -11750,8 +13600,12 @@
       <c r="T439" s="4"/>
       <c r="U439" s="4"/>
       <c r="V439" s="4"/>
-    </row>
-    <row r="440" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W439" s="4"/>
+      <c r="X439" s="4"/>
+      <c r="Y439" s="4"/>
+      <c r="Z439" s="4"/>
+    </row>
+    <row r="440" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C440" s="4"/>
       <c r="D440" s="4"/>
       <c r="E440" s="4"/>
@@ -11772,8 +13626,12 @@
       <c r="T440" s="4"/>
       <c r="U440" s="4"/>
       <c r="V440" s="4"/>
-    </row>
-    <row r="441" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W440" s="4"/>
+      <c r="X440" s="4"/>
+      <c r="Y440" s="4"/>
+      <c r="Z440" s="4"/>
+    </row>
+    <row r="441" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C441" s="4"/>
       <c r="D441" s="4"/>
       <c r="E441" s="4"/>
@@ -11794,8 +13652,12 @@
       <c r="T441" s="4"/>
       <c r="U441" s="4"/>
       <c r="V441" s="4"/>
-    </row>
-    <row r="442" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W441" s="4"/>
+      <c r="X441" s="4"/>
+      <c r="Y441" s="4"/>
+      <c r="Z441" s="4"/>
+    </row>
+    <row r="442" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C442" s="4"/>
       <c r="D442" s="4"/>
       <c r="E442" s="4"/>
@@ -11816,8 +13678,12 @@
       <c r="T442" s="4"/>
       <c r="U442" s="4"/>
       <c r="V442" s="4"/>
-    </row>
-    <row r="443" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W442" s="4"/>
+      <c r="X442" s="4"/>
+      <c r="Y442" s="4"/>
+      <c r="Z442" s="4"/>
+    </row>
+    <row r="443" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C443" s="4"/>
       <c r="D443" s="4"/>
       <c r="E443" s="4"/>
@@ -11838,8 +13704,12 @@
       <c r="T443" s="4"/>
       <c r="U443" s="4"/>
       <c r="V443" s="4"/>
-    </row>
-    <row r="444" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W443" s="4"/>
+      <c r="X443" s="4"/>
+      <c r="Y443" s="4"/>
+      <c r="Z443" s="4"/>
+    </row>
+    <row r="444" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C444" s="4"/>
       <c r="D444" s="4"/>
       <c r="E444" s="4"/>
@@ -11860,8 +13730,12 @@
       <c r="T444" s="4"/>
       <c r="U444" s="4"/>
       <c r="V444" s="4"/>
-    </row>
-    <row r="445" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W444" s="4"/>
+      <c r="X444" s="4"/>
+      <c r="Y444" s="4"/>
+      <c r="Z444" s="4"/>
+    </row>
+    <row r="445" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C445" s="4"/>
       <c r="D445" s="4"/>
       <c r="E445" s="4"/>
@@ -11882,8 +13756,12 @@
       <c r="T445" s="4"/>
       <c r="U445" s="4"/>
       <c r="V445" s="4"/>
-    </row>
-    <row r="446" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W445" s="4"/>
+      <c r="X445" s="4"/>
+      <c r="Y445" s="4"/>
+      <c r="Z445" s="4"/>
+    </row>
+    <row r="446" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C446" s="4"/>
       <c r="D446" s="4"/>
       <c r="E446" s="4"/>
@@ -11904,8 +13782,12 @@
       <c r="T446" s="4"/>
       <c r="U446" s="4"/>
       <c r="V446" s="4"/>
-    </row>
-    <row r="447" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W446" s="4"/>
+      <c r="X446" s="4"/>
+      <c r="Y446" s="4"/>
+      <c r="Z446" s="4"/>
+    </row>
+    <row r="447" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C447" s="4"/>
       <c r="D447" s="4"/>
       <c r="E447" s="4"/>
@@ -11926,8 +13808,12 @@
       <c r="T447" s="4"/>
       <c r="U447" s="4"/>
       <c r="V447" s="4"/>
-    </row>
-    <row r="448" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W447" s="4"/>
+      <c r="X447" s="4"/>
+      <c r="Y447" s="4"/>
+      <c r="Z447" s="4"/>
+    </row>
+    <row r="448" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C448" s="4"/>
       <c r="D448" s="4"/>
       <c r="E448" s="4"/>
@@ -11948,8 +13834,12 @@
       <c r="T448" s="4"/>
       <c r="U448" s="4"/>
       <c r="V448" s="4"/>
-    </row>
-    <row r="449" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W448" s="4"/>
+      <c r="X448" s="4"/>
+      <c r="Y448" s="4"/>
+      <c r="Z448" s="4"/>
+    </row>
+    <row r="449" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C449" s="4"/>
       <c r="D449" s="4"/>
       <c r="E449" s="4"/>
@@ -11970,8 +13860,12 @@
       <c r="T449" s="4"/>
       <c r="U449" s="4"/>
       <c r="V449" s="4"/>
-    </row>
-    <row r="450" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W449" s="4"/>
+      <c r="X449" s="4"/>
+      <c r="Y449" s="4"/>
+      <c r="Z449" s="4"/>
+    </row>
+    <row r="450" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C450" s="4"/>
       <c r="D450" s="4"/>
       <c r="E450" s="4"/>
@@ -11992,8 +13886,12 @@
       <c r="T450" s="4"/>
       <c r="U450" s="4"/>
       <c r="V450" s="4"/>
-    </row>
-    <row r="451" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W450" s="4"/>
+      <c r="X450" s="4"/>
+      <c r="Y450" s="4"/>
+      <c r="Z450" s="4"/>
+    </row>
+    <row r="451" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C451" s="4"/>
       <c r="D451" s="4"/>
       <c r="E451" s="4"/>
@@ -12014,8 +13912,12 @@
       <c r="T451" s="4"/>
       <c r="U451" s="4"/>
       <c r="V451" s="4"/>
-    </row>
-    <row r="452" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W451" s="4"/>
+      <c r="X451" s="4"/>
+      <c r="Y451" s="4"/>
+      <c r="Z451" s="4"/>
+    </row>
+    <row r="452" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C452" s="4"/>
       <c r="D452" s="4"/>
       <c r="E452" s="4"/>
@@ -12036,8 +13938,12 @@
       <c r="T452" s="4"/>
       <c r="U452" s="4"/>
       <c r="V452" s="4"/>
-    </row>
-    <row r="453" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W452" s="4"/>
+      <c r="X452" s="4"/>
+      <c r="Y452" s="4"/>
+      <c r="Z452" s="4"/>
+    </row>
+    <row r="453" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C453" s="4"/>
       <c r="D453" s="4"/>
       <c r="E453" s="4"/>
@@ -12058,8 +13964,12 @@
       <c r="T453" s="4"/>
       <c r="U453" s="4"/>
       <c r="V453" s="4"/>
-    </row>
-    <row r="454" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W453" s="4"/>
+      <c r="X453" s="4"/>
+      <c r="Y453" s="4"/>
+      <c r="Z453" s="4"/>
+    </row>
+    <row r="454" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C454" s="4"/>
       <c r="D454" s="4"/>
       <c r="E454" s="4"/>
@@ -12080,8 +13990,12 @@
       <c r="T454" s="4"/>
       <c r="U454" s="4"/>
       <c r="V454" s="4"/>
-    </row>
-    <row r="455" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W454" s="4"/>
+      <c r="X454" s="4"/>
+      <c r="Y454" s="4"/>
+      <c r="Z454" s="4"/>
+    </row>
+    <row r="455" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C455" s="4"/>
       <c r="D455" s="4"/>
       <c r="E455" s="4"/>
@@ -12102,8 +14016,12 @@
       <c r="T455" s="4"/>
       <c r="U455" s="4"/>
       <c r="V455" s="4"/>
-    </row>
-    <row r="456" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W455" s="4"/>
+      <c r="X455" s="4"/>
+      <c r="Y455" s="4"/>
+      <c r="Z455" s="4"/>
+    </row>
+    <row r="456" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C456" s="4"/>
       <c r="D456" s="4"/>
       <c r="E456" s="4"/>
@@ -12124,8 +14042,12 @@
       <c r="T456" s="4"/>
       <c r="U456" s="4"/>
       <c r="V456" s="4"/>
-    </row>
-    <row r="457" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W456" s="4"/>
+      <c r="X456" s="4"/>
+      <c r="Y456" s="4"/>
+      <c r="Z456" s="4"/>
+    </row>
+    <row r="457" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C457" s="4"/>
       <c r="D457" s="4"/>
       <c r="E457" s="4"/>
@@ -12146,8 +14068,12 @@
       <c r="T457" s="4"/>
       <c r="U457" s="4"/>
       <c r="V457" s="4"/>
-    </row>
-    <row r="458" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W457" s="4"/>
+      <c r="X457" s="4"/>
+      <c r="Y457" s="4"/>
+      <c r="Z457" s="4"/>
+    </row>
+    <row r="458" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C458" s="4"/>
       <c r="D458" s="4"/>
       <c r="E458" s="4"/>
@@ -12168,8 +14094,12 @@
       <c r="T458" s="4"/>
       <c r="U458" s="4"/>
       <c r="V458" s="4"/>
-    </row>
-    <row r="459" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W458" s="4"/>
+      <c r="X458" s="4"/>
+      <c r="Y458" s="4"/>
+      <c r="Z458" s="4"/>
+    </row>
+    <row r="459" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C459" s="4"/>
       <c r="D459" s="4"/>
       <c r="E459" s="4"/>
@@ -12190,8 +14120,12 @@
       <c r="T459" s="4"/>
       <c r="U459" s="4"/>
       <c r="V459" s="4"/>
-    </row>
-    <row r="460" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W459" s="4"/>
+      <c r="X459" s="4"/>
+      <c r="Y459" s="4"/>
+      <c r="Z459" s="4"/>
+    </row>
+    <row r="460" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C460" s="4"/>
       <c r="D460" s="4"/>
       <c r="E460" s="4"/>
@@ -12212,8 +14146,12 @@
       <c r="T460" s="4"/>
       <c r="U460" s="4"/>
       <c r="V460" s="4"/>
-    </row>
-    <row r="461" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W460" s="4"/>
+      <c r="X460" s="4"/>
+      <c r="Y460" s="4"/>
+      <c r="Z460" s="4"/>
+    </row>
+    <row r="461" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C461" s="4"/>
       <c r="D461" s="4"/>
       <c r="E461" s="4"/>
@@ -12234,8 +14172,12 @@
       <c r="T461" s="4"/>
       <c r="U461" s="4"/>
       <c r="V461" s="4"/>
-    </row>
-    <row r="462" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W461" s="4"/>
+      <c r="X461" s="4"/>
+      <c r="Y461" s="4"/>
+      <c r="Z461" s="4"/>
+    </row>
+    <row r="462" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C462" s="4"/>
       <c r="D462" s="4"/>
       <c r="E462" s="4"/>
@@ -12256,8 +14198,12 @@
       <c r="T462" s="4"/>
       <c r="U462" s="4"/>
       <c r="V462" s="4"/>
-    </row>
-    <row r="463" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W462" s="4"/>
+      <c r="X462" s="4"/>
+      <c r="Y462" s="4"/>
+      <c r="Z462" s="4"/>
+    </row>
+    <row r="463" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C463" s="4"/>
       <c r="D463" s="4"/>
       <c r="E463" s="4"/>
@@ -12278,8 +14224,12 @@
       <c r="T463" s="4"/>
       <c r="U463" s="4"/>
       <c r="V463" s="4"/>
-    </row>
-    <row r="464" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W463" s="4"/>
+      <c r="X463" s="4"/>
+      <c r="Y463" s="4"/>
+      <c r="Z463" s="4"/>
+    </row>
+    <row r="464" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C464" s="4"/>
       <c r="D464" s="4"/>
       <c r="E464" s="4"/>
@@ -12300,8 +14250,12 @@
       <c r="T464" s="4"/>
       <c r="U464" s="4"/>
       <c r="V464" s="4"/>
-    </row>
-    <row r="465" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W464" s="4"/>
+      <c r="X464" s="4"/>
+      <c r="Y464" s="4"/>
+      <c r="Z464" s="4"/>
+    </row>
+    <row r="465" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C465" s="4"/>
       <c r="D465" s="4"/>
       <c r="E465" s="4"/>
@@ -12322,8 +14276,12 @@
       <c r="T465" s="4"/>
       <c r="U465" s="4"/>
       <c r="V465" s="4"/>
-    </row>
-    <row r="466" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W465" s="4"/>
+      <c r="X465" s="4"/>
+      <c r="Y465" s="4"/>
+      <c r="Z465" s="4"/>
+    </row>
+    <row r="466" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C466" s="4"/>
       <c r="D466" s="4"/>
       <c r="E466" s="4"/>
@@ -12344,8 +14302,12 @@
       <c r="T466" s="4"/>
       <c r="U466" s="4"/>
       <c r="V466" s="4"/>
-    </row>
-    <row r="467" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W466" s="4"/>
+      <c r="X466" s="4"/>
+      <c r="Y466" s="4"/>
+      <c r="Z466" s="4"/>
+    </row>
+    <row r="467" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C467" s="4"/>
       <c r="D467" s="4"/>
       <c r="E467" s="4"/>
@@ -12366,8 +14328,12 @@
       <c r="T467" s="4"/>
       <c r="U467" s="4"/>
       <c r="V467" s="4"/>
-    </row>
-    <row r="468" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W467" s="4"/>
+      <c r="X467" s="4"/>
+      <c r="Y467" s="4"/>
+      <c r="Z467" s="4"/>
+    </row>
+    <row r="468" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C468" s="4"/>
       <c r="D468" s="4"/>
       <c r="E468" s="4"/>
@@ -12388,8 +14354,12 @@
       <c r="T468" s="4"/>
       <c r="U468" s="4"/>
       <c r="V468" s="4"/>
-    </row>
-    <row r="469" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W468" s="4"/>
+      <c r="X468" s="4"/>
+      <c r="Y468" s="4"/>
+      <c r="Z468" s="4"/>
+    </row>
+    <row r="469" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C469" s="4"/>
       <c r="D469" s="4"/>
       <c r="E469" s="4"/>
@@ -12410,8 +14380,12 @@
       <c r="T469" s="4"/>
       <c r="U469" s="4"/>
       <c r="V469" s="4"/>
-    </row>
-    <row r="470" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W469" s="4"/>
+      <c r="X469" s="4"/>
+      <c r="Y469" s="4"/>
+      <c r="Z469" s="4"/>
+    </row>
+    <row r="470" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C470" s="4"/>
       <c r="D470" s="4"/>
       <c r="E470" s="4"/>
@@ -12432,8 +14406,12 @@
       <c r="T470" s="4"/>
       <c r="U470" s="4"/>
       <c r="V470" s="4"/>
-    </row>
-    <row r="471" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W470" s="4"/>
+      <c r="X470" s="4"/>
+      <c r="Y470" s="4"/>
+      <c r="Z470" s="4"/>
+    </row>
+    <row r="471" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C471" s="4"/>
       <c r="D471" s="4"/>
       <c r="E471" s="4"/>
@@ -12454,8 +14432,12 @@
       <c r="T471" s="4"/>
       <c r="U471" s="4"/>
       <c r="V471" s="4"/>
-    </row>
-    <row r="472" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W471" s="4"/>
+      <c r="X471" s="4"/>
+      <c r="Y471" s="4"/>
+      <c r="Z471" s="4"/>
+    </row>
+    <row r="472" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C472" s="4"/>
       <c r="D472" s="4"/>
       <c r="E472" s="4"/>
@@ -12476,8 +14458,12 @@
       <c r="T472" s="4"/>
       <c r="U472" s="4"/>
       <c r="V472" s="4"/>
-    </row>
-    <row r="473" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W472" s="4"/>
+      <c r="X472" s="4"/>
+      <c r="Y472" s="4"/>
+      <c r="Z472" s="4"/>
+    </row>
+    <row r="473" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C473" s="4"/>
       <c r="D473" s="4"/>
       <c r="E473" s="4"/>
@@ -12498,8 +14484,12 @@
       <c r="T473" s="4"/>
       <c r="U473" s="4"/>
       <c r="V473" s="4"/>
-    </row>
-    <row r="474" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W473" s="4"/>
+      <c r="X473" s="4"/>
+      <c r="Y473" s="4"/>
+      <c r="Z473" s="4"/>
+    </row>
+    <row r="474" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C474" s="4"/>
       <c r="D474" s="4"/>
       <c r="E474" s="4"/>
@@ -12520,8 +14510,12 @@
       <c r="T474" s="4"/>
       <c r="U474" s="4"/>
       <c r="V474" s="4"/>
-    </row>
-    <row r="475" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W474" s="4"/>
+      <c r="X474" s="4"/>
+      <c r="Y474" s="4"/>
+      <c r="Z474" s="4"/>
+    </row>
+    <row r="475" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C475" s="4"/>
       <c r="D475" s="4"/>
       <c r="E475" s="4"/>
@@ -12542,8 +14536,12 @@
       <c r="T475" s="4"/>
       <c r="U475" s="4"/>
       <c r="V475" s="4"/>
-    </row>
-    <row r="476" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W475" s="4"/>
+      <c r="X475" s="4"/>
+      <c r="Y475" s="4"/>
+      <c r="Z475" s="4"/>
+    </row>
+    <row r="476" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C476" s="4"/>
       <c r="D476" s="4"/>
       <c r="E476" s="4"/>
@@ -12564,8 +14562,12 @@
       <c r="T476" s="4"/>
       <c r="U476" s="4"/>
       <c r="V476" s="4"/>
-    </row>
-    <row r="477" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W476" s="4"/>
+      <c r="X476" s="4"/>
+      <c r="Y476" s="4"/>
+      <c r="Z476" s="4"/>
+    </row>
+    <row r="477" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C477" s="4"/>
       <c r="D477" s="4"/>
       <c r="E477" s="4"/>
@@ -12586,8 +14588,12 @@
       <c r="T477" s="4"/>
       <c r="U477" s="4"/>
       <c r="V477" s="4"/>
-    </row>
-    <row r="478" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W477" s="4"/>
+      <c r="X477" s="4"/>
+      <c r="Y477" s="4"/>
+      <c r="Z477" s="4"/>
+    </row>
+    <row r="478" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C478" s="4"/>
       <c r="D478" s="4"/>
       <c r="E478" s="4"/>
@@ -12608,8 +14614,12 @@
       <c r="T478" s="4"/>
       <c r="U478" s="4"/>
       <c r="V478" s="4"/>
-    </row>
-    <row r="479" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W478" s="4"/>
+      <c r="X478" s="4"/>
+      <c r="Y478" s="4"/>
+      <c r="Z478" s="4"/>
+    </row>
+    <row r="479" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C479" s="4"/>
       <c r="D479" s="4"/>
       <c r="E479" s="4"/>
@@ -12630,8 +14640,12 @@
       <c r="T479" s="4"/>
       <c r="U479" s="4"/>
       <c r="V479" s="4"/>
-    </row>
-    <row r="480" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W479" s="4"/>
+      <c r="X479" s="4"/>
+      <c r="Y479" s="4"/>
+      <c r="Z479" s="4"/>
+    </row>
+    <row r="480" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C480" s="4"/>
       <c r="D480" s="4"/>
       <c r="E480" s="4"/>
@@ -12652,8 +14666,12 @@
       <c r="T480" s="4"/>
       <c r="U480" s="4"/>
       <c r="V480" s="4"/>
-    </row>
-    <row r="481" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W480" s="4"/>
+      <c r="X480" s="4"/>
+      <c r="Y480" s="4"/>
+      <c r="Z480" s="4"/>
+    </row>
+    <row r="481" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C481" s="4"/>
       <c r="D481" s="4"/>
       <c r="E481" s="4"/>
@@ -12674,8 +14692,12 @@
       <c r="T481" s="4"/>
       <c r="U481" s="4"/>
       <c r="V481" s="4"/>
-    </row>
-    <row r="482" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W481" s="4"/>
+      <c r="X481" s="4"/>
+      <c r="Y481" s="4"/>
+      <c r="Z481" s="4"/>
+    </row>
+    <row r="482" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C482" s="4"/>
       <c r="D482" s="4"/>
       <c r="E482" s="4"/>
@@ -12696,8 +14718,12 @@
       <c r="T482" s="4"/>
       <c r="U482" s="4"/>
       <c r="V482" s="4"/>
-    </row>
-    <row r="483" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W482" s="4"/>
+      <c r="X482" s="4"/>
+      <c r="Y482" s="4"/>
+      <c r="Z482" s="4"/>
+    </row>
+    <row r="483" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C483" s="4"/>
       <c r="D483" s="4"/>
       <c r="E483" s="4"/>
@@ -12718,8 +14744,12 @@
       <c r="T483" s="4"/>
       <c r="U483" s="4"/>
       <c r="V483" s="4"/>
-    </row>
-    <row r="484" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W483" s="4"/>
+      <c r="X483" s="4"/>
+      <c r="Y483" s="4"/>
+      <c r="Z483" s="4"/>
+    </row>
+    <row r="484" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C484" s="4"/>
       <c r="D484" s="4"/>
       <c r="E484" s="4"/>
@@ -12740,6 +14770,10 @@
       <c r="T484" s="4"/>
       <c r="U484" s="4"/>
       <c r="V484" s="4"/>
+      <c r="W484" s="4"/>
+      <c r="X484" s="4"/>
+      <c r="Y484" s="4"/>
+      <c r="Z484" s="4"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/AMZN.xlsx
+++ b/AMZN.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A7B6300-AD81-4C62-BA47-ADC8A3312120}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2820FBDD-20CD-4A72-9B49-C1F8526740C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" xr2:uid="{479CF3AA-260E-4E31-88AC-4C0599CDC74D}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" activeTab="1" xr2:uid="{479CF3AA-260E-4E31-88AC-4C0599CDC74D}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -266,13 +266,19 @@
     <numFmt numFmtId="164" formatCode="#,##0;\(#,##0\)"/>
     <numFmt numFmtId="165" formatCode="#,##0.00;\(#,##0.00\)"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -356,31 +362,34 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -744,7 +753,7 @@
         <v>4</v>
       </c>
       <c r="I3" s="2">
-        <v>257.5</v>
+        <v>261.29000000000002</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
@@ -755,10 +764,10 @@
         <v>5</v>
       </c>
       <c r="I4" s="4">
-        <v>10757.109436000001</v>
-      </c>
-      <c r="J4" s="15" t="s">
-        <v>69</v>
+        <v>10786.313571999999</v>
+      </c>
+      <c r="J4" s="16" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
@@ -767,7 +776,7 @@
       </c>
       <c r="I5" s="4">
         <f>I3*I4</f>
-        <v>2769955.6797700003</v>
+        <v>2818355.8732278799</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
@@ -781,11 +790,11 @@
         <v>7</v>
       </c>
       <c r="I6" s="4">
-        <f>101816+41273</f>
-        <v>143089</v>
-      </c>
-      <c r="J6" s="15" t="s">
-        <v>69</v>
+        <f>86810+36219</f>
+        <v>123029</v>
+      </c>
+      <c r="J6" s="16" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
@@ -793,10 +802,10 @@
         <v>8</v>
       </c>
       <c r="I7" s="4">
-        <v>119074</v>
-      </c>
-      <c r="J7" s="15" t="s">
-        <v>69</v>
+        <v>65648</v>
+      </c>
+      <c r="J7" s="16" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
@@ -805,7 +814,7 @@
       </c>
       <c r="I8" s="4">
         <f>I5-I6+I7</f>
-        <v>2745940.6797700003</v>
+        <v>2760974.8732278799</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
@@ -989,7 +998,9 @@
       <c r="O3" s="4">
         <v>104143</v>
       </c>
-      <c r="P3" s="4"/>
+      <c r="P3" s="4">
+        <v>116177</v>
+      </c>
       <c r="Q3" s="4"/>
       <c r="R3" s="4"/>
       <c r="S3" s="4"/>
@@ -1053,7 +1064,9 @@
       <c r="O4" s="14">
         <v>39789</v>
       </c>
-      <c r="P4" s="14"/>
+      <c r="P4" s="14">
+        <v>42197</v>
+      </c>
       <c r="Q4" s="14"/>
       <c r="R4" s="14"/>
       <c r="S4" s="4"/>
@@ -1117,7 +1130,9 @@
       <c r="O5" s="4">
         <v>37587</v>
       </c>
-      <c r="P5" s="4"/>
+      <c r="P5" s="4">
+        <v>42232</v>
+      </c>
       <c r="Q5" s="4"/>
       <c r="R5" s="4"/>
       <c r="S5" s="4"/>
@@ -1181,7 +1196,9 @@
       <c r="O6" s="4">
         <v>71304</v>
       </c>
-      <c r="P6" s="4"/>
+      <c r="P6" s="4">
+        <v>77602</v>
+      </c>
       <c r="Q6" s="4"/>
       <c r="R6" s="4"/>
       <c r="S6" s="4"/>
@@ -1247,7 +1264,9 @@
       <c r="O7" s="4">
         <v>110215</v>
       </c>
-      <c r="P7" s="4"/>
+      <c r="P7" s="4">
+        <v>123004</v>
+      </c>
       <c r="Q7" s="4"/>
       <c r="R7" s="4"/>
       <c r="S7" s="4"/>
@@ -1297,7 +1316,7 @@
         <v>147977</v>
       </c>
       <c r="I8" s="9">
-        <f t="shared" ref="I8:O8" si="3">SUM(I6:I7)</f>
+        <f t="shared" ref="I8:P8" si="3">SUM(I6:I7)</f>
         <v>158877</v>
       </c>
       <c r="J8" s="9">
@@ -1324,7 +1343,10 @@
         <f t="shared" si="3"/>
         <v>181519</v>
       </c>
-      <c r="P8" s="9"/>
+      <c r="P8" s="9">
+        <f t="shared" si="3"/>
+        <v>200606</v>
+      </c>
       <c r="Q8" s="9"/>
       <c r="R8" s="9"/>
       <c r="S8" s="4"/>
@@ -1391,7 +1413,9 @@
       <c r="O9" s="4">
         <v>87463</v>
       </c>
-      <c r="P9" s="4"/>
+      <c r="P9" s="4">
+        <v>95778</v>
+      </c>
       <c r="Q9" s="4"/>
       <c r="R9" s="4"/>
       <c r="S9" s="4"/>
@@ -1468,7 +1492,10 @@
         <f>O8-O9</f>
         <v>94056</v>
       </c>
-      <c r="P10" s="4"/>
+      <c r="P10" s="4">
+        <f>P8-P9</f>
+        <v>104828</v>
+      </c>
       <c r="Q10" s="4"/>
       <c r="R10" s="4"/>
       <c r="S10" s="4"/>
@@ -1541,7 +1568,9 @@
       <c r="O11" s="4">
         <v>27289</v>
       </c>
-      <c r="P11" s="4"/>
+      <c r="P11" s="4">
+        <v>29633</v>
+      </c>
       <c r="Q11" s="4"/>
       <c r="R11" s="4"/>
       <c r="S11" s="4"/>
@@ -1607,7 +1636,9 @@
       <c r="O12" s="4">
         <v>29567</v>
       </c>
-      <c r="P12" s="4"/>
+      <c r="P12" s="4">
+        <v>33158</v>
+      </c>
       <c r="Q12" s="4"/>
       <c r="R12" s="4"/>
       <c r="S12" s="4"/>
@@ -1673,7 +1704,9 @@
       <c r="O13" s="4">
         <v>10314</v>
       </c>
-      <c r="P13" s="4"/>
+      <c r="P13" s="4">
+        <v>11698</v>
+      </c>
       <c r="Q13" s="4"/>
       <c r="R13" s="4"/>
       <c r="S13" s="4"/>
@@ -1739,7 +1772,9 @@
       <c r="O14" s="4">
         <v>2587</v>
       </c>
-      <c r="P14" s="4"/>
+      <c r="P14" s="4">
+        <v>2788</v>
+      </c>
       <c r="Q14" s="4"/>
       <c r="R14" s="4"/>
       <c r="S14" s="4"/>
@@ -1805,7 +1840,9 @@
       <c r="O15" s="4">
         <v>447</v>
       </c>
-      <c r="P15" s="4"/>
+      <c r="P15" s="4">
+        <v>90</v>
+      </c>
       <c r="Q15" s="4"/>
       <c r="R15" s="4"/>
       <c r="S15" s="4"/>
@@ -1882,7 +1919,10 @@
         <f>O10-SUM(O11:O15)</f>
         <v>23852</v>
       </c>
-      <c r="P16" s="4"/>
+      <c r="P16" s="4">
+        <f>P10-SUM(P11:P15)</f>
+        <v>27461</v>
+      </c>
       <c r="Q16" s="4"/>
       <c r="R16" s="4"/>
       <c r="S16" s="4"/>
@@ -1964,7 +2004,9 @@
       <c r="O17" s="4">
         <v>1135</v>
       </c>
-      <c r="P17" s="4"/>
+      <c r="P17" s="4">
+        <v>1295</v>
+      </c>
       <c r="Q17" s="4"/>
       <c r="R17" s="4"/>
       <c r="S17" s="4"/>
@@ -2030,7 +2072,9 @@
       <c r="O18" s="4">
         <v>800</v>
       </c>
-      <c r="P18" s="4"/>
+      <c r="P18" s="4">
+        <v>1314</v>
+      </c>
       <c r="Q18" s="4"/>
       <c r="R18" s="4"/>
       <c r="S18" s="4"/>
@@ -2096,7 +2140,9 @@
       <c r="O19" s="4">
         <v>-15647</v>
       </c>
-      <c r="P19" s="4"/>
+      <c r="P19" s="4">
+        <v>-53415</v>
+      </c>
       <c r="Q19" s="4"/>
       <c r="R19" s="4"/>
       <c r="S19" s="4"/>
@@ -2173,7 +2219,10 @@
         <f t="shared" si="10"/>
         <v>39834</v>
       </c>
-      <c r="P20" s="4"/>
+      <c r="P20" s="4">
+        <f t="shared" si="10"/>
+        <v>80857</v>
+      </c>
       <c r="Q20" s="4"/>
       <c r="R20" s="4"/>
       <c r="S20" s="4"/>
@@ -2257,7 +2306,9 @@
       <c r="O21" s="4">
         <v>9560</v>
       </c>
-      <c r="P21" s="4"/>
+      <c r="P21" s="4">
+        <v>18199</v>
+      </c>
       <c r="Q21" s="4"/>
       <c r="R21" s="4"/>
       <c r="S21" s="4"/>
@@ -2323,7 +2374,9 @@
       <c r="O22" s="4">
         <v>19</v>
       </c>
-      <c r="P22" s="4"/>
+      <c r="P22" s="4">
+        <v>11</v>
+      </c>
       <c r="Q22" s="4"/>
       <c r="R22" s="4"/>
       <c r="S22" s="4"/>
@@ -2377,7 +2430,7 @@
         <v>15328</v>
       </c>
       <c r="J23" s="4">
-        <f t="shared" ref="J22:AA23" si="12">+J20-J21-J22</f>
+        <f t="shared" ref="J23:AA23" si="12">+J20-J21-J22</f>
         <v>20004</v>
       </c>
       <c r="K23" s="4">
@@ -2400,7 +2453,10 @@
         <f t="shared" si="12"/>
         <v>30255</v>
       </c>
-      <c r="P23" s="4"/>
+      <c r="P23" s="4">
+        <f t="shared" si="12"/>
+        <v>62647</v>
+      </c>
       <c r="Q23" s="4"/>
       <c r="R23" s="4"/>
       <c r="S23" s="4"/>
@@ -2496,52 +2552,55 @@
         <v>1.4596705075707075</v>
       </c>
       <c r="J25" s="10">
-        <f>J23/J26</f>
+        <f t="shared" ref="J25:P25" si="15">J23/J26</f>
         <v>1.9100544256659984</v>
       </c>
       <c r="K25" s="10">
-        <f>K23/K26</f>
+        <f t="shared" si="15"/>
         <v>1.6152975572951052</v>
       </c>
       <c r="L25" s="10">
-        <f>L23/L26</f>
+        <f t="shared" si="15"/>
         <v>1.7076243301682805</v>
       </c>
       <c r="M25" s="10">
-        <f>M23/M26</f>
+        <f t="shared" si="15"/>
         <v>1.984916619823871</v>
       </c>
       <c r="N25" s="10">
-        <f>N23/N26</f>
+        <f t="shared" si="15"/>
         <v>1.9788962554860399</v>
       </c>
       <c r="O25" s="10">
-        <f>O23/O26</f>
+        <f t="shared" si="15"/>
         <v>2.8162524434515497</v>
       </c>
-      <c r="P25" s="10"/>
+      <c r="P25" s="10">
+        <f t="shared" si="15"/>
+        <v>5.8173460859875572</v>
+      </c>
       <c r="Q25" s="10"/>
       <c r="R25" s="10"/>
       <c r="S25" s="4"/>
       <c r="T25" s="4"/>
       <c r="U25" s="10" t="e">
-        <f t="shared" ref="U25:Y25" si="15">+U23/U26</f>
+        <f t="shared" ref="U25:Y25" si="16">+U23/U26</f>
         <v>#DIV/0!</v>
       </c>
       <c r="V25" s="10" t="e">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W25" s="10" t="e">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X25" s="10">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-0.2671508489547551</v>
       </c>
       <c r="Y25" s="10">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>2.9527368012422359</v>
       </c>
       <c r="Z25" s="10">
@@ -2596,7 +2655,9 @@
       <c r="O26" s="4">
         <v>10743</v>
       </c>
-      <c r="P26" s="4"/>
+      <c r="P26" s="4">
+        <v>10769</v>
+      </c>
       <c r="Q26" s="4"/>
       <c r="R26" s="4"/>
       <c r="S26" s="4"/>
@@ -2660,38 +2721,41 @@
         <v>0.17247354125690739</v>
       </c>
       <c r="H28" s="11">
-        <f t="shared" ref="H28:O28" si="16">H5/D5-1</f>
+        <f t="shared" ref="H28:P28" si="17">H5/D5-1</f>
         <v>0.18703703703703711</v>
       </c>
       <c r="I28" s="11">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0.1905112971074201</v>
       </c>
       <c r="J28" s="11">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-0.30540209484288683</v>
       </c>
       <c r="K28" s="11">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0.1689499540679793</v>
       </c>
       <c r="L28" s="11">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0.17472698907956308</v>
       </c>
       <c r="M28" s="11">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0.20231677109135937</v>
       </c>
       <c r="N28" s="11">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0.28046498236521988</v>
       </c>
       <c r="O28" s="11">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0.28427922233231961</v>
       </c>
-      <c r="P28" s="11"/>
+      <c r="P28" s="11">
+        <f t="shared" si="17"/>
+        <v>0.36792666731448187</v>
+      </c>
       <c r="Q28" s="11"/>
       <c r="R28" s="11"/>
       <c r="S28" s="4"/>
@@ -2716,38 +2780,41 @@
         <v>6.9040557378775347E-2</v>
       </c>
       <c r="H29" s="11">
-        <f t="shared" ref="H29:H30" si="17">H6/D6-1</f>
+        <f t="shared" ref="H29:H30" si="18">H6/D6-1</f>
         <v>4.2976690608483636E-2</v>
       </c>
       <c r="I29" s="11">
-        <f t="shared" ref="I29:O31" si="18">I6/E6-1</f>
+        <f t="shared" ref="I29:P31" si="19">I6/E6-1</f>
         <v>7.0127115290243847E-2</v>
       </c>
       <c r="J29" s="11">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-0.11705520418353432</v>
       </c>
       <c r="K29" s="11">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>5.0151850939834208E-2</v>
       </c>
       <c r="L29" s="11">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0.10844743296139292</v>
       </c>
       <c r="M29" s="11">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>9.5516338515702515E-2</v>
       </c>
       <c r="N29" s="11">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>9.4447011894048138E-2</v>
       </c>
       <c r="O29" s="11">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0.1146474910114117</v>
       </c>
-      <c r="P29" s="11"/>
+      <c r="P29" s="11">
+        <f t="shared" si="19"/>
+        <v>0.13709228379685245</v>
+      </c>
       <c r="Q29" s="11"/>
       <c r="R29" s="11"/>
       <c r="S29" s="4"/>
@@ -2772,38 +2839,41 @@
         <v>0.17080864486977276</v>
       </c>
       <c r="H30" s="11">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.14673992382317413</v>
       </c>
       <c r="I30" s="11">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0.14220642706977671</v>
       </c>
       <c r="J30" s="11">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-0.24600022855836812</v>
       </c>
       <c r="K30" s="11">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0.11285468093885775</v>
       </c>
       <c r="L30" s="11">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0.15100453661697988</v>
       </c>
       <c r="M30" s="11">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0.16252903282352427</v>
       </c>
       <c r="N30" s="11">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0.168880131860637</v>
       </c>
       <c r="O30" s="11">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0.20194771911840093</v>
       </c>
-      <c r="P30" s="11"/>
+      <c r="P30" s="11">
+        <f t="shared" si="19"/>
+        <v>0.23676801801801806</v>
+      </c>
       <c r="Q30" s="11"/>
       <c r="R30" s="11"/>
       <c r="S30" s="4"/>
@@ -2832,34 +2902,37 @@
         <v>0.10115862869559389</v>
       </c>
       <c r="I31" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0.11038348371225104</v>
       </c>
       <c r="J31" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-0.19449246144937482</v>
       </c>
       <c r="K31" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>8.6202926461660834E-2</v>
       </c>
       <c r="L31" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0.13329774221669588</v>
       </c>
       <c r="M31" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0.13401562214795093</v>
       </c>
       <c r="N31" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0.13628908579705201</v>
       </c>
       <c r="O31" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0.16607244952366274</v>
       </c>
-      <c r="P31" s="12"/>
+      <c r="P31" s="12">
+        <f t="shared" si="19"/>
+        <v>0.19620517346245125</v>
+      </c>
       <c r="Q31" s="12"/>
       <c r="R31" s="12"/>
       <c r="S31" s="4"/>
@@ -2876,23 +2949,23 @@
         <v>38</v>
       </c>
       <c r="C32" s="11">
-        <f t="shared" ref="C32:G32" si="19">C10/C8</f>
+        <f t="shared" ref="C32:G32" si="20">C10/C8</f>
         <v>0.46771306082067871</v>
       </c>
       <c r="D32" s="11">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0.48376654785203488</v>
       </c>
       <c r="E32" s="11">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0.47567495789157344</v>
       </c>
       <c r="F32" s="11">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0.51057541767645354</v>
       </c>
       <c r="G32" s="11">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0.49318624269954575</v>
       </c>
       <c r="H32" s="11">
@@ -2900,11 +2973,11 @@
         <v>0.50137521371564497</v>
       </c>
       <c r="I32" s="11">
-        <f t="shared" ref="I32:J32" si="20">I10/I8</f>
+        <f t="shared" ref="I32:J32" si="21">I10/I8</f>
         <v>0.49031640829069029</v>
       </c>
       <c r="J32" s="11">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0.47339077276987307</v>
       </c>
       <c r="K32" s="11">
@@ -2927,7 +3000,10 @@
         <f>O10/O8</f>
         <v>0.51816063332213158</v>
       </c>
-      <c r="P32" s="11"/>
+      <c r="P32" s="11">
+        <f>P10/P8</f>
+        <v>0.52255665334037871</v>
+      </c>
       <c r="Q32" s="11"/>
       <c r="R32" s="11"/>
       <c r="S32" s="4"/>
@@ -2944,23 +3020,23 @@
         <v>37</v>
       </c>
       <c r="C33" s="11">
-        <f t="shared" ref="C33:G33" si="21">C16/C8</f>
+        <f t="shared" ref="C33:G33" si="22">C16/C8</f>
         <v>3.7484885126964934E-2</v>
       </c>
       <c r="D33" s="11">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>5.7157527365812637E-2</v>
       </c>
       <c r="E33" s="11">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>7.8192377850618167E-2</v>
       </c>
       <c r="F33" s="11">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0.1928067428743003</v>
       </c>
       <c r="G33" s="11">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0.10680817511321374</v>
       </c>
       <c r="H33" s="11">
@@ -2968,34 +3044,37 @@
         <v>9.9150543665569649E-2</v>
       </c>
       <c r="I33" s="11">
-        <f t="shared" ref="I33:J33" si="22">I16/I8</f>
+        <f t="shared" ref="I33:J33" si="23">I16/I8</f>
         <v>0.1095879202150091</v>
       </c>
       <c r="J33" s="11">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0.1129068330919315</v>
       </c>
       <c r="K33" s="11">
-        <f t="shared" ref="K33:L33" si="23">K16/K8</f>
+        <f t="shared" ref="K33:L33" si="24">K16/K8</f>
         <v>0.11823315153500742</v>
       </c>
       <c r="L33" s="11">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0.11431586981669867</v>
       </c>
       <c r="M33" s="11">
-        <f t="shared" ref="M33:N33" si="24">M16/M8</f>
+        <f t="shared" ref="M33:N33" si="25">M16/M8</f>
         <v>9.6698100117112273E-2</v>
       </c>
       <c r="N33" s="11">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0.11705079058607407</v>
       </c>
       <c r="O33" s="11">
-        <f t="shared" ref="O33" si="25">O16/O8</f>
+        <f t="shared" ref="O33:P33" si="26">O16/O8</f>
         <v>0.13140222235688825</v>
       </c>
-      <c r="P33" s="11"/>
+      <c r="P33" s="11">
+        <f t="shared" si="26"/>
+        <v>0.1368902226254449</v>
+      </c>
       <c r="Q33" s="11"/>
       <c r="R33" s="11"/>
       <c r="S33" s="4"/>
@@ -3012,23 +3091,23 @@
         <v>39</v>
       </c>
       <c r="C34" s="11">
-        <f t="shared" ref="C34:G34" si="26">C21/C20</f>
+        <f t="shared" ref="C34:G34" si="27">C21/C20</f>
         <v>0.23015294974508377</v>
       </c>
       <c r="D34" s="11">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0.10630702102340341</v>
       </c>
       <c r="E34" s="11">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0.18918697185987365</v>
       </c>
       <c r="F34" s="11">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0.11637574592673715</v>
       </c>
       <c r="G34" s="11">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0.1900177154740815</v>
       </c>
       <c r="H34" s="11">
@@ -3036,34 +3115,37 @@
         <v>0.11590685470646113</v>
       </c>
       <c r="I34" s="11">
-        <f t="shared" ref="I34:J34" si="27">I21/I20</f>
+        <f t="shared" ref="I34:J34" si="28">I21/I20</f>
         <v>0.15002494871652713</v>
       </c>
       <c r="J34" s="11">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0.10403150029084075</v>
       </c>
       <c r="K34" s="11">
-        <f t="shared" ref="K34:L34" si="28">K21/K20</f>
+        <f t="shared" ref="K34:L34" si="29">K21/K20</f>
         <v>0.21001891231145348</v>
       </c>
       <c r="L34" s="11">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0.1283981397132857</v>
       </c>
       <c r="M34" s="11">
-        <f t="shared" ref="M34:N34" si="29">M21/M20</f>
+        <f t="shared" ref="M34:N34" si="30">M21/M20</f>
         <v>0.2452964146254881</v>
       </c>
       <c r="N34" s="11">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0.18590490509302762</v>
       </c>
       <c r="O34" s="11">
-        <f t="shared" ref="O34" si="30">O21/O20</f>
+        <f t="shared" ref="O34:P34" si="31">O21/O20</f>
         <v>0.23999598333082292</v>
       </c>
-      <c r="P34" s="11"/>
+      <c r="P34" s="11">
+        <f t="shared" si="31"/>
+        <v>0.22507636939287878</v>
+      </c>
       <c r="Q34" s="11"/>
       <c r="R34" s="11"/>
       <c r="S34" s="4"/>
